--- a/assets/examples/OUTPUT/customs-declaration-draft.xlsx
+++ b/assets/examples/OUTPUT/customs-declaration-draft.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10308"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wujunye/Desktop/报关单/customs-declaration-safe/assets/examples/OUTPUT/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B634DC36-FAE8-AF45-8877-F83C094792AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11805"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -237,21 +243,17 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="7">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.0000"/>
-    <numFmt numFmtId="177" formatCode="0.00_ "/>
-    <numFmt numFmtId="178" formatCode="0.0000_);[Red]\(0.0000\)"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
+    <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="0.00_ "/>
+    <numFmt numFmtId="170" formatCode="0.0000_);[Red]\(0.0000\)"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -313,346 +315,16 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="40">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -1001,253 +673,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="36" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="37" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1261,6 +691,102 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1273,9 +799,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -1284,15 +807,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
@@ -1321,9 +835,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -1333,18 +844,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -1353,6 +852,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
@@ -1375,35 +877,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
@@ -1413,12 +897,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1438,9 +916,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1456,31 +931,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1489,22 +952,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1513,96 +967,40 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="IV"/>
@@ -1619,50 +1017,40 @@
           <cell r="D9">
             <v>125</v>
           </cell>
-        </row>
-        <row r="9">
           <cell r="F9">
-            <v>4.35090909090909</v>
+            <v>4.3509090909090897</v>
           </cell>
         </row>
         <row r="10">
           <cell r="D10">
             <v>192</v>
           </cell>
-        </row>
-        <row r="10">
           <cell r="F10">
-            <v>9.12181818181818</v>
+            <v>9.1218181818181794</v>
           </cell>
         </row>
         <row r="11">
           <cell r="D11">
             <v>66</v>
           </cell>
-        </row>
-        <row r="11">
           <cell r="F11">
-            <v>18.6290909090909</v>
+            <v>18.629090909090898</v>
           </cell>
         </row>
         <row r="12">
           <cell r="D12">
             <v>30</v>
           </cell>
-        </row>
-        <row r="12">
           <cell r="F12">
-            <v>20.4927272727273</v>
+            <v>20.492727272727301</v>
           </cell>
         </row>
         <row r="13">
           <cell r="D13">
             <v>40</v>
           </cell>
-        </row>
-        <row r="13">
           <cell r="F13">
-            <v>30.2072727272727</v>
+            <v>30.207272727272699</v>
           </cell>
         </row>
       </sheetData>
@@ -1671,8 +1059,6 @@
           <cell r="B9">
             <v>3918909000</v>
           </cell>
-        </row>
-        <row r="9">
           <cell r="G9">
             <v>75</v>
           </cell>
@@ -1715,7 +1101,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="sheet"/>
@@ -2014,2088 +1400,2024 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:XEP34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="2" max="2" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" style="3" customWidth="1"/>
     <col min="3" max="3" width="6" style="3" customWidth="1"/>
-    <col min="4" max="4" width="25.45" style="3" customWidth="1"/>
-    <col min="5" max="5" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="6" max="6" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="4" max="4" width="25.5" style="3" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" style="3" customWidth="1"/>
     <col min="7" max="7" width="11" style="3" customWidth="1"/>
-    <col min="8" max="8" width="6.725" style="3" customWidth="1"/>
-    <col min="9" max="9" width="7.90833333333333" style="4" customWidth="1"/>
-    <col min="10" max="10" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="11" max="11" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="12" max="12" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="13" max="13" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="14" max="14" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="15" max="15" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="16" max="16" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="17" max="17" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="18" max="18" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="19" max="19" width="8.45" style="3" customWidth="1"/>
+    <col min="8" max="8" width="6.6640625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="7.83203125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="7.1640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="7.6640625" style="3" customWidth="1"/>
+    <col min="12" max="13" width="5.33203125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="5.1640625" style="3" customWidth="1"/>
+    <col min="15" max="15" width="7.33203125" style="3" customWidth="1"/>
+    <col min="16" max="16" width="4.1640625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="6.33203125" style="3" customWidth="1"/>
+    <col min="18" max="18" width="7.6640625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="8.5" style="3" customWidth="1"/>
     <col min="20" max="242" width="9" style="3"/>
-    <col min="243" max="243" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="244" max="244" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="243" max="243" width="6.33203125" style="3" customWidth="1"/>
+    <col min="244" max="244" width="7.33203125" style="3" customWidth="1"/>
     <col min="245" max="245" width="6" style="3" customWidth="1"/>
-    <col min="246" max="246" width="25.45" style="3" customWidth="1"/>
-    <col min="247" max="247" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="248" max="248" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="246" max="246" width="25.5" style="3" customWidth="1"/>
+    <col min="247" max="247" width="10.83203125" style="3" customWidth="1"/>
+    <col min="248" max="248" width="12.33203125" style="3" customWidth="1"/>
     <col min="249" max="249" width="11" style="3" customWidth="1"/>
-    <col min="250" max="250" width="6.725" style="3" customWidth="1"/>
-    <col min="251" max="251" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="252" max="252" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="253" max="253" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="254" max="254" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="255" max="255" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="256" max="256" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="257" max="257" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="258" max="258" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="259" max="259" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="260" max="260" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="261" max="261" width="8.45" style="3" customWidth="1"/>
-    <col min="262" max="262" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="263" max="263" width="7.725" style="3" customWidth="1"/>
-    <col min="264" max="264" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="250" max="250" width="6.6640625" style="3" customWidth="1"/>
+    <col min="251" max="251" width="7.83203125" style="3" customWidth="1"/>
+    <col min="252" max="252" width="7.1640625" style="3" customWidth="1"/>
+    <col min="253" max="253" width="7.6640625" style="3" customWidth="1"/>
+    <col min="254" max="255" width="5.33203125" style="3" customWidth="1"/>
+    <col min="256" max="256" width="5.1640625" style="3" customWidth="1"/>
+    <col min="257" max="257" width="7.33203125" style="3" customWidth="1"/>
+    <col min="258" max="258" width="4.1640625" style="3" customWidth="1"/>
+    <col min="259" max="259" width="6.33203125" style="3" customWidth="1"/>
+    <col min="260" max="260" width="7.6640625" style="3" customWidth="1"/>
+    <col min="261" max="261" width="8.5" style="3" customWidth="1"/>
+    <col min="262" max="262" width="8.33203125" style="3" customWidth="1"/>
+    <col min="263" max="263" width="7.6640625" style="3" customWidth="1"/>
+    <col min="264" max="264" width="6.83203125" style="3" customWidth="1"/>
     <col min="265" max="498" width="9" style="3"/>
-    <col min="499" max="499" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="500" max="500" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="499" max="499" width="6.33203125" style="3" customWidth="1"/>
+    <col min="500" max="500" width="7.33203125" style="3" customWidth="1"/>
     <col min="501" max="501" width="6" style="3" customWidth="1"/>
-    <col min="502" max="502" width="25.45" style="3" customWidth="1"/>
-    <col min="503" max="503" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="504" max="504" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="502" max="502" width="25.5" style="3" customWidth="1"/>
+    <col min="503" max="503" width="10.83203125" style="3" customWidth="1"/>
+    <col min="504" max="504" width="12.33203125" style="3" customWidth="1"/>
     <col min="505" max="505" width="11" style="3" customWidth="1"/>
-    <col min="506" max="506" width="6.725" style="3" customWidth="1"/>
-    <col min="507" max="507" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="508" max="508" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="509" max="509" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="510" max="510" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="511" max="511" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="512" max="512" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="513" max="513" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="514" max="514" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="515" max="515" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="516" max="516" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="517" max="517" width="8.45" style="3" customWidth="1"/>
-    <col min="518" max="518" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="519" max="519" width="7.725" style="3" customWidth="1"/>
-    <col min="520" max="520" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="506" max="506" width="6.6640625" style="3" customWidth="1"/>
+    <col min="507" max="507" width="7.83203125" style="3" customWidth="1"/>
+    <col min="508" max="508" width="7.1640625" style="3" customWidth="1"/>
+    <col min="509" max="509" width="7.6640625" style="3" customWidth="1"/>
+    <col min="510" max="511" width="5.33203125" style="3" customWidth="1"/>
+    <col min="512" max="512" width="5.1640625" style="3" customWidth="1"/>
+    <col min="513" max="513" width="7.33203125" style="3" customWidth="1"/>
+    <col min="514" max="514" width="4.1640625" style="3" customWidth="1"/>
+    <col min="515" max="515" width="6.33203125" style="3" customWidth="1"/>
+    <col min="516" max="516" width="7.6640625" style="3" customWidth="1"/>
+    <col min="517" max="517" width="8.5" style="3" customWidth="1"/>
+    <col min="518" max="518" width="8.33203125" style="3" customWidth="1"/>
+    <col min="519" max="519" width="7.6640625" style="3" customWidth="1"/>
+    <col min="520" max="520" width="6.83203125" style="3" customWidth="1"/>
     <col min="521" max="754" width="9" style="3"/>
-    <col min="755" max="755" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="756" max="756" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="755" max="755" width="6.33203125" style="3" customWidth="1"/>
+    <col min="756" max="756" width="7.33203125" style="3" customWidth="1"/>
     <col min="757" max="757" width="6" style="3" customWidth="1"/>
-    <col min="758" max="758" width="25.45" style="3" customWidth="1"/>
-    <col min="759" max="759" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="760" max="760" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="758" max="758" width="25.5" style="3" customWidth="1"/>
+    <col min="759" max="759" width="10.83203125" style="3" customWidth="1"/>
+    <col min="760" max="760" width="12.33203125" style="3" customWidth="1"/>
     <col min="761" max="761" width="11" style="3" customWidth="1"/>
-    <col min="762" max="762" width="6.725" style="3" customWidth="1"/>
-    <col min="763" max="763" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="764" max="764" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="765" max="765" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="766" max="766" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="767" max="767" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="768" max="768" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="769" max="769" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="770" max="770" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="771" max="771" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="772" max="772" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="773" max="773" width="8.45" style="3" customWidth="1"/>
-    <col min="774" max="774" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="775" max="775" width="7.725" style="3" customWidth="1"/>
-    <col min="776" max="776" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="762" max="762" width="6.6640625" style="3" customWidth="1"/>
+    <col min="763" max="763" width="7.83203125" style="3" customWidth="1"/>
+    <col min="764" max="764" width="7.1640625" style="3" customWidth="1"/>
+    <col min="765" max="765" width="7.6640625" style="3" customWidth="1"/>
+    <col min="766" max="767" width="5.33203125" style="3" customWidth="1"/>
+    <col min="768" max="768" width="5.1640625" style="3" customWidth="1"/>
+    <col min="769" max="769" width="7.33203125" style="3" customWidth="1"/>
+    <col min="770" max="770" width="4.1640625" style="3" customWidth="1"/>
+    <col min="771" max="771" width="6.33203125" style="3" customWidth="1"/>
+    <col min="772" max="772" width="7.6640625" style="3" customWidth="1"/>
+    <col min="773" max="773" width="8.5" style="3" customWidth="1"/>
+    <col min="774" max="774" width="8.33203125" style="3" customWidth="1"/>
+    <col min="775" max="775" width="7.6640625" style="3" customWidth="1"/>
+    <col min="776" max="776" width="6.83203125" style="3" customWidth="1"/>
     <col min="777" max="1010" width="9" style="3"/>
-    <col min="1011" max="1011" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="1012" max="1012" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="1011" max="1011" width="6.33203125" style="3" customWidth="1"/>
+    <col min="1012" max="1012" width="7.33203125" style="3" customWidth="1"/>
     <col min="1013" max="1013" width="6" style="3" customWidth="1"/>
-    <col min="1014" max="1014" width="25.45" style="3" customWidth="1"/>
-    <col min="1015" max="1015" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="1016" max="1016" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="1014" max="1014" width="25.5" style="3" customWidth="1"/>
+    <col min="1015" max="1015" width="10.83203125" style="3" customWidth="1"/>
+    <col min="1016" max="1016" width="12.33203125" style="3" customWidth="1"/>
     <col min="1017" max="1017" width="11" style="3" customWidth="1"/>
-    <col min="1018" max="1018" width="6.725" style="3" customWidth="1"/>
-    <col min="1019" max="1019" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="1020" max="1020" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="1021" max="1021" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="1022" max="1022" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="1023" max="1023" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="1024" max="1024" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="1025" max="1025" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="1026" max="1026" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="1027" max="1027" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="1028" max="1028" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="1029" max="1029" width="8.45" style="3" customWidth="1"/>
-    <col min="1030" max="1030" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="1031" max="1031" width="7.725" style="3" customWidth="1"/>
-    <col min="1032" max="1032" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="1018" max="1018" width="6.6640625" style="3" customWidth="1"/>
+    <col min="1019" max="1019" width="7.83203125" style="3" customWidth="1"/>
+    <col min="1020" max="1020" width="7.1640625" style="3" customWidth="1"/>
+    <col min="1021" max="1021" width="7.6640625" style="3" customWidth="1"/>
+    <col min="1022" max="1023" width="5.33203125" style="3" customWidth="1"/>
+    <col min="1024" max="1024" width="5.1640625" style="3" customWidth="1"/>
+    <col min="1025" max="1025" width="7.33203125" style="3" customWidth="1"/>
+    <col min="1026" max="1026" width="4.1640625" style="3" customWidth="1"/>
+    <col min="1027" max="1027" width="6.33203125" style="3" customWidth="1"/>
+    <col min="1028" max="1028" width="7.6640625" style="3" customWidth="1"/>
+    <col min="1029" max="1029" width="8.5" style="3" customWidth="1"/>
+    <col min="1030" max="1030" width="8.33203125" style="3" customWidth="1"/>
+    <col min="1031" max="1031" width="7.6640625" style="3" customWidth="1"/>
+    <col min="1032" max="1032" width="6.83203125" style="3" customWidth="1"/>
     <col min="1033" max="1266" width="9" style="3"/>
-    <col min="1267" max="1267" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="1268" max="1268" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="1267" max="1267" width="6.33203125" style="3" customWidth="1"/>
+    <col min="1268" max="1268" width="7.33203125" style="3" customWidth="1"/>
     <col min="1269" max="1269" width="6" style="3" customWidth="1"/>
-    <col min="1270" max="1270" width="25.45" style="3" customWidth="1"/>
-    <col min="1271" max="1271" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="1272" max="1272" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="1270" max="1270" width="25.5" style="3" customWidth="1"/>
+    <col min="1271" max="1271" width="10.83203125" style="3" customWidth="1"/>
+    <col min="1272" max="1272" width="12.33203125" style="3" customWidth="1"/>
     <col min="1273" max="1273" width="11" style="3" customWidth="1"/>
-    <col min="1274" max="1274" width="6.725" style="3" customWidth="1"/>
-    <col min="1275" max="1275" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="1276" max="1276" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="1277" max="1277" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="1278" max="1278" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="1279" max="1279" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="1280" max="1280" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="1281" max="1281" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="1282" max="1282" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="1283" max="1283" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="1284" max="1284" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="1285" max="1285" width="8.45" style="3" customWidth="1"/>
-    <col min="1286" max="1286" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="1287" max="1287" width="7.725" style="3" customWidth="1"/>
-    <col min="1288" max="1288" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="1274" max="1274" width="6.6640625" style="3" customWidth="1"/>
+    <col min="1275" max="1275" width="7.83203125" style="3" customWidth="1"/>
+    <col min="1276" max="1276" width="7.1640625" style="3" customWidth="1"/>
+    <col min="1277" max="1277" width="7.6640625" style="3" customWidth="1"/>
+    <col min="1278" max="1279" width="5.33203125" style="3" customWidth="1"/>
+    <col min="1280" max="1280" width="5.1640625" style="3" customWidth="1"/>
+    <col min="1281" max="1281" width="7.33203125" style="3" customWidth="1"/>
+    <col min="1282" max="1282" width="4.1640625" style="3" customWidth="1"/>
+    <col min="1283" max="1283" width="6.33203125" style="3" customWidth="1"/>
+    <col min="1284" max="1284" width="7.6640625" style="3" customWidth="1"/>
+    <col min="1285" max="1285" width="8.5" style="3" customWidth="1"/>
+    <col min="1286" max="1286" width="8.33203125" style="3" customWidth="1"/>
+    <col min="1287" max="1287" width="7.6640625" style="3" customWidth="1"/>
+    <col min="1288" max="1288" width="6.83203125" style="3" customWidth="1"/>
     <col min="1289" max="1522" width="9" style="3"/>
-    <col min="1523" max="1523" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="1524" max="1524" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="1523" max="1523" width="6.33203125" style="3" customWidth="1"/>
+    <col min="1524" max="1524" width="7.33203125" style="3" customWidth="1"/>
     <col min="1525" max="1525" width="6" style="3" customWidth="1"/>
-    <col min="1526" max="1526" width="25.45" style="3" customWidth="1"/>
-    <col min="1527" max="1527" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="1528" max="1528" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="1526" max="1526" width="25.5" style="3" customWidth="1"/>
+    <col min="1527" max="1527" width="10.83203125" style="3" customWidth="1"/>
+    <col min="1528" max="1528" width="12.33203125" style="3" customWidth="1"/>
     <col min="1529" max="1529" width="11" style="3" customWidth="1"/>
-    <col min="1530" max="1530" width="6.725" style="3" customWidth="1"/>
-    <col min="1531" max="1531" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="1532" max="1532" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="1533" max="1533" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="1534" max="1534" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="1535" max="1535" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="1536" max="1536" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="1537" max="1537" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="1538" max="1538" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="1539" max="1539" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="1540" max="1540" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="1541" max="1541" width="8.45" style="3" customWidth="1"/>
-    <col min="1542" max="1542" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="1543" max="1543" width="7.725" style="3" customWidth="1"/>
-    <col min="1544" max="1544" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="1530" max="1530" width="6.6640625" style="3" customWidth="1"/>
+    <col min="1531" max="1531" width="7.83203125" style="3" customWidth="1"/>
+    <col min="1532" max="1532" width="7.1640625" style="3" customWidth="1"/>
+    <col min="1533" max="1533" width="7.6640625" style="3" customWidth="1"/>
+    <col min="1534" max="1535" width="5.33203125" style="3" customWidth="1"/>
+    <col min="1536" max="1536" width="5.1640625" style="3" customWidth="1"/>
+    <col min="1537" max="1537" width="7.33203125" style="3" customWidth="1"/>
+    <col min="1538" max="1538" width="4.1640625" style="3" customWidth="1"/>
+    <col min="1539" max="1539" width="6.33203125" style="3" customWidth="1"/>
+    <col min="1540" max="1540" width="7.6640625" style="3" customWidth="1"/>
+    <col min="1541" max="1541" width="8.5" style="3" customWidth="1"/>
+    <col min="1542" max="1542" width="8.33203125" style="3" customWidth="1"/>
+    <col min="1543" max="1543" width="7.6640625" style="3" customWidth="1"/>
+    <col min="1544" max="1544" width="6.83203125" style="3" customWidth="1"/>
     <col min="1545" max="1778" width="9" style="3"/>
-    <col min="1779" max="1779" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="1780" max="1780" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="1779" max="1779" width="6.33203125" style="3" customWidth="1"/>
+    <col min="1780" max="1780" width="7.33203125" style="3" customWidth="1"/>
     <col min="1781" max="1781" width="6" style="3" customWidth="1"/>
-    <col min="1782" max="1782" width="25.45" style="3" customWidth="1"/>
-    <col min="1783" max="1783" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="1784" max="1784" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="1782" max="1782" width="25.5" style="3" customWidth="1"/>
+    <col min="1783" max="1783" width="10.83203125" style="3" customWidth="1"/>
+    <col min="1784" max="1784" width="12.33203125" style="3" customWidth="1"/>
     <col min="1785" max="1785" width="11" style="3" customWidth="1"/>
-    <col min="1786" max="1786" width="6.725" style="3" customWidth="1"/>
-    <col min="1787" max="1787" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="1788" max="1788" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="1789" max="1789" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="1790" max="1790" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="1791" max="1791" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="1792" max="1792" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="1793" max="1793" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="1794" max="1794" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="1795" max="1795" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="1796" max="1796" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="1797" max="1797" width="8.45" style="3" customWidth="1"/>
-    <col min="1798" max="1798" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="1799" max="1799" width="7.725" style="3" customWidth="1"/>
-    <col min="1800" max="1800" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="1786" max="1786" width="6.6640625" style="3" customWidth="1"/>
+    <col min="1787" max="1787" width="7.83203125" style="3" customWidth="1"/>
+    <col min="1788" max="1788" width="7.1640625" style="3" customWidth="1"/>
+    <col min="1789" max="1789" width="7.6640625" style="3" customWidth="1"/>
+    <col min="1790" max="1791" width="5.33203125" style="3" customWidth="1"/>
+    <col min="1792" max="1792" width="5.1640625" style="3" customWidth="1"/>
+    <col min="1793" max="1793" width="7.33203125" style="3" customWidth="1"/>
+    <col min="1794" max="1794" width="4.1640625" style="3" customWidth="1"/>
+    <col min="1795" max="1795" width="6.33203125" style="3" customWidth="1"/>
+    <col min="1796" max="1796" width="7.6640625" style="3" customWidth="1"/>
+    <col min="1797" max="1797" width="8.5" style="3" customWidth="1"/>
+    <col min="1798" max="1798" width="8.33203125" style="3" customWidth="1"/>
+    <col min="1799" max="1799" width="7.6640625" style="3" customWidth="1"/>
+    <col min="1800" max="1800" width="6.83203125" style="3" customWidth="1"/>
     <col min="1801" max="2034" width="9" style="3"/>
-    <col min="2035" max="2035" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="2036" max="2036" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="2035" max="2035" width="6.33203125" style="3" customWidth="1"/>
+    <col min="2036" max="2036" width="7.33203125" style="3" customWidth="1"/>
     <col min="2037" max="2037" width="6" style="3" customWidth="1"/>
-    <col min="2038" max="2038" width="25.45" style="3" customWidth="1"/>
-    <col min="2039" max="2039" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="2040" max="2040" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="2038" max="2038" width="25.5" style="3" customWidth="1"/>
+    <col min="2039" max="2039" width="10.83203125" style="3" customWidth="1"/>
+    <col min="2040" max="2040" width="12.33203125" style="3" customWidth="1"/>
     <col min="2041" max="2041" width="11" style="3" customWidth="1"/>
-    <col min="2042" max="2042" width="6.725" style="3" customWidth="1"/>
-    <col min="2043" max="2043" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="2044" max="2044" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="2045" max="2045" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="2046" max="2046" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="2047" max="2047" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="2048" max="2048" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="2049" max="2049" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="2050" max="2050" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="2051" max="2051" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="2052" max="2052" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="2053" max="2053" width="8.45" style="3" customWidth="1"/>
-    <col min="2054" max="2054" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="2055" max="2055" width="7.725" style="3" customWidth="1"/>
-    <col min="2056" max="2056" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="2042" max="2042" width="6.6640625" style="3" customWidth="1"/>
+    <col min="2043" max="2043" width="7.83203125" style="3" customWidth="1"/>
+    <col min="2044" max="2044" width="7.1640625" style="3" customWidth="1"/>
+    <col min="2045" max="2045" width="7.6640625" style="3" customWidth="1"/>
+    <col min="2046" max="2047" width="5.33203125" style="3" customWidth="1"/>
+    <col min="2048" max="2048" width="5.1640625" style="3" customWidth="1"/>
+    <col min="2049" max="2049" width="7.33203125" style="3" customWidth="1"/>
+    <col min="2050" max="2050" width="4.1640625" style="3" customWidth="1"/>
+    <col min="2051" max="2051" width="6.33203125" style="3" customWidth="1"/>
+    <col min="2052" max="2052" width="7.6640625" style="3" customWidth="1"/>
+    <col min="2053" max="2053" width="8.5" style="3" customWidth="1"/>
+    <col min="2054" max="2054" width="8.33203125" style="3" customWidth="1"/>
+    <col min="2055" max="2055" width="7.6640625" style="3" customWidth="1"/>
+    <col min="2056" max="2056" width="6.83203125" style="3" customWidth="1"/>
     <col min="2057" max="2290" width="9" style="3"/>
-    <col min="2291" max="2291" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="2292" max="2292" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="2291" max="2291" width="6.33203125" style="3" customWidth="1"/>
+    <col min="2292" max="2292" width="7.33203125" style="3" customWidth="1"/>
     <col min="2293" max="2293" width="6" style="3" customWidth="1"/>
-    <col min="2294" max="2294" width="25.45" style="3" customWidth="1"/>
-    <col min="2295" max="2295" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="2296" max="2296" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="2294" max="2294" width="25.5" style="3" customWidth="1"/>
+    <col min="2295" max="2295" width="10.83203125" style="3" customWidth="1"/>
+    <col min="2296" max="2296" width="12.33203125" style="3" customWidth="1"/>
     <col min="2297" max="2297" width="11" style="3" customWidth="1"/>
-    <col min="2298" max="2298" width="6.725" style="3" customWidth="1"/>
-    <col min="2299" max="2299" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="2300" max="2300" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="2301" max="2301" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="2302" max="2302" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="2303" max="2303" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="2304" max="2304" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="2305" max="2305" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="2306" max="2306" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="2307" max="2307" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="2308" max="2308" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="2309" max="2309" width="8.45" style="3" customWidth="1"/>
-    <col min="2310" max="2310" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="2311" max="2311" width="7.725" style="3" customWidth="1"/>
-    <col min="2312" max="2312" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="2298" max="2298" width="6.6640625" style="3" customWidth="1"/>
+    <col min="2299" max="2299" width="7.83203125" style="3" customWidth="1"/>
+    <col min="2300" max="2300" width="7.1640625" style="3" customWidth="1"/>
+    <col min="2301" max="2301" width="7.6640625" style="3" customWidth="1"/>
+    <col min="2302" max="2303" width="5.33203125" style="3" customWidth="1"/>
+    <col min="2304" max="2304" width="5.1640625" style="3" customWidth="1"/>
+    <col min="2305" max="2305" width="7.33203125" style="3" customWidth="1"/>
+    <col min="2306" max="2306" width="4.1640625" style="3" customWidth="1"/>
+    <col min="2307" max="2307" width="6.33203125" style="3" customWidth="1"/>
+    <col min="2308" max="2308" width="7.6640625" style="3" customWidth="1"/>
+    <col min="2309" max="2309" width="8.5" style="3" customWidth="1"/>
+    <col min="2310" max="2310" width="8.33203125" style="3" customWidth="1"/>
+    <col min="2311" max="2311" width="7.6640625" style="3" customWidth="1"/>
+    <col min="2312" max="2312" width="6.83203125" style="3" customWidth="1"/>
     <col min="2313" max="2546" width="9" style="3"/>
-    <col min="2547" max="2547" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="2548" max="2548" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="2547" max="2547" width="6.33203125" style="3" customWidth="1"/>
+    <col min="2548" max="2548" width="7.33203125" style="3" customWidth="1"/>
     <col min="2549" max="2549" width="6" style="3" customWidth="1"/>
-    <col min="2550" max="2550" width="25.45" style="3" customWidth="1"/>
-    <col min="2551" max="2551" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="2552" max="2552" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="2550" max="2550" width="25.5" style="3" customWidth="1"/>
+    <col min="2551" max="2551" width="10.83203125" style="3" customWidth="1"/>
+    <col min="2552" max="2552" width="12.33203125" style="3" customWidth="1"/>
     <col min="2553" max="2553" width="11" style="3" customWidth="1"/>
-    <col min="2554" max="2554" width="6.725" style="3" customWidth="1"/>
-    <col min="2555" max="2555" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="2556" max="2556" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="2557" max="2557" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="2558" max="2558" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="2559" max="2559" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="2560" max="2560" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="2561" max="2561" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="2562" max="2562" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="2563" max="2563" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="2564" max="2564" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="2565" max="2565" width="8.45" style="3" customWidth="1"/>
-    <col min="2566" max="2566" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="2567" max="2567" width="7.725" style="3" customWidth="1"/>
-    <col min="2568" max="2568" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="2554" max="2554" width="6.6640625" style="3" customWidth="1"/>
+    <col min="2555" max="2555" width="7.83203125" style="3" customWidth="1"/>
+    <col min="2556" max="2556" width="7.1640625" style="3" customWidth="1"/>
+    <col min="2557" max="2557" width="7.6640625" style="3" customWidth="1"/>
+    <col min="2558" max="2559" width="5.33203125" style="3" customWidth="1"/>
+    <col min="2560" max="2560" width="5.1640625" style="3" customWidth="1"/>
+    <col min="2561" max="2561" width="7.33203125" style="3" customWidth="1"/>
+    <col min="2562" max="2562" width="4.1640625" style="3" customWidth="1"/>
+    <col min="2563" max="2563" width="6.33203125" style="3" customWidth="1"/>
+    <col min="2564" max="2564" width="7.6640625" style="3" customWidth="1"/>
+    <col min="2565" max="2565" width="8.5" style="3" customWidth="1"/>
+    <col min="2566" max="2566" width="8.33203125" style="3" customWidth="1"/>
+    <col min="2567" max="2567" width="7.6640625" style="3" customWidth="1"/>
+    <col min="2568" max="2568" width="6.83203125" style="3" customWidth="1"/>
     <col min="2569" max="2802" width="9" style="3"/>
-    <col min="2803" max="2803" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="2804" max="2804" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="2803" max="2803" width="6.33203125" style="3" customWidth="1"/>
+    <col min="2804" max="2804" width="7.33203125" style="3" customWidth="1"/>
     <col min="2805" max="2805" width="6" style="3" customWidth="1"/>
-    <col min="2806" max="2806" width="25.45" style="3" customWidth="1"/>
-    <col min="2807" max="2807" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="2808" max="2808" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="2806" max="2806" width="25.5" style="3" customWidth="1"/>
+    <col min="2807" max="2807" width="10.83203125" style="3" customWidth="1"/>
+    <col min="2808" max="2808" width="12.33203125" style="3" customWidth="1"/>
     <col min="2809" max="2809" width="11" style="3" customWidth="1"/>
-    <col min="2810" max="2810" width="6.725" style="3" customWidth="1"/>
-    <col min="2811" max="2811" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="2812" max="2812" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="2813" max="2813" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="2814" max="2814" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="2815" max="2815" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="2816" max="2816" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="2817" max="2817" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="2818" max="2818" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="2819" max="2819" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="2820" max="2820" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="2821" max="2821" width="8.45" style="3" customWidth="1"/>
-    <col min="2822" max="2822" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="2823" max="2823" width="7.725" style="3" customWidth="1"/>
-    <col min="2824" max="2824" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="2810" max="2810" width="6.6640625" style="3" customWidth="1"/>
+    <col min="2811" max="2811" width="7.83203125" style="3" customWidth="1"/>
+    <col min="2812" max="2812" width="7.1640625" style="3" customWidth="1"/>
+    <col min="2813" max="2813" width="7.6640625" style="3" customWidth="1"/>
+    <col min="2814" max="2815" width="5.33203125" style="3" customWidth="1"/>
+    <col min="2816" max="2816" width="5.1640625" style="3" customWidth="1"/>
+    <col min="2817" max="2817" width="7.33203125" style="3" customWidth="1"/>
+    <col min="2818" max="2818" width="4.1640625" style="3" customWidth="1"/>
+    <col min="2819" max="2819" width="6.33203125" style="3" customWidth="1"/>
+    <col min="2820" max="2820" width="7.6640625" style="3" customWidth="1"/>
+    <col min="2821" max="2821" width="8.5" style="3" customWidth="1"/>
+    <col min="2822" max="2822" width="8.33203125" style="3" customWidth="1"/>
+    <col min="2823" max="2823" width="7.6640625" style="3" customWidth="1"/>
+    <col min="2824" max="2824" width="6.83203125" style="3" customWidth="1"/>
     <col min="2825" max="3058" width="9" style="3"/>
-    <col min="3059" max="3059" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="3060" max="3060" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="3059" max="3059" width="6.33203125" style="3" customWidth="1"/>
+    <col min="3060" max="3060" width="7.33203125" style="3" customWidth="1"/>
     <col min="3061" max="3061" width="6" style="3" customWidth="1"/>
-    <col min="3062" max="3062" width="25.45" style="3" customWidth="1"/>
-    <col min="3063" max="3063" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="3064" max="3064" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="3062" max="3062" width="25.5" style="3" customWidth="1"/>
+    <col min="3063" max="3063" width="10.83203125" style="3" customWidth="1"/>
+    <col min="3064" max="3064" width="12.33203125" style="3" customWidth="1"/>
     <col min="3065" max="3065" width="11" style="3" customWidth="1"/>
-    <col min="3066" max="3066" width="6.725" style="3" customWidth="1"/>
-    <col min="3067" max="3067" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="3068" max="3068" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="3069" max="3069" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="3070" max="3070" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="3071" max="3071" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="3072" max="3072" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="3073" max="3073" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="3074" max="3074" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="3075" max="3075" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="3076" max="3076" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="3077" max="3077" width="8.45" style="3" customWidth="1"/>
-    <col min="3078" max="3078" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="3079" max="3079" width="7.725" style="3" customWidth="1"/>
-    <col min="3080" max="3080" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="3066" max="3066" width="6.6640625" style="3" customWidth="1"/>
+    <col min="3067" max="3067" width="7.83203125" style="3" customWidth="1"/>
+    <col min="3068" max="3068" width="7.1640625" style="3" customWidth="1"/>
+    <col min="3069" max="3069" width="7.6640625" style="3" customWidth="1"/>
+    <col min="3070" max="3071" width="5.33203125" style="3" customWidth="1"/>
+    <col min="3072" max="3072" width="5.1640625" style="3" customWidth="1"/>
+    <col min="3073" max="3073" width="7.33203125" style="3" customWidth="1"/>
+    <col min="3074" max="3074" width="4.1640625" style="3" customWidth="1"/>
+    <col min="3075" max="3075" width="6.33203125" style="3" customWidth="1"/>
+    <col min="3076" max="3076" width="7.6640625" style="3" customWidth="1"/>
+    <col min="3077" max="3077" width="8.5" style="3" customWidth="1"/>
+    <col min="3078" max="3078" width="8.33203125" style="3" customWidth="1"/>
+    <col min="3079" max="3079" width="7.6640625" style="3" customWidth="1"/>
+    <col min="3080" max="3080" width="6.83203125" style="3" customWidth="1"/>
     <col min="3081" max="3314" width="9" style="3"/>
-    <col min="3315" max="3315" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="3316" max="3316" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="3315" max="3315" width="6.33203125" style="3" customWidth="1"/>
+    <col min="3316" max="3316" width="7.33203125" style="3" customWidth="1"/>
     <col min="3317" max="3317" width="6" style="3" customWidth="1"/>
-    <col min="3318" max="3318" width="25.45" style="3" customWidth="1"/>
-    <col min="3319" max="3319" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="3320" max="3320" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="3318" max="3318" width="25.5" style="3" customWidth="1"/>
+    <col min="3319" max="3319" width="10.83203125" style="3" customWidth="1"/>
+    <col min="3320" max="3320" width="12.33203125" style="3" customWidth="1"/>
     <col min="3321" max="3321" width="11" style="3" customWidth="1"/>
-    <col min="3322" max="3322" width="6.725" style="3" customWidth="1"/>
-    <col min="3323" max="3323" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="3324" max="3324" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="3325" max="3325" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="3326" max="3326" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="3327" max="3327" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="3328" max="3328" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="3329" max="3329" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="3330" max="3330" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="3331" max="3331" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="3332" max="3332" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="3333" max="3333" width="8.45" style="3" customWidth="1"/>
-    <col min="3334" max="3334" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="3335" max="3335" width="7.725" style="3" customWidth="1"/>
-    <col min="3336" max="3336" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="3322" max="3322" width="6.6640625" style="3" customWidth="1"/>
+    <col min="3323" max="3323" width="7.83203125" style="3" customWidth="1"/>
+    <col min="3324" max="3324" width="7.1640625" style="3" customWidth="1"/>
+    <col min="3325" max="3325" width="7.6640625" style="3" customWidth="1"/>
+    <col min="3326" max="3327" width="5.33203125" style="3" customWidth="1"/>
+    <col min="3328" max="3328" width="5.1640625" style="3" customWidth="1"/>
+    <col min="3329" max="3329" width="7.33203125" style="3" customWidth="1"/>
+    <col min="3330" max="3330" width="4.1640625" style="3" customWidth="1"/>
+    <col min="3331" max="3331" width="6.33203125" style="3" customWidth="1"/>
+    <col min="3332" max="3332" width="7.6640625" style="3" customWidth="1"/>
+    <col min="3333" max="3333" width="8.5" style="3" customWidth="1"/>
+    <col min="3334" max="3334" width="8.33203125" style="3" customWidth="1"/>
+    <col min="3335" max="3335" width="7.6640625" style="3" customWidth="1"/>
+    <col min="3336" max="3336" width="6.83203125" style="3" customWidth="1"/>
     <col min="3337" max="3570" width="9" style="3"/>
-    <col min="3571" max="3571" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="3572" max="3572" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="3571" max="3571" width="6.33203125" style="3" customWidth="1"/>
+    <col min="3572" max="3572" width="7.33203125" style="3" customWidth="1"/>
     <col min="3573" max="3573" width="6" style="3" customWidth="1"/>
-    <col min="3574" max="3574" width="25.45" style="3" customWidth="1"/>
-    <col min="3575" max="3575" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="3576" max="3576" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="3574" max="3574" width="25.5" style="3" customWidth="1"/>
+    <col min="3575" max="3575" width="10.83203125" style="3" customWidth="1"/>
+    <col min="3576" max="3576" width="12.33203125" style="3" customWidth="1"/>
     <col min="3577" max="3577" width="11" style="3" customWidth="1"/>
-    <col min="3578" max="3578" width="6.725" style="3" customWidth="1"/>
-    <col min="3579" max="3579" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="3580" max="3580" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="3581" max="3581" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="3582" max="3582" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="3583" max="3583" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="3584" max="3584" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="3585" max="3585" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="3586" max="3586" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="3587" max="3587" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="3588" max="3588" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="3589" max="3589" width="8.45" style="3" customWidth="1"/>
-    <col min="3590" max="3590" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="3591" max="3591" width="7.725" style="3" customWidth="1"/>
-    <col min="3592" max="3592" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="3578" max="3578" width="6.6640625" style="3" customWidth="1"/>
+    <col min="3579" max="3579" width="7.83203125" style="3" customWidth="1"/>
+    <col min="3580" max="3580" width="7.1640625" style="3" customWidth="1"/>
+    <col min="3581" max="3581" width="7.6640625" style="3" customWidth="1"/>
+    <col min="3582" max="3583" width="5.33203125" style="3" customWidth="1"/>
+    <col min="3584" max="3584" width="5.1640625" style="3" customWidth="1"/>
+    <col min="3585" max="3585" width="7.33203125" style="3" customWidth="1"/>
+    <col min="3586" max="3586" width="4.1640625" style="3" customWidth="1"/>
+    <col min="3587" max="3587" width="6.33203125" style="3" customWidth="1"/>
+    <col min="3588" max="3588" width="7.6640625" style="3" customWidth="1"/>
+    <col min="3589" max="3589" width="8.5" style="3" customWidth="1"/>
+    <col min="3590" max="3590" width="8.33203125" style="3" customWidth="1"/>
+    <col min="3591" max="3591" width="7.6640625" style="3" customWidth="1"/>
+    <col min="3592" max="3592" width="6.83203125" style="3" customWidth="1"/>
     <col min="3593" max="3826" width="9" style="3"/>
-    <col min="3827" max="3827" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="3828" max="3828" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="3827" max="3827" width="6.33203125" style="3" customWidth="1"/>
+    <col min="3828" max="3828" width="7.33203125" style="3" customWidth="1"/>
     <col min="3829" max="3829" width="6" style="3" customWidth="1"/>
-    <col min="3830" max="3830" width="25.45" style="3" customWidth="1"/>
-    <col min="3831" max="3831" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="3832" max="3832" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="3830" max="3830" width="25.5" style="3" customWidth="1"/>
+    <col min="3831" max="3831" width="10.83203125" style="3" customWidth="1"/>
+    <col min="3832" max="3832" width="12.33203125" style="3" customWidth="1"/>
     <col min="3833" max="3833" width="11" style="3" customWidth="1"/>
-    <col min="3834" max="3834" width="6.725" style="3" customWidth="1"/>
-    <col min="3835" max="3835" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="3836" max="3836" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="3837" max="3837" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="3838" max="3838" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="3839" max="3839" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="3840" max="3840" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="3841" max="3841" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="3842" max="3842" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="3843" max="3843" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="3844" max="3844" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="3845" max="3845" width="8.45" style="3" customWidth="1"/>
-    <col min="3846" max="3846" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="3847" max="3847" width="7.725" style="3" customWidth="1"/>
-    <col min="3848" max="3848" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="3834" max="3834" width="6.6640625" style="3" customWidth="1"/>
+    <col min="3835" max="3835" width="7.83203125" style="3" customWidth="1"/>
+    <col min="3836" max="3836" width="7.1640625" style="3" customWidth="1"/>
+    <col min="3837" max="3837" width="7.6640625" style="3" customWidth="1"/>
+    <col min="3838" max="3839" width="5.33203125" style="3" customWidth="1"/>
+    <col min="3840" max="3840" width="5.1640625" style="3" customWidth="1"/>
+    <col min="3841" max="3841" width="7.33203125" style="3" customWidth="1"/>
+    <col min="3842" max="3842" width="4.1640625" style="3" customWidth="1"/>
+    <col min="3843" max="3843" width="6.33203125" style="3" customWidth="1"/>
+    <col min="3844" max="3844" width="7.6640625" style="3" customWidth="1"/>
+    <col min="3845" max="3845" width="8.5" style="3" customWidth="1"/>
+    <col min="3846" max="3846" width="8.33203125" style="3" customWidth="1"/>
+    <col min="3847" max="3847" width="7.6640625" style="3" customWidth="1"/>
+    <col min="3848" max="3848" width="6.83203125" style="3" customWidth="1"/>
     <col min="3849" max="4082" width="9" style="3"/>
-    <col min="4083" max="4083" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="4084" max="4084" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="4083" max="4083" width="6.33203125" style="3" customWidth="1"/>
+    <col min="4084" max="4084" width="7.33203125" style="3" customWidth="1"/>
     <col min="4085" max="4085" width="6" style="3" customWidth="1"/>
-    <col min="4086" max="4086" width="25.45" style="3" customWidth="1"/>
-    <col min="4087" max="4087" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="4088" max="4088" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="4086" max="4086" width="25.5" style="3" customWidth="1"/>
+    <col min="4087" max="4087" width="10.83203125" style="3" customWidth="1"/>
+    <col min="4088" max="4088" width="12.33203125" style="3" customWidth="1"/>
     <col min="4089" max="4089" width="11" style="3" customWidth="1"/>
-    <col min="4090" max="4090" width="6.725" style="3" customWidth="1"/>
-    <col min="4091" max="4091" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="4092" max="4092" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="4093" max="4093" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="4094" max="4094" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="4095" max="4095" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="4096" max="4096" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="4097" max="4097" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="4098" max="4098" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="4099" max="4099" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="4100" max="4100" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="4101" max="4101" width="8.45" style="3" customWidth="1"/>
-    <col min="4102" max="4102" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="4103" max="4103" width="7.725" style="3" customWidth="1"/>
-    <col min="4104" max="4104" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="4090" max="4090" width="6.6640625" style="3" customWidth="1"/>
+    <col min="4091" max="4091" width="7.83203125" style="3" customWidth="1"/>
+    <col min="4092" max="4092" width="7.1640625" style="3" customWidth="1"/>
+    <col min="4093" max="4093" width="7.6640625" style="3" customWidth="1"/>
+    <col min="4094" max="4095" width="5.33203125" style="3" customWidth="1"/>
+    <col min="4096" max="4096" width="5.1640625" style="3" customWidth="1"/>
+    <col min="4097" max="4097" width="7.33203125" style="3" customWidth="1"/>
+    <col min="4098" max="4098" width="4.1640625" style="3" customWidth="1"/>
+    <col min="4099" max="4099" width="6.33203125" style="3" customWidth="1"/>
+    <col min="4100" max="4100" width="7.6640625" style="3" customWidth="1"/>
+    <col min="4101" max="4101" width="8.5" style="3" customWidth="1"/>
+    <col min="4102" max="4102" width="8.33203125" style="3" customWidth="1"/>
+    <col min="4103" max="4103" width="7.6640625" style="3" customWidth="1"/>
+    <col min="4104" max="4104" width="6.83203125" style="3" customWidth="1"/>
     <col min="4105" max="4338" width="9" style="3"/>
-    <col min="4339" max="4339" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="4340" max="4340" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="4339" max="4339" width="6.33203125" style="3" customWidth="1"/>
+    <col min="4340" max="4340" width="7.33203125" style="3" customWidth="1"/>
     <col min="4341" max="4341" width="6" style="3" customWidth="1"/>
-    <col min="4342" max="4342" width="25.45" style="3" customWidth="1"/>
-    <col min="4343" max="4343" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="4344" max="4344" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="4342" max="4342" width="25.5" style="3" customWidth="1"/>
+    <col min="4343" max="4343" width="10.83203125" style="3" customWidth="1"/>
+    <col min="4344" max="4344" width="12.33203125" style="3" customWidth="1"/>
     <col min="4345" max="4345" width="11" style="3" customWidth="1"/>
-    <col min="4346" max="4346" width="6.725" style="3" customWidth="1"/>
-    <col min="4347" max="4347" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="4348" max="4348" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="4349" max="4349" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="4350" max="4350" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="4351" max="4351" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="4352" max="4352" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="4353" max="4353" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="4354" max="4354" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="4355" max="4355" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="4356" max="4356" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="4357" max="4357" width="8.45" style="3" customWidth="1"/>
-    <col min="4358" max="4358" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="4359" max="4359" width="7.725" style="3" customWidth="1"/>
-    <col min="4360" max="4360" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="4346" max="4346" width="6.6640625" style="3" customWidth="1"/>
+    <col min="4347" max="4347" width="7.83203125" style="3" customWidth="1"/>
+    <col min="4348" max="4348" width="7.1640625" style="3" customWidth="1"/>
+    <col min="4349" max="4349" width="7.6640625" style="3" customWidth="1"/>
+    <col min="4350" max="4351" width="5.33203125" style="3" customWidth="1"/>
+    <col min="4352" max="4352" width="5.1640625" style="3" customWidth="1"/>
+    <col min="4353" max="4353" width="7.33203125" style="3" customWidth="1"/>
+    <col min="4354" max="4354" width="4.1640625" style="3" customWidth="1"/>
+    <col min="4355" max="4355" width="6.33203125" style="3" customWidth="1"/>
+    <col min="4356" max="4356" width="7.6640625" style="3" customWidth="1"/>
+    <col min="4357" max="4357" width="8.5" style="3" customWidth="1"/>
+    <col min="4358" max="4358" width="8.33203125" style="3" customWidth="1"/>
+    <col min="4359" max="4359" width="7.6640625" style="3" customWidth="1"/>
+    <col min="4360" max="4360" width="6.83203125" style="3" customWidth="1"/>
     <col min="4361" max="4594" width="9" style="3"/>
-    <col min="4595" max="4595" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="4596" max="4596" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="4595" max="4595" width="6.33203125" style="3" customWidth="1"/>
+    <col min="4596" max="4596" width="7.33203125" style="3" customWidth="1"/>
     <col min="4597" max="4597" width="6" style="3" customWidth="1"/>
-    <col min="4598" max="4598" width="25.45" style="3" customWidth="1"/>
-    <col min="4599" max="4599" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="4600" max="4600" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="4598" max="4598" width="25.5" style="3" customWidth="1"/>
+    <col min="4599" max="4599" width="10.83203125" style="3" customWidth="1"/>
+    <col min="4600" max="4600" width="12.33203125" style="3" customWidth="1"/>
     <col min="4601" max="4601" width="11" style="3" customWidth="1"/>
-    <col min="4602" max="4602" width="6.725" style="3" customWidth="1"/>
-    <col min="4603" max="4603" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="4604" max="4604" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="4605" max="4605" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="4606" max="4606" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="4607" max="4607" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="4608" max="4608" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="4609" max="4609" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="4610" max="4610" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="4611" max="4611" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="4612" max="4612" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="4613" max="4613" width="8.45" style="3" customWidth="1"/>
-    <col min="4614" max="4614" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="4615" max="4615" width="7.725" style="3" customWidth="1"/>
-    <col min="4616" max="4616" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="4602" max="4602" width="6.6640625" style="3" customWidth="1"/>
+    <col min="4603" max="4603" width="7.83203125" style="3" customWidth="1"/>
+    <col min="4604" max="4604" width="7.1640625" style="3" customWidth="1"/>
+    <col min="4605" max="4605" width="7.6640625" style="3" customWidth="1"/>
+    <col min="4606" max="4607" width="5.33203125" style="3" customWidth="1"/>
+    <col min="4608" max="4608" width="5.1640625" style="3" customWidth="1"/>
+    <col min="4609" max="4609" width="7.33203125" style="3" customWidth="1"/>
+    <col min="4610" max="4610" width="4.1640625" style="3" customWidth="1"/>
+    <col min="4611" max="4611" width="6.33203125" style="3" customWidth="1"/>
+    <col min="4612" max="4612" width="7.6640625" style="3" customWidth="1"/>
+    <col min="4613" max="4613" width="8.5" style="3" customWidth="1"/>
+    <col min="4614" max="4614" width="8.33203125" style="3" customWidth="1"/>
+    <col min="4615" max="4615" width="7.6640625" style="3" customWidth="1"/>
+    <col min="4616" max="4616" width="6.83203125" style="3" customWidth="1"/>
     <col min="4617" max="4850" width="9" style="3"/>
-    <col min="4851" max="4851" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="4852" max="4852" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="4851" max="4851" width="6.33203125" style="3" customWidth="1"/>
+    <col min="4852" max="4852" width="7.33203125" style="3" customWidth="1"/>
     <col min="4853" max="4853" width="6" style="3" customWidth="1"/>
-    <col min="4854" max="4854" width="25.45" style="3" customWidth="1"/>
-    <col min="4855" max="4855" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="4856" max="4856" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="4854" max="4854" width="25.5" style="3" customWidth="1"/>
+    <col min="4855" max="4855" width="10.83203125" style="3" customWidth="1"/>
+    <col min="4856" max="4856" width="12.33203125" style="3" customWidth="1"/>
     <col min="4857" max="4857" width="11" style="3" customWidth="1"/>
-    <col min="4858" max="4858" width="6.725" style="3" customWidth="1"/>
-    <col min="4859" max="4859" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="4860" max="4860" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="4861" max="4861" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="4862" max="4862" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="4863" max="4863" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="4864" max="4864" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="4865" max="4865" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="4866" max="4866" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="4867" max="4867" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="4868" max="4868" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="4869" max="4869" width="8.45" style="3" customWidth="1"/>
-    <col min="4870" max="4870" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="4871" max="4871" width="7.725" style="3" customWidth="1"/>
-    <col min="4872" max="4872" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="4858" max="4858" width="6.6640625" style="3" customWidth="1"/>
+    <col min="4859" max="4859" width="7.83203125" style="3" customWidth="1"/>
+    <col min="4860" max="4860" width="7.1640625" style="3" customWidth="1"/>
+    <col min="4861" max="4861" width="7.6640625" style="3" customWidth="1"/>
+    <col min="4862" max="4863" width="5.33203125" style="3" customWidth="1"/>
+    <col min="4864" max="4864" width="5.1640625" style="3" customWidth="1"/>
+    <col min="4865" max="4865" width="7.33203125" style="3" customWidth="1"/>
+    <col min="4866" max="4866" width="4.1640625" style="3" customWidth="1"/>
+    <col min="4867" max="4867" width="6.33203125" style="3" customWidth="1"/>
+    <col min="4868" max="4868" width="7.6640625" style="3" customWidth="1"/>
+    <col min="4869" max="4869" width="8.5" style="3" customWidth="1"/>
+    <col min="4870" max="4870" width="8.33203125" style="3" customWidth="1"/>
+    <col min="4871" max="4871" width="7.6640625" style="3" customWidth="1"/>
+    <col min="4872" max="4872" width="6.83203125" style="3" customWidth="1"/>
     <col min="4873" max="5106" width="9" style="3"/>
-    <col min="5107" max="5107" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="5108" max="5108" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="5107" max="5107" width="6.33203125" style="3" customWidth="1"/>
+    <col min="5108" max="5108" width="7.33203125" style="3" customWidth="1"/>
     <col min="5109" max="5109" width="6" style="3" customWidth="1"/>
-    <col min="5110" max="5110" width="25.45" style="3" customWidth="1"/>
-    <col min="5111" max="5111" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="5112" max="5112" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="5110" max="5110" width="25.5" style="3" customWidth="1"/>
+    <col min="5111" max="5111" width="10.83203125" style="3" customWidth="1"/>
+    <col min="5112" max="5112" width="12.33203125" style="3" customWidth="1"/>
     <col min="5113" max="5113" width="11" style="3" customWidth="1"/>
-    <col min="5114" max="5114" width="6.725" style="3" customWidth="1"/>
-    <col min="5115" max="5115" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="5116" max="5116" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="5117" max="5117" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="5118" max="5118" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="5119" max="5119" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="5120" max="5120" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="5121" max="5121" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="5122" max="5122" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="5123" max="5123" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="5124" max="5124" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="5125" max="5125" width="8.45" style="3" customWidth="1"/>
-    <col min="5126" max="5126" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="5127" max="5127" width="7.725" style="3" customWidth="1"/>
-    <col min="5128" max="5128" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="5114" max="5114" width="6.6640625" style="3" customWidth="1"/>
+    <col min="5115" max="5115" width="7.83203125" style="3" customWidth="1"/>
+    <col min="5116" max="5116" width="7.1640625" style="3" customWidth="1"/>
+    <col min="5117" max="5117" width="7.6640625" style="3" customWidth="1"/>
+    <col min="5118" max="5119" width="5.33203125" style="3" customWidth="1"/>
+    <col min="5120" max="5120" width="5.1640625" style="3" customWidth="1"/>
+    <col min="5121" max="5121" width="7.33203125" style="3" customWidth="1"/>
+    <col min="5122" max="5122" width="4.1640625" style="3" customWidth="1"/>
+    <col min="5123" max="5123" width="6.33203125" style="3" customWidth="1"/>
+    <col min="5124" max="5124" width="7.6640625" style="3" customWidth="1"/>
+    <col min="5125" max="5125" width="8.5" style="3" customWidth="1"/>
+    <col min="5126" max="5126" width="8.33203125" style="3" customWidth="1"/>
+    <col min="5127" max="5127" width="7.6640625" style="3" customWidth="1"/>
+    <col min="5128" max="5128" width="6.83203125" style="3" customWidth="1"/>
     <col min="5129" max="5362" width="9" style="3"/>
-    <col min="5363" max="5363" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="5364" max="5364" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="5363" max="5363" width="6.33203125" style="3" customWidth="1"/>
+    <col min="5364" max="5364" width="7.33203125" style="3" customWidth="1"/>
     <col min="5365" max="5365" width="6" style="3" customWidth="1"/>
-    <col min="5366" max="5366" width="25.45" style="3" customWidth="1"/>
-    <col min="5367" max="5367" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="5368" max="5368" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="5366" max="5366" width="25.5" style="3" customWidth="1"/>
+    <col min="5367" max="5367" width="10.83203125" style="3" customWidth="1"/>
+    <col min="5368" max="5368" width="12.33203125" style="3" customWidth="1"/>
     <col min="5369" max="5369" width="11" style="3" customWidth="1"/>
-    <col min="5370" max="5370" width="6.725" style="3" customWidth="1"/>
-    <col min="5371" max="5371" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="5372" max="5372" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="5373" max="5373" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="5374" max="5374" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="5375" max="5375" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="5376" max="5376" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="5377" max="5377" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="5378" max="5378" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="5379" max="5379" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="5380" max="5380" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="5381" max="5381" width="8.45" style="3" customWidth="1"/>
-    <col min="5382" max="5382" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="5383" max="5383" width="7.725" style="3" customWidth="1"/>
-    <col min="5384" max="5384" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="5370" max="5370" width="6.6640625" style="3" customWidth="1"/>
+    <col min="5371" max="5371" width="7.83203125" style="3" customWidth="1"/>
+    <col min="5372" max="5372" width="7.1640625" style="3" customWidth="1"/>
+    <col min="5373" max="5373" width="7.6640625" style="3" customWidth="1"/>
+    <col min="5374" max="5375" width="5.33203125" style="3" customWidth="1"/>
+    <col min="5376" max="5376" width="5.1640625" style="3" customWidth="1"/>
+    <col min="5377" max="5377" width="7.33203125" style="3" customWidth="1"/>
+    <col min="5378" max="5378" width="4.1640625" style="3" customWidth="1"/>
+    <col min="5379" max="5379" width="6.33203125" style="3" customWidth="1"/>
+    <col min="5380" max="5380" width="7.6640625" style="3" customWidth="1"/>
+    <col min="5381" max="5381" width="8.5" style="3" customWidth="1"/>
+    <col min="5382" max="5382" width="8.33203125" style="3" customWidth="1"/>
+    <col min="5383" max="5383" width="7.6640625" style="3" customWidth="1"/>
+    <col min="5384" max="5384" width="6.83203125" style="3" customWidth="1"/>
     <col min="5385" max="5618" width="9" style="3"/>
-    <col min="5619" max="5619" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="5620" max="5620" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="5619" max="5619" width="6.33203125" style="3" customWidth="1"/>
+    <col min="5620" max="5620" width="7.33203125" style="3" customWidth="1"/>
     <col min="5621" max="5621" width="6" style="3" customWidth="1"/>
-    <col min="5622" max="5622" width="25.45" style="3" customWidth="1"/>
-    <col min="5623" max="5623" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="5624" max="5624" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="5622" max="5622" width="25.5" style="3" customWidth="1"/>
+    <col min="5623" max="5623" width="10.83203125" style="3" customWidth="1"/>
+    <col min="5624" max="5624" width="12.33203125" style="3" customWidth="1"/>
     <col min="5625" max="5625" width="11" style="3" customWidth="1"/>
-    <col min="5626" max="5626" width="6.725" style="3" customWidth="1"/>
-    <col min="5627" max="5627" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="5628" max="5628" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="5629" max="5629" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="5630" max="5630" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="5631" max="5631" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="5632" max="5632" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="5633" max="5633" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="5634" max="5634" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="5635" max="5635" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="5636" max="5636" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="5637" max="5637" width="8.45" style="3" customWidth="1"/>
-    <col min="5638" max="5638" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="5639" max="5639" width="7.725" style="3" customWidth="1"/>
-    <col min="5640" max="5640" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="5626" max="5626" width="6.6640625" style="3" customWidth="1"/>
+    <col min="5627" max="5627" width="7.83203125" style="3" customWidth="1"/>
+    <col min="5628" max="5628" width="7.1640625" style="3" customWidth="1"/>
+    <col min="5629" max="5629" width="7.6640625" style="3" customWidth="1"/>
+    <col min="5630" max="5631" width="5.33203125" style="3" customWidth="1"/>
+    <col min="5632" max="5632" width="5.1640625" style="3" customWidth="1"/>
+    <col min="5633" max="5633" width="7.33203125" style="3" customWidth="1"/>
+    <col min="5634" max="5634" width="4.1640625" style="3" customWidth="1"/>
+    <col min="5635" max="5635" width="6.33203125" style="3" customWidth="1"/>
+    <col min="5636" max="5636" width="7.6640625" style="3" customWidth="1"/>
+    <col min="5637" max="5637" width="8.5" style="3" customWidth="1"/>
+    <col min="5638" max="5638" width="8.33203125" style="3" customWidth="1"/>
+    <col min="5639" max="5639" width="7.6640625" style="3" customWidth="1"/>
+    <col min="5640" max="5640" width="6.83203125" style="3" customWidth="1"/>
     <col min="5641" max="5874" width="9" style="3"/>
-    <col min="5875" max="5875" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="5876" max="5876" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="5875" max="5875" width="6.33203125" style="3" customWidth="1"/>
+    <col min="5876" max="5876" width="7.33203125" style="3" customWidth="1"/>
     <col min="5877" max="5877" width="6" style="3" customWidth="1"/>
-    <col min="5878" max="5878" width="25.45" style="3" customWidth="1"/>
-    <col min="5879" max="5879" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="5880" max="5880" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="5878" max="5878" width="25.5" style="3" customWidth="1"/>
+    <col min="5879" max="5879" width="10.83203125" style="3" customWidth="1"/>
+    <col min="5880" max="5880" width="12.33203125" style="3" customWidth="1"/>
     <col min="5881" max="5881" width="11" style="3" customWidth="1"/>
-    <col min="5882" max="5882" width="6.725" style="3" customWidth="1"/>
-    <col min="5883" max="5883" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="5884" max="5884" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="5885" max="5885" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="5886" max="5886" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="5887" max="5887" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="5888" max="5888" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="5889" max="5889" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="5890" max="5890" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="5891" max="5891" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="5892" max="5892" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="5893" max="5893" width="8.45" style="3" customWidth="1"/>
-    <col min="5894" max="5894" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="5895" max="5895" width="7.725" style="3" customWidth="1"/>
-    <col min="5896" max="5896" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="5882" max="5882" width="6.6640625" style="3" customWidth="1"/>
+    <col min="5883" max="5883" width="7.83203125" style="3" customWidth="1"/>
+    <col min="5884" max="5884" width="7.1640625" style="3" customWidth="1"/>
+    <col min="5885" max="5885" width="7.6640625" style="3" customWidth="1"/>
+    <col min="5886" max="5887" width="5.33203125" style="3" customWidth="1"/>
+    <col min="5888" max="5888" width="5.1640625" style="3" customWidth="1"/>
+    <col min="5889" max="5889" width="7.33203125" style="3" customWidth="1"/>
+    <col min="5890" max="5890" width="4.1640625" style="3" customWidth="1"/>
+    <col min="5891" max="5891" width="6.33203125" style="3" customWidth="1"/>
+    <col min="5892" max="5892" width="7.6640625" style="3" customWidth="1"/>
+    <col min="5893" max="5893" width="8.5" style="3" customWidth="1"/>
+    <col min="5894" max="5894" width="8.33203125" style="3" customWidth="1"/>
+    <col min="5895" max="5895" width="7.6640625" style="3" customWidth="1"/>
+    <col min="5896" max="5896" width="6.83203125" style="3" customWidth="1"/>
     <col min="5897" max="6130" width="9" style="3"/>
-    <col min="6131" max="6131" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="6132" max="6132" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="6131" max="6131" width="6.33203125" style="3" customWidth="1"/>
+    <col min="6132" max="6132" width="7.33203125" style="3" customWidth="1"/>
     <col min="6133" max="6133" width="6" style="3" customWidth="1"/>
-    <col min="6134" max="6134" width="25.45" style="3" customWidth="1"/>
-    <col min="6135" max="6135" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="6136" max="6136" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="6134" max="6134" width="25.5" style="3" customWidth="1"/>
+    <col min="6135" max="6135" width="10.83203125" style="3" customWidth="1"/>
+    <col min="6136" max="6136" width="12.33203125" style="3" customWidth="1"/>
     <col min="6137" max="6137" width="11" style="3" customWidth="1"/>
-    <col min="6138" max="6138" width="6.725" style="3" customWidth="1"/>
-    <col min="6139" max="6139" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="6140" max="6140" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="6141" max="6141" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="6142" max="6142" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="6143" max="6143" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="6144" max="6144" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="6145" max="6145" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="6146" max="6146" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="6147" max="6147" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="6148" max="6148" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="6149" max="6149" width="8.45" style="3" customWidth="1"/>
-    <col min="6150" max="6150" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="6151" max="6151" width="7.725" style="3" customWidth="1"/>
-    <col min="6152" max="6152" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="6138" max="6138" width="6.6640625" style="3" customWidth="1"/>
+    <col min="6139" max="6139" width="7.83203125" style="3" customWidth="1"/>
+    <col min="6140" max="6140" width="7.1640625" style="3" customWidth="1"/>
+    <col min="6141" max="6141" width="7.6640625" style="3" customWidth="1"/>
+    <col min="6142" max="6143" width="5.33203125" style="3" customWidth="1"/>
+    <col min="6144" max="6144" width="5.1640625" style="3" customWidth="1"/>
+    <col min="6145" max="6145" width="7.33203125" style="3" customWidth="1"/>
+    <col min="6146" max="6146" width="4.1640625" style="3" customWidth="1"/>
+    <col min="6147" max="6147" width="6.33203125" style="3" customWidth="1"/>
+    <col min="6148" max="6148" width="7.6640625" style="3" customWidth="1"/>
+    <col min="6149" max="6149" width="8.5" style="3" customWidth="1"/>
+    <col min="6150" max="6150" width="8.33203125" style="3" customWidth="1"/>
+    <col min="6151" max="6151" width="7.6640625" style="3" customWidth="1"/>
+    <col min="6152" max="6152" width="6.83203125" style="3" customWidth="1"/>
     <col min="6153" max="6386" width="9" style="3"/>
-    <col min="6387" max="6387" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="6388" max="6388" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="6387" max="6387" width="6.33203125" style="3" customWidth="1"/>
+    <col min="6388" max="6388" width="7.33203125" style="3" customWidth="1"/>
     <col min="6389" max="6389" width="6" style="3" customWidth="1"/>
-    <col min="6390" max="6390" width="25.45" style="3" customWidth="1"/>
-    <col min="6391" max="6391" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="6392" max="6392" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="6390" max="6390" width="25.5" style="3" customWidth="1"/>
+    <col min="6391" max="6391" width="10.83203125" style="3" customWidth="1"/>
+    <col min="6392" max="6392" width="12.33203125" style="3" customWidth="1"/>
     <col min="6393" max="6393" width="11" style="3" customWidth="1"/>
-    <col min="6394" max="6394" width="6.725" style="3" customWidth="1"/>
-    <col min="6395" max="6395" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="6396" max="6396" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="6397" max="6397" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="6398" max="6398" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="6399" max="6399" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="6400" max="6400" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="6401" max="6401" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="6402" max="6402" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="6403" max="6403" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="6404" max="6404" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="6405" max="6405" width="8.45" style="3" customWidth="1"/>
-    <col min="6406" max="6406" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="6407" max="6407" width="7.725" style="3" customWidth="1"/>
-    <col min="6408" max="6408" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="6394" max="6394" width="6.6640625" style="3" customWidth="1"/>
+    <col min="6395" max="6395" width="7.83203125" style="3" customWidth="1"/>
+    <col min="6396" max="6396" width="7.1640625" style="3" customWidth="1"/>
+    <col min="6397" max="6397" width="7.6640625" style="3" customWidth="1"/>
+    <col min="6398" max="6399" width="5.33203125" style="3" customWidth="1"/>
+    <col min="6400" max="6400" width="5.1640625" style="3" customWidth="1"/>
+    <col min="6401" max="6401" width="7.33203125" style="3" customWidth="1"/>
+    <col min="6402" max="6402" width="4.1640625" style="3" customWidth="1"/>
+    <col min="6403" max="6403" width="6.33203125" style="3" customWidth="1"/>
+    <col min="6404" max="6404" width="7.6640625" style="3" customWidth="1"/>
+    <col min="6405" max="6405" width="8.5" style="3" customWidth="1"/>
+    <col min="6406" max="6406" width="8.33203125" style="3" customWidth="1"/>
+    <col min="6407" max="6407" width="7.6640625" style="3" customWidth="1"/>
+    <col min="6408" max="6408" width="6.83203125" style="3" customWidth="1"/>
     <col min="6409" max="6642" width="9" style="3"/>
-    <col min="6643" max="6643" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="6644" max="6644" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="6643" max="6643" width="6.33203125" style="3" customWidth="1"/>
+    <col min="6644" max="6644" width="7.33203125" style="3" customWidth="1"/>
     <col min="6645" max="6645" width="6" style="3" customWidth="1"/>
-    <col min="6646" max="6646" width="25.45" style="3" customWidth="1"/>
-    <col min="6647" max="6647" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="6648" max="6648" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="6646" max="6646" width="25.5" style="3" customWidth="1"/>
+    <col min="6647" max="6647" width="10.83203125" style="3" customWidth="1"/>
+    <col min="6648" max="6648" width="12.33203125" style="3" customWidth="1"/>
     <col min="6649" max="6649" width="11" style="3" customWidth="1"/>
-    <col min="6650" max="6650" width="6.725" style="3" customWidth="1"/>
-    <col min="6651" max="6651" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="6652" max="6652" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="6653" max="6653" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="6654" max="6654" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="6655" max="6655" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="6656" max="6656" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="6657" max="6657" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="6658" max="6658" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="6659" max="6659" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="6660" max="6660" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="6661" max="6661" width="8.45" style="3" customWidth="1"/>
-    <col min="6662" max="6662" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="6663" max="6663" width="7.725" style="3" customWidth="1"/>
-    <col min="6664" max="6664" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="6650" max="6650" width="6.6640625" style="3" customWidth="1"/>
+    <col min="6651" max="6651" width="7.83203125" style="3" customWidth="1"/>
+    <col min="6652" max="6652" width="7.1640625" style="3" customWidth="1"/>
+    <col min="6653" max="6653" width="7.6640625" style="3" customWidth="1"/>
+    <col min="6654" max="6655" width="5.33203125" style="3" customWidth="1"/>
+    <col min="6656" max="6656" width="5.1640625" style="3" customWidth="1"/>
+    <col min="6657" max="6657" width="7.33203125" style="3" customWidth="1"/>
+    <col min="6658" max="6658" width="4.1640625" style="3" customWidth="1"/>
+    <col min="6659" max="6659" width="6.33203125" style="3" customWidth="1"/>
+    <col min="6660" max="6660" width="7.6640625" style="3" customWidth="1"/>
+    <col min="6661" max="6661" width="8.5" style="3" customWidth="1"/>
+    <col min="6662" max="6662" width="8.33203125" style="3" customWidth="1"/>
+    <col min="6663" max="6663" width="7.6640625" style="3" customWidth="1"/>
+    <col min="6664" max="6664" width="6.83203125" style="3" customWidth="1"/>
     <col min="6665" max="6898" width="9" style="3"/>
-    <col min="6899" max="6899" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="6900" max="6900" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="6899" max="6899" width="6.33203125" style="3" customWidth="1"/>
+    <col min="6900" max="6900" width="7.33203125" style="3" customWidth="1"/>
     <col min="6901" max="6901" width="6" style="3" customWidth="1"/>
-    <col min="6902" max="6902" width="25.45" style="3" customWidth="1"/>
-    <col min="6903" max="6903" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="6904" max="6904" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="6902" max="6902" width="25.5" style="3" customWidth="1"/>
+    <col min="6903" max="6903" width="10.83203125" style="3" customWidth="1"/>
+    <col min="6904" max="6904" width="12.33203125" style="3" customWidth="1"/>
     <col min="6905" max="6905" width="11" style="3" customWidth="1"/>
-    <col min="6906" max="6906" width="6.725" style="3" customWidth="1"/>
-    <col min="6907" max="6907" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="6908" max="6908" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="6909" max="6909" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="6910" max="6910" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="6911" max="6911" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="6912" max="6912" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="6913" max="6913" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="6914" max="6914" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="6915" max="6915" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="6916" max="6916" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="6917" max="6917" width="8.45" style="3" customWidth="1"/>
-    <col min="6918" max="6918" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="6919" max="6919" width="7.725" style="3" customWidth="1"/>
-    <col min="6920" max="6920" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="6906" max="6906" width="6.6640625" style="3" customWidth="1"/>
+    <col min="6907" max="6907" width="7.83203125" style="3" customWidth="1"/>
+    <col min="6908" max="6908" width="7.1640625" style="3" customWidth="1"/>
+    <col min="6909" max="6909" width="7.6640625" style="3" customWidth="1"/>
+    <col min="6910" max="6911" width="5.33203125" style="3" customWidth="1"/>
+    <col min="6912" max="6912" width="5.1640625" style="3" customWidth="1"/>
+    <col min="6913" max="6913" width="7.33203125" style="3" customWidth="1"/>
+    <col min="6914" max="6914" width="4.1640625" style="3" customWidth="1"/>
+    <col min="6915" max="6915" width="6.33203125" style="3" customWidth="1"/>
+    <col min="6916" max="6916" width="7.6640625" style="3" customWidth="1"/>
+    <col min="6917" max="6917" width="8.5" style="3" customWidth="1"/>
+    <col min="6918" max="6918" width="8.33203125" style="3" customWidth="1"/>
+    <col min="6919" max="6919" width="7.6640625" style="3" customWidth="1"/>
+    <col min="6920" max="6920" width="6.83203125" style="3" customWidth="1"/>
     <col min="6921" max="7154" width="9" style="3"/>
-    <col min="7155" max="7155" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="7156" max="7156" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="7155" max="7155" width="6.33203125" style="3" customWidth="1"/>
+    <col min="7156" max="7156" width="7.33203125" style="3" customWidth="1"/>
     <col min="7157" max="7157" width="6" style="3" customWidth="1"/>
-    <col min="7158" max="7158" width="25.45" style="3" customWidth="1"/>
-    <col min="7159" max="7159" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="7160" max="7160" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="7158" max="7158" width="25.5" style="3" customWidth="1"/>
+    <col min="7159" max="7159" width="10.83203125" style="3" customWidth="1"/>
+    <col min="7160" max="7160" width="12.33203125" style="3" customWidth="1"/>
     <col min="7161" max="7161" width="11" style="3" customWidth="1"/>
-    <col min="7162" max="7162" width="6.725" style="3" customWidth="1"/>
-    <col min="7163" max="7163" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="7164" max="7164" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="7165" max="7165" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="7166" max="7166" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="7167" max="7167" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="7168" max="7168" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="7169" max="7169" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="7170" max="7170" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="7171" max="7171" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="7172" max="7172" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="7173" max="7173" width="8.45" style="3" customWidth="1"/>
-    <col min="7174" max="7174" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="7175" max="7175" width="7.725" style="3" customWidth="1"/>
-    <col min="7176" max="7176" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="7162" max="7162" width="6.6640625" style="3" customWidth="1"/>
+    <col min="7163" max="7163" width="7.83203125" style="3" customWidth="1"/>
+    <col min="7164" max="7164" width="7.1640625" style="3" customWidth="1"/>
+    <col min="7165" max="7165" width="7.6640625" style="3" customWidth="1"/>
+    <col min="7166" max="7167" width="5.33203125" style="3" customWidth="1"/>
+    <col min="7168" max="7168" width="5.1640625" style="3" customWidth="1"/>
+    <col min="7169" max="7169" width="7.33203125" style="3" customWidth="1"/>
+    <col min="7170" max="7170" width="4.1640625" style="3" customWidth="1"/>
+    <col min="7171" max="7171" width="6.33203125" style="3" customWidth="1"/>
+    <col min="7172" max="7172" width="7.6640625" style="3" customWidth="1"/>
+    <col min="7173" max="7173" width="8.5" style="3" customWidth="1"/>
+    <col min="7174" max="7174" width="8.33203125" style="3" customWidth="1"/>
+    <col min="7175" max="7175" width="7.6640625" style="3" customWidth="1"/>
+    <col min="7176" max="7176" width="6.83203125" style="3" customWidth="1"/>
     <col min="7177" max="7410" width="9" style="3"/>
-    <col min="7411" max="7411" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="7412" max="7412" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="7411" max="7411" width="6.33203125" style="3" customWidth="1"/>
+    <col min="7412" max="7412" width="7.33203125" style="3" customWidth="1"/>
     <col min="7413" max="7413" width="6" style="3" customWidth="1"/>
-    <col min="7414" max="7414" width="25.45" style="3" customWidth="1"/>
-    <col min="7415" max="7415" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="7416" max="7416" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="7414" max="7414" width="25.5" style="3" customWidth="1"/>
+    <col min="7415" max="7415" width="10.83203125" style="3" customWidth="1"/>
+    <col min="7416" max="7416" width="12.33203125" style="3" customWidth="1"/>
     <col min="7417" max="7417" width="11" style="3" customWidth="1"/>
-    <col min="7418" max="7418" width="6.725" style="3" customWidth="1"/>
-    <col min="7419" max="7419" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="7420" max="7420" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="7421" max="7421" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="7422" max="7422" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="7423" max="7423" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="7424" max="7424" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="7425" max="7425" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="7426" max="7426" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="7427" max="7427" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="7428" max="7428" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="7429" max="7429" width="8.45" style="3" customWidth="1"/>
-    <col min="7430" max="7430" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="7431" max="7431" width="7.725" style="3" customWidth="1"/>
-    <col min="7432" max="7432" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="7418" max="7418" width="6.6640625" style="3" customWidth="1"/>
+    <col min="7419" max="7419" width="7.83203125" style="3" customWidth="1"/>
+    <col min="7420" max="7420" width="7.1640625" style="3" customWidth="1"/>
+    <col min="7421" max="7421" width="7.6640625" style="3" customWidth="1"/>
+    <col min="7422" max="7423" width="5.33203125" style="3" customWidth="1"/>
+    <col min="7424" max="7424" width="5.1640625" style="3" customWidth="1"/>
+    <col min="7425" max="7425" width="7.33203125" style="3" customWidth="1"/>
+    <col min="7426" max="7426" width="4.1640625" style="3" customWidth="1"/>
+    <col min="7427" max="7427" width="6.33203125" style="3" customWidth="1"/>
+    <col min="7428" max="7428" width="7.6640625" style="3" customWidth="1"/>
+    <col min="7429" max="7429" width="8.5" style="3" customWidth="1"/>
+    <col min="7430" max="7430" width="8.33203125" style="3" customWidth="1"/>
+    <col min="7431" max="7431" width="7.6640625" style="3" customWidth="1"/>
+    <col min="7432" max="7432" width="6.83203125" style="3" customWidth="1"/>
     <col min="7433" max="7666" width="9" style="3"/>
-    <col min="7667" max="7667" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="7668" max="7668" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="7667" max="7667" width="6.33203125" style="3" customWidth="1"/>
+    <col min="7668" max="7668" width="7.33203125" style="3" customWidth="1"/>
     <col min="7669" max="7669" width="6" style="3" customWidth="1"/>
-    <col min="7670" max="7670" width="25.45" style="3" customWidth="1"/>
-    <col min="7671" max="7671" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="7672" max="7672" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="7670" max="7670" width="25.5" style="3" customWidth="1"/>
+    <col min="7671" max="7671" width="10.83203125" style="3" customWidth="1"/>
+    <col min="7672" max="7672" width="12.33203125" style="3" customWidth="1"/>
     <col min="7673" max="7673" width="11" style="3" customWidth="1"/>
-    <col min="7674" max="7674" width="6.725" style="3" customWidth="1"/>
-    <col min="7675" max="7675" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="7676" max="7676" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="7677" max="7677" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="7678" max="7678" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="7679" max="7679" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="7680" max="7680" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="7681" max="7681" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="7682" max="7682" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="7683" max="7683" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="7684" max="7684" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="7685" max="7685" width="8.45" style="3" customWidth="1"/>
-    <col min="7686" max="7686" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="7687" max="7687" width="7.725" style="3" customWidth="1"/>
-    <col min="7688" max="7688" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="7674" max="7674" width="6.6640625" style="3" customWidth="1"/>
+    <col min="7675" max="7675" width="7.83203125" style="3" customWidth="1"/>
+    <col min="7676" max="7676" width="7.1640625" style="3" customWidth="1"/>
+    <col min="7677" max="7677" width="7.6640625" style="3" customWidth="1"/>
+    <col min="7678" max="7679" width="5.33203125" style="3" customWidth="1"/>
+    <col min="7680" max="7680" width="5.1640625" style="3" customWidth="1"/>
+    <col min="7681" max="7681" width="7.33203125" style="3" customWidth="1"/>
+    <col min="7682" max="7682" width="4.1640625" style="3" customWidth="1"/>
+    <col min="7683" max="7683" width="6.33203125" style="3" customWidth="1"/>
+    <col min="7684" max="7684" width="7.6640625" style="3" customWidth="1"/>
+    <col min="7685" max="7685" width="8.5" style="3" customWidth="1"/>
+    <col min="7686" max="7686" width="8.33203125" style="3" customWidth="1"/>
+    <col min="7687" max="7687" width="7.6640625" style="3" customWidth="1"/>
+    <col min="7688" max="7688" width="6.83203125" style="3" customWidth="1"/>
     <col min="7689" max="7922" width="9" style="3"/>
-    <col min="7923" max="7923" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="7924" max="7924" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="7923" max="7923" width="6.33203125" style="3" customWidth="1"/>
+    <col min="7924" max="7924" width="7.33203125" style="3" customWidth="1"/>
     <col min="7925" max="7925" width="6" style="3" customWidth="1"/>
-    <col min="7926" max="7926" width="25.45" style="3" customWidth="1"/>
-    <col min="7927" max="7927" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="7928" max="7928" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="7926" max="7926" width="25.5" style="3" customWidth="1"/>
+    <col min="7927" max="7927" width="10.83203125" style="3" customWidth="1"/>
+    <col min="7928" max="7928" width="12.33203125" style="3" customWidth="1"/>
     <col min="7929" max="7929" width="11" style="3" customWidth="1"/>
-    <col min="7930" max="7930" width="6.725" style="3" customWidth="1"/>
-    <col min="7931" max="7931" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="7932" max="7932" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="7933" max="7933" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="7934" max="7934" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="7935" max="7935" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="7936" max="7936" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="7937" max="7937" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="7938" max="7938" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="7939" max="7939" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="7940" max="7940" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="7941" max="7941" width="8.45" style="3" customWidth="1"/>
-    <col min="7942" max="7942" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="7943" max="7943" width="7.725" style="3" customWidth="1"/>
-    <col min="7944" max="7944" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="7930" max="7930" width="6.6640625" style="3" customWidth="1"/>
+    <col min="7931" max="7931" width="7.83203125" style="3" customWidth="1"/>
+    <col min="7932" max="7932" width="7.1640625" style="3" customWidth="1"/>
+    <col min="7933" max="7933" width="7.6640625" style="3" customWidth="1"/>
+    <col min="7934" max="7935" width="5.33203125" style="3" customWidth="1"/>
+    <col min="7936" max="7936" width="5.1640625" style="3" customWidth="1"/>
+    <col min="7937" max="7937" width="7.33203125" style="3" customWidth="1"/>
+    <col min="7938" max="7938" width="4.1640625" style="3" customWidth="1"/>
+    <col min="7939" max="7939" width="6.33203125" style="3" customWidth="1"/>
+    <col min="7940" max="7940" width="7.6640625" style="3" customWidth="1"/>
+    <col min="7941" max="7941" width="8.5" style="3" customWidth="1"/>
+    <col min="7942" max="7942" width="8.33203125" style="3" customWidth="1"/>
+    <col min="7943" max="7943" width="7.6640625" style="3" customWidth="1"/>
+    <col min="7944" max="7944" width="6.83203125" style="3" customWidth="1"/>
     <col min="7945" max="8178" width="9" style="3"/>
-    <col min="8179" max="8179" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="8180" max="8180" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="8179" max="8179" width="6.33203125" style="3" customWidth="1"/>
+    <col min="8180" max="8180" width="7.33203125" style="3" customWidth="1"/>
     <col min="8181" max="8181" width="6" style="3" customWidth="1"/>
-    <col min="8182" max="8182" width="25.45" style="3" customWidth="1"/>
-    <col min="8183" max="8183" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="8184" max="8184" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="8182" max="8182" width="25.5" style="3" customWidth="1"/>
+    <col min="8183" max="8183" width="10.83203125" style="3" customWidth="1"/>
+    <col min="8184" max="8184" width="12.33203125" style="3" customWidth="1"/>
     <col min="8185" max="8185" width="11" style="3" customWidth="1"/>
-    <col min="8186" max="8186" width="6.725" style="3" customWidth="1"/>
-    <col min="8187" max="8187" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="8188" max="8188" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="8189" max="8189" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="8190" max="8190" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="8191" max="8191" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="8192" max="8192" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="8193" max="8193" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="8194" max="8194" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="8195" max="8195" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="8196" max="8196" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="8197" max="8197" width="8.45" style="3" customWidth="1"/>
-    <col min="8198" max="8198" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="8199" max="8199" width="7.725" style="3" customWidth="1"/>
-    <col min="8200" max="8200" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="8186" max="8186" width="6.6640625" style="3" customWidth="1"/>
+    <col min="8187" max="8187" width="7.83203125" style="3" customWidth="1"/>
+    <col min="8188" max="8188" width="7.1640625" style="3" customWidth="1"/>
+    <col min="8189" max="8189" width="7.6640625" style="3" customWidth="1"/>
+    <col min="8190" max="8191" width="5.33203125" style="3" customWidth="1"/>
+    <col min="8192" max="8192" width="5.1640625" style="3" customWidth="1"/>
+    <col min="8193" max="8193" width="7.33203125" style="3" customWidth="1"/>
+    <col min="8194" max="8194" width="4.1640625" style="3" customWidth="1"/>
+    <col min="8195" max="8195" width="6.33203125" style="3" customWidth="1"/>
+    <col min="8196" max="8196" width="7.6640625" style="3" customWidth="1"/>
+    <col min="8197" max="8197" width="8.5" style="3" customWidth="1"/>
+    <col min="8198" max="8198" width="8.33203125" style="3" customWidth="1"/>
+    <col min="8199" max="8199" width="7.6640625" style="3" customWidth="1"/>
+    <col min="8200" max="8200" width="6.83203125" style="3" customWidth="1"/>
     <col min="8201" max="8434" width="9" style="3"/>
-    <col min="8435" max="8435" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="8436" max="8436" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="8435" max="8435" width="6.33203125" style="3" customWidth="1"/>
+    <col min="8436" max="8436" width="7.33203125" style="3" customWidth="1"/>
     <col min="8437" max="8437" width="6" style="3" customWidth="1"/>
-    <col min="8438" max="8438" width="25.45" style="3" customWidth="1"/>
-    <col min="8439" max="8439" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="8440" max="8440" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="8438" max="8438" width="25.5" style="3" customWidth="1"/>
+    <col min="8439" max="8439" width="10.83203125" style="3" customWidth="1"/>
+    <col min="8440" max="8440" width="12.33203125" style="3" customWidth="1"/>
     <col min="8441" max="8441" width="11" style="3" customWidth="1"/>
-    <col min="8442" max="8442" width="6.725" style="3" customWidth="1"/>
-    <col min="8443" max="8443" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="8444" max="8444" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="8445" max="8445" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="8446" max="8446" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="8447" max="8447" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="8448" max="8448" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="8449" max="8449" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="8450" max="8450" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="8451" max="8451" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="8452" max="8452" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="8453" max="8453" width="8.45" style="3" customWidth="1"/>
-    <col min="8454" max="8454" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="8455" max="8455" width="7.725" style="3" customWidth="1"/>
-    <col min="8456" max="8456" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="8442" max="8442" width="6.6640625" style="3" customWidth="1"/>
+    <col min="8443" max="8443" width="7.83203125" style="3" customWidth="1"/>
+    <col min="8444" max="8444" width="7.1640625" style="3" customWidth="1"/>
+    <col min="8445" max="8445" width="7.6640625" style="3" customWidth="1"/>
+    <col min="8446" max="8447" width="5.33203125" style="3" customWidth="1"/>
+    <col min="8448" max="8448" width="5.1640625" style="3" customWidth="1"/>
+    <col min="8449" max="8449" width="7.33203125" style="3" customWidth="1"/>
+    <col min="8450" max="8450" width="4.1640625" style="3" customWidth="1"/>
+    <col min="8451" max="8451" width="6.33203125" style="3" customWidth="1"/>
+    <col min="8452" max="8452" width="7.6640625" style="3" customWidth="1"/>
+    <col min="8453" max="8453" width="8.5" style="3" customWidth="1"/>
+    <col min="8454" max="8454" width="8.33203125" style="3" customWidth="1"/>
+    <col min="8455" max="8455" width="7.6640625" style="3" customWidth="1"/>
+    <col min="8456" max="8456" width="6.83203125" style="3" customWidth="1"/>
     <col min="8457" max="8690" width="9" style="3"/>
-    <col min="8691" max="8691" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="8692" max="8692" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="8691" max="8691" width="6.33203125" style="3" customWidth="1"/>
+    <col min="8692" max="8692" width="7.33203125" style="3" customWidth="1"/>
     <col min="8693" max="8693" width="6" style="3" customWidth="1"/>
-    <col min="8694" max="8694" width="25.45" style="3" customWidth="1"/>
-    <col min="8695" max="8695" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="8696" max="8696" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="8694" max="8694" width="25.5" style="3" customWidth="1"/>
+    <col min="8695" max="8695" width="10.83203125" style="3" customWidth="1"/>
+    <col min="8696" max="8696" width="12.33203125" style="3" customWidth="1"/>
     <col min="8697" max="8697" width="11" style="3" customWidth="1"/>
-    <col min="8698" max="8698" width="6.725" style="3" customWidth="1"/>
-    <col min="8699" max="8699" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="8700" max="8700" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="8701" max="8701" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="8702" max="8702" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="8703" max="8703" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="8704" max="8704" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="8705" max="8705" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="8706" max="8706" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="8707" max="8707" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="8708" max="8708" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="8709" max="8709" width="8.45" style="3" customWidth="1"/>
-    <col min="8710" max="8710" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="8711" max="8711" width="7.725" style="3" customWidth="1"/>
-    <col min="8712" max="8712" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="8698" max="8698" width="6.6640625" style="3" customWidth="1"/>
+    <col min="8699" max="8699" width="7.83203125" style="3" customWidth="1"/>
+    <col min="8700" max="8700" width="7.1640625" style="3" customWidth="1"/>
+    <col min="8701" max="8701" width="7.6640625" style="3" customWidth="1"/>
+    <col min="8702" max="8703" width="5.33203125" style="3" customWidth="1"/>
+    <col min="8704" max="8704" width="5.1640625" style="3" customWidth="1"/>
+    <col min="8705" max="8705" width="7.33203125" style="3" customWidth="1"/>
+    <col min="8706" max="8706" width="4.1640625" style="3" customWidth="1"/>
+    <col min="8707" max="8707" width="6.33203125" style="3" customWidth="1"/>
+    <col min="8708" max="8708" width="7.6640625" style="3" customWidth="1"/>
+    <col min="8709" max="8709" width="8.5" style="3" customWidth="1"/>
+    <col min="8710" max="8710" width="8.33203125" style="3" customWidth="1"/>
+    <col min="8711" max="8711" width="7.6640625" style="3" customWidth="1"/>
+    <col min="8712" max="8712" width="6.83203125" style="3" customWidth="1"/>
     <col min="8713" max="8946" width="9" style="3"/>
-    <col min="8947" max="8947" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="8948" max="8948" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="8947" max="8947" width="6.33203125" style="3" customWidth="1"/>
+    <col min="8948" max="8948" width="7.33203125" style="3" customWidth="1"/>
     <col min="8949" max="8949" width="6" style="3" customWidth="1"/>
-    <col min="8950" max="8950" width="25.45" style="3" customWidth="1"/>
-    <col min="8951" max="8951" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="8952" max="8952" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="8950" max="8950" width="25.5" style="3" customWidth="1"/>
+    <col min="8951" max="8951" width="10.83203125" style="3" customWidth="1"/>
+    <col min="8952" max="8952" width="12.33203125" style="3" customWidth="1"/>
     <col min="8953" max="8953" width="11" style="3" customWidth="1"/>
-    <col min="8954" max="8954" width="6.725" style="3" customWidth="1"/>
-    <col min="8955" max="8955" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="8956" max="8956" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="8957" max="8957" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="8958" max="8958" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="8959" max="8959" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="8960" max="8960" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="8961" max="8961" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="8962" max="8962" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="8963" max="8963" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="8964" max="8964" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="8965" max="8965" width="8.45" style="3" customWidth="1"/>
-    <col min="8966" max="8966" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="8967" max="8967" width="7.725" style="3" customWidth="1"/>
-    <col min="8968" max="8968" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="8954" max="8954" width="6.6640625" style="3" customWidth="1"/>
+    <col min="8955" max="8955" width="7.83203125" style="3" customWidth="1"/>
+    <col min="8956" max="8956" width="7.1640625" style="3" customWidth="1"/>
+    <col min="8957" max="8957" width="7.6640625" style="3" customWidth="1"/>
+    <col min="8958" max="8959" width="5.33203125" style="3" customWidth="1"/>
+    <col min="8960" max="8960" width="5.1640625" style="3" customWidth="1"/>
+    <col min="8961" max="8961" width="7.33203125" style="3" customWidth="1"/>
+    <col min="8962" max="8962" width="4.1640625" style="3" customWidth="1"/>
+    <col min="8963" max="8963" width="6.33203125" style="3" customWidth="1"/>
+    <col min="8964" max="8964" width="7.6640625" style="3" customWidth="1"/>
+    <col min="8965" max="8965" width="8.5" style="3" customWidth="1"/>
+    <col min="8966" max="8966" width="8.33203125" style="3" customWidth="1"/>
+    <col min="8967" max="8967" width="7.6640625" style="3" customWidth="1"/>
+    <col min="8968" max="8968" width="6.83203125" style="3" customWidth="1"/>
     <col min="8969" max="9202" width="9" style="3"/>
-    <col min="9203" max="9203" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="9204" max="9204" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="9203" max="9203" width="6.33203125" style="3" customWidth="1"/>
+    <col min="9204" max="9204" width="7.33203125" style="3" customWidth="1"/>
     <col min="9205" max="9205" width="6" style="3" customWidth="1"/>
-    <col min="9206" max="9206" width="25.45" style="3" customWidth="1"/>
-    <col min="9207" max="9207" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="9208" max="9208" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="9206" max="9206" width="25.5" style="3" customWidth="1"/>
+    <col min="9207" max="9207" width="10.83203125" style="3" customWidth="1"/>
+    <col min="9208" max="9208" width="12.33203125" style="3" customWidth="1"/>
     <col min="9209" max="9209" width="11" style="3" customWidth="1"/>
-    <col min="9210" max="9210" width="6.725" style="3" customWidth="1"/>
-    <col min="9211" max="9211" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="9212" max="9212" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="9213" max="9213" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="9214" max="9214" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="9215" max="9215" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="9216" max="9216" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="9217" max="9217" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="9218" max="9218" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="9219" max="9219" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="9220" max="9220" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="9221" max="9221" width="8.45" style="3" customWidth="1"/>
-    <col min="9222" max="9222" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="9223" max="9223" width="7.725" style="3" customWidth="1"/>
-    <col min="9224" max="9224" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="9210" max="9210" width="6.6640625" style="3" customWidth="1"/>
+    <col min="9211" max="9211" width="7.83203125" style="3" customWidth="1"/>
+    <col min="9212" max="9212" width="7.1640625" style="3" customWidth="1"/>
+    <col min="9213" max="9213" width="7.6640625" style="3" customWidth="1"/>
+    <col min="9214" max="9215" width="5.33203125" style="3" customWidth="1"/>
+    <col min="9216" max="9216" width="5.1640625" style="3" customWidth="1"/>
+    <col min="9217" max="9217" width="7.33203125" style="3" customWidth="1"/>
+    <col min="9218" max="9218" width="4.1640625" style="3" customWidth="1"/>
+    <col min="9219" max="9219" width="6.33203125" style="3" customWidth="1"/>
+    <col min="9220" max="9220" width="7.6640625" style="3" customWidth="1"/>
+    <col min="9221" max="9221" width="8.5" style="3" customWidth="1"/>
+    <col min="9222" max="9222" width="8.33203125" style="3" customWidth="1"/>
+    <col min="9223" max="9223" width="7.6640625" style="3" customWidth="1"/>
+    <col min="9224" max="9224" width="6.83203125" style="3" customWidth="1"/>
     <col min="9225" max="9458" width="9" style="3"/>
-    <col min="9459" max="9459" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="9460" max="9460" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="9459" max="9459" width="6.33203125" style="3" customWidth="1"/>
+    <col min="9460" max="9460" width="7.33203125" style="3" customWidth="1"/>
     <col min="9461" max="9461" width="6" style="3" customWidth="1"/>
-    <col min="9462" max="9462" width="25.45" style="3" customWidth="1"/>
-    <col min="9463" max="9463" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="9464" max="9464" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="9462" max="9462" width="25.5" style="3" customWidth="1"/>
+    <col min="9463" max="9463" width="10.83203125" style="3" customWidth="1"/>
+    <col min="9464" max="9464" width="12.33203125" style="3" customWidth="1"/>
     <col min="9465" max="9465" width="11" style="3" customWidth="1"/>
-    <col min="9466" max="9466" width="6.725" style="3" customWidth="1"/>
-    <col min="9467" max="9467" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="9468" max="9468" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="9469" max="9469" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="9470" max="9470" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="9471" max="9471" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="9472" max="9472" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="9473" max="9473" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="9474" max="9474" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="9475" max="9475" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="9476" max="9476" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="9477" max="9477" width="8.45" style="3" customWidth="1"/>
-    <col min="9478" max="9478" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="9479" max="9479" width="7.725" style="3" customWidth="1"/>
-    <col min="9480" max="9480" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="9466" max="9466" width="6.6640625" style="3" customWidth="1"/>
+    <col min="9467" max="9467" width="7.83203125" style="3" customWidth="1"/>
+    <col min="9468" max="9468" width="7.1640625" style="3" customWidth="1"/>
+    <col min="9469" max="9469" width="7.6640625" style="3" customWidth="1"/>
+    <col min="9470" max="9471" width="5.33203125" style="3" customWidth="1"/>
+    <col min="9472" max="9472" width="5.1640625" style="3" customWidth="1"/>
+    <col min="9473" max="9473" width="7.33203125" style="3" customWidth="1"/>
+    <col min="9474" max="9474" width="4.1640625" style="3" customWidth="1"/>
+    <col min="9475" max="9475" width="6.33203125" style="3" customWidth="1"/>
+    <col min="9476" max="9476" width="7.6640625" style="3" customWidth="1"/>
+    <col min="9477" max="9477" width="8.5" style="3" customWidth="1"/>
+    <col min="9478" max="9478" width="8.33203125" style="3" customWidth="1"/>
+    <col min="9479" max="9479" width="7.6640625" style="3" customWidth="1"/>
+    <col min="9480" max="9480" width="6.83203125" style="3" customWidth="1"/>
     <col min="9481" max="9714" width="9" style="3"/>
-    <col min="9715" max="9715" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="9716" max="9716" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="9715" max="9715" width="6.33203125" style="3" customWidth="1"/>
+    <col min="9716" max="9716" width="7.33203125" style="3" customWidth="1"/>
     <col min="9717" max="9717" width="6" style="3" customWidth="1"/>
-    <col min="9718" max="9718" width="25.45" style="3" customWidth="1"/>
-    <col min="9719" max="9719" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="9720" max="9720" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="9718" max="9718" width="25.5" style="3" customWidth="1"/>
+    <col min="9719" max="9719" width="10.83203125" style="3" customWidth="1"/>
+    <col min="9720" max="9720" width="12.33203125" style="3" customWidth="1"/>
     <col min="9721" max="9721" width="11" style="3" customWidth="1"/>
-    <col min="9722" max="9722" width="6.725" style="3" customWidth="1"/>
-    <col min="9723" max="9723" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="9724" max="9724" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="9725" max="9725" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="9726" max="9726" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="9727" max="9727" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="9728" max="9728" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="9729" max="9729" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="9730" max="9730" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="9731" max="9731" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="9732" max="9732" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="9733" max="9733" width="8.45" style="3" customWidth="1"/>
-    <col min="9734" max="9734" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="9735" max="9735" width="7.725" style="3" customWidth="1"/>
-    <col min="9736" max="9736" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="9722" max="9722" width="6.6640625" style="3" customWidth="1"/>
+    <col min="9723" max="9723" width="7.83203125" style="3" customWidth="1"/>
+    <col min="9724" max="9724" width="7.1640625" style="3" customWidth="1"/>
+    <col min="9725" max="9725" width="7.6640625" style="3" customWidth="1"/>
+    <col min="9726" max="9727" width="5.33203125" style="3" customWidth="1"/>
+    <col min="9728" max="9728" width="5.1640625" style="3" customWidth="1"/>
+    <col min="9729" max="9729" width="7.33203125" style="3" customWidth="1"/>
+    <col min="9730" max="9730" width="4.1640625" style="3" customWidth="1"/>
+    <col min="9731" max="9731" width="6.33203125" style="3" customWidth="1"/>
+    <col min="9732" max="9732" width="7.6640625" style="3" customWidth="1"/>
+    <col min="9733" max="9733" width="8.5" style="3" customWidth="1"/>
+    <col min="9734" max="9734" width="8.33203125" style="3" customWidth="1"/>
+    <col min="9735" max="9735" width="7.6640625" style="3" customWidth="1"/>
+    <col min="9736" max="9736" width="6.83203125" style="3" customWidth="1"/>
     <col min="9737" max="9970" width="9" style="3"/>
-    <col min="9971" max="9971" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="9972" max="9972" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="9971" max="9971" width="6.33203125" style="3" customWidth="1"/>
+    <col min="9972" max="9972" width="7.33203125" style="3" customWidth="1"/>
     <col min="9973" max="9973" width="6" style="3" customWidth="1"/>
-    <col min="9974" max="9974" width="25.45" style="3" customWidth="1"/>
-    <col min="9975" max="9975" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="9976" max="9976" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="9974" max="9974" width="25.5" style="3" customWidth="1"/>
+    <col min="9975" max="9975" width="10.83203125" style="3" customWidth="1"/>
+    <col min="9976" max="9976" width="12.33203125" style="3" customWidth="1"/>
     <col min="9977" max="9977" width="11" style="3" customWidth="1"/>
-    <col min="9978" max="9978" width="6.725" style="3" customWidth="1"/>
-    <col min="9979" max="9979" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="9980" max="9980" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="9981" max="9981" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="9982" max="9982" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="9983" max="9983" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="9984" max="9984" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="9985" max="9985" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="9986" max="9986" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="9987" max="9987" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="9988" max="9988" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="9989" max="9989" width="8.45" style="3" customWidth="1"/>
-    <col min="9990" max="9990" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="9991" max="9991" width="7.725" style="3" customWidth="1"/>
-    <col min="9992" max="9992" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="9978" max="9978" width="6.6640625" style="3" customWidth="1"/>
+    <col min="9979" max="9979" width="7.83203125" style="3" customWidth="1"/>
+    <col min="9980" max="9980" width="7.1640625" style="3" customWidth="1"/>
+    <col min="9981" max="9981" width="7.6640625" style="3" customWidth="1"/>
+    <col min="9982" max="9983" width="5.33203125" style="3" customWidth="1"/>
+    <col min="9984" max="9984" width="5.1640625" style="3" customWidth="1"/>
+    <col min="9985" max="9985" width="7.33203125" style="3" customWidth="1"/>
+    <col min="9986" max="9986" width="4.1640625" style="3" customWidth="1"/>
+    <col min="9987" max="9987" width="6.33203125" style="3" customWidth="1"/>
+    <col min="9988" max="9988" width="7.6640625" style="3" customWidth="1"/>
+    <col min="9989" max="9989" width="8.5" style="3" customWidth="1"/>
+    <col min="9990" max="9990" width="8.33203125" style="3" customWidth="1"/>
+    <col min="9991" max="9991" width="7.6640625" style="3" customWidth="1"/>
+    <col min="9992" max="9992" width="6.83203125" style="3" customWidth="1"/>
     <col min="9993" max="10226" width="9" style="3"/>
-    <col min="10227" max="10227" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="10228" max="10228" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="10227" max="10227" width="6.33203125" style="3" customWidth="1"/>
+    <col min="10228" max="10228" width="7.33203125" style="3" customWidth="1"/>
     <col min="10229" max="10229" width="6" style="3" customWidth="1"/>
-    <col min="10230" max="10230" width="25.45" style="3" customWidth="1"/>
-    <col min="10231" max="10231" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="10232" max="10232" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="10230" max="10230" width="25.5" style="3" customWidth="1"/>
+    <col min="10231" max="10231" width="10.83203125" style="3" customWidth="1"/>
+    <col min="10232" max="10232" width="12.33203125" style="3" customWidth="1"/>
     <col min="10233" max="10233" width="11" style="3" customWidth="1"/>
-    <col min="10234" max="10234" width="6.725" style="3" customWidth="1"/>
-    <col min="10235" max="10235" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="10236" max="10236" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="10237" max="10237" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="10238" max="10238" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="10239" max="10239" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="10240" max="10240" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="10241" max="10241" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="10242" max="10242" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="10243" max="10243" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="10244" max="10244" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="10245" max="10245" width="8.45" style="3" customWidth="1"/>
-    <col min="10246" max="10246" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="10247" max="10247" width="7.725" style="3" customWidth="1"/>
-    <col min="10248" max="10248" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="10234" max="10234" width="6.6640625" style="3" customWidth="1"/>
+    <col min="10235" max="10235" width="7.83203125" style="3" customWidth="1"/>
+    <col min="10236" max="10236" width="7.1640625" style="3" customWidth="1"/>
+    <col min="10237" max="10237" width="7.6640625" style="3" customWidth="1"/>
+    <col min="10238" max="10239" width="5.33203125" style="3" customWidth="1"/>
+    <col min="10240" max="10240" width="5.1640625" style="3" customWidth="1"/>
+    <col min="10241" max="10241" width="7.33203125" style="3" customWidth="1"/>
+    <col min="10242" max="10242" width="4.1640625" style="3" customWidth="1"/>
+    <col min="10243" max="10243" width="6.33203125" style="3" customWidth="1"/>
+    <col min="10244" max="10244" width="7.6640625" style="3" customWidth="1"/>
+    <col min="10245" max="10245" width="8.5" style="3" customWidth="1"/>
+    <col min="10246" max="10246" width="8.33203125" style="3" customWidth="1"/>
+    <col min="10247" max="10247" width="7.6640625" style="3" customWidth="1"/>
+    <col min="10248" max="10248" width="6.83203125" style="3" customWidth="1"/>
     <col min="10249" max="10482" width="9" style="3"/>
-    <col min="10483" max="10483" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="10484" max="10484" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="10483" max="10483" width="6.33203125" style="3" customWidth="1"/>
+    <col min="10484" max="10484" width="7.33203125" style="3" customWidth="1"/>
     <col min="10485" max="10485" width="6" style="3" customWidth="1"/>
-    <col min="10486" max="10486" width="25.45" style="3" customWidth="1"/>
-    <col min="10487" max="10487" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="10488" max="10488" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="10486" max="10486" width="25.5" style="3" customWidth="1"/>
+    <col min="10487" max="10487" width="10.83203125" style="3" customWidth="1"/>
+    <col min="10488" max="10488" width="12.33203125" style="3" customWidth="1"/>
     <col min="10489" max="10489" width="11" style="3" customWidth="1"/>
-    <col min="10490" max="10490" width="6.725" style="3" customWidth="1"/>
-    <col min="10491" max="10491" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="10492" max="10492" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="10493" max="10493" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="10494" max="10494" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="10495" max="10495" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="10496" max="10496" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="10497" max="10497" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="10498" max="10498" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="10499" max="10499" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="10500" max="10500" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="10501" max="10501" width="8.45" style="3" customWidth="1"/>
-    <col min="10502" max="10502" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="10503" max="10503" width="7.725" style="3" customWidth="1"/>
-    <col min="10504" max="10504" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="10490" max="10490" width="6.6640625" style="3" customWidth="1"/>
+    <col min="10491" max="10491" width="7.83203125" style="3" customWidth="1"/>
+    <col min="10492" max="10492" width="7.1640625" style="3" customWidth="1"/>
+    <col min="10493" max="10493" width="7.6640625" style="3" customWidth="1"/>
+    <col min="10494" max="10495" width="5.33203125" style="3" customWidth="1"/>
+    <col min="10496" max="10496" width="5.1640625" style="3" customWidth="1"/>
+    <col min="10497" max="10497" width="7.33203125" style="3" customWidth="1"/>
+    <col min="10498" max="10498" width="4.1640625" style="3" customWidth="1"/>
+    <col min="10499" max="10499" width="6.33203125" style="3" customWidth="1"/>
+    <col min="10500" max="10500" width="7.6640625" style="3" customWidth="1"/>
+    <col min="10501" max="10501" width="8.5" style="3" customWidth="1"/>
+    <col min="10502" max="10502" width="8.33203125" style="3" customWidth="1"/>
+    <col min="10503" max="10503" width="7.6640625" style="3" customWidth="1"/>
+    <col min="10504" max="10504" width="6.83203125" style="3" customWidth="1"/>
     <col min="10505" max="10738" width="9" style="3"/>
-    <col min="10739" max="10739" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="10740" max="10740" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="10739" max="10739" width="6.33203125" style="3" customWidth="1"/>
+    <col min="10740" max="10740" width="7.33203125" style="3" customWidth="1"/>
     <col min="10741" max="10741" width="6" style="3" customWidth="1"/>
-    <col min="10742" max="10742" width="25.45" style="3" customWidth="1"/>
-    <col min="10743" max="10743" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="10744" max="10744" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="10742" max="10742" width="25.5" style="3" customWidth="1"/>
+    <col min="10743" max="10743" width="10.83203125" style="3" customWidth="1"/>
+    <col min="10744" max="10744" width="12.33203125" style="3" customWidth="1"/>
     <col min="10745" max="10745" width="11" style="3" customWidth="1"/>
-    <col min="10746" max="10746" width="6.725" style="3" customWidth="1"/>
-    <col min="10747" max="10747" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="10748" max="10748" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="10749" max="10749" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="10750" max="10750" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="10751" max="10751" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="10752" max="10752" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="10753" max="10753" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="10754" max="10754" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="10755" max="10755" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="10756" max="10756" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="10757" max="10757" width="8.45" style="3" customWidth="1"/>
-    <col min="10758" max="10758" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="10759" max="10759" width="7.725" style="3" customWidth="1"/>
-    <col min="10760" max="10760" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="10746" max="10746" width="6.6640625" style="3" customWidth="1"/>
+    <col min="10747" max="10747" width="7.83203125" style="3" customWidth="1"/>
+    <col min="10748" max="10748" width="7.1640625" style="3" customWidth="1"/>
+    <col min="10749" max="10749" width="7.6640625" style="3" customWidth="1"/>
+    <col min="10750" max="10751" width="5.33203125" style="3" customWidth="1"/>
+    <col min="10752" max="10752" width="5.1640625" style="3" customWidth="1"/>
+    <col min="10753" max="10753" width="7.33203125" style="3" customWidth="1"/>
+    <col min="10754" max="10754" width="4.1640625" style="3" customWidth="1"/>
+    <col min="10755" max="10755" width="6.33203125" style="3" customWidth="1"/>
+    <col min="10756" max="10756" width="7.6640625" style="3" customWidth="1"/>
+    <col min="10757" max="10757" width="8.5" style="3" customWidth="1"/>
+    <col min="10758" max="10758" width="8.33203125" style="3" customWidth="1"/>
+    <col min="10759" max="10759" width="7.6640625" style="3" customWidth="1"/>
+    <col min="10760" max="10760" width="6.83203125" style="3" customWidth="1"/>
     <col min="10761" max="10994" width="9" style="3"/>
-    <col min="10995" max="10995" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="10996" max="10996" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="10995" max="10995" width="6.33203125" style="3" customWidth="1"/>
+    <col min="10996" max="10996" width="7.33203125" style="3" customWidth="1"/>
     <col min="10997" max="10997" width="6" style="3" customWidth="1"/>
-    <col min="10998" max="10998" width="25.45" style="3" customWidth="1"/>
-    <col min="10999" max="10999" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="11000" max="11000" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="10998" max="10998" width="25.5" style="3" customWidth="1"/>
+    <col min="10999" max="10999" width="10.83203125" style="3" customWidth="1"/>
+    <col min="11000" max="11000" width="12.33203125" style="3" customWidth="1"/>
     <col min="11001" max="11001" width="11" style="3" customWidth="1"/>
-    <col min="11002" max="11002" width="6.725" style="3" customWidth="1"/>
-    <col min="11003" max="11003" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="11004" max="11004" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="11005" max="11005" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="11006" max="11006" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="11007" max="11007" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="11008" max="11008" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="11009" max="11009" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="11010" max="11010" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="11011" max="11011" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="11012" max="11012" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="11013" max="11013" width="8.45" style="3" customWidth="1"/>
-    <col min="11014" max="11014" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="11015" max="11015" width="7.725" style="3" customWidth="1"/>
-    <col min="11016" max="11016" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="11002" max="11002" width="6.6640625" style="3" customWidth="1"/>
+    <col min="11003" max="11003" width="7.83203125" style="3" customWidth="1"/>
+    <col min="11004" max="11004" width="7.1640625" style="3" customWidth="1"/>
+    <col min="11005" max="11005" width="7.6640625" style="3" customWidth="1"/>
+    <col min="11006" max="11007" width="5.33203125" style="3" customWidth="1"/>
+    <col min="11008" max="11008" width="5.1640625" style="3" customWidth="1"/>
+    <col min="11009" max="11009" width="7.33203125" style="3" customWidth="1"/>
+    <col min="11010" max="11010" width="4.1640625" style="3" customWidth="1"/>
+    <col min="11011" max="11011" width="6.33203125" style="3" customWidth="1"/>
+    <col min="11012" max="11012" width="7.6640625" style="3" customWidth="1"/>
+    <col min="11013" max="11013" width="8.5" style="3" customWidth="1"/>
+    <col min="11014" max="11014" width="8.33203125" style="3" customWidth="1"/>
+    <col min="11015" max="11015" width="7.6640625" style="3" customWidth="1"/>
+    <col min="11016" max="11016" width="6.83203125" style="3" customWidth="1"/>
     <col min="11017" max="11250" width="9" style="3"/>
-    <col min="11251" max="11251" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="11252" max="11252" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="11251" max="11251" width="6.33203125" style="3" customWidth="1"/>
+    <col min="11252" max="11252" width="7.33203125" style="3" customWidth="1"/>
     <col min="11253" max="11253" width="6" style="3" customWidth="1"/>
-    <col min="11254" max="11254" width="25.45" style="3" customWidth="1"/>
-    <col min="11255" max="11255" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="11256" max="11256" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="11254" max="11254" width="25.5" style="3" customWidth="1"/>
+    <col min="11255" max="11255" width="10.83203125" style="3" customWidth="1"/>
+    <col min="11256" max="11256" width="12.33203125" style="3" customWidth="1"/>
     <col min="11257" max="11257" width="11" style="3" customWidth="1"/>
-    <col min="11258" max="11258" width="6.725" style="3" customWidth="1"/>
-    <col min="11259" max="11259" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="11260" max="11260" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="11261" max="11261" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="11262" max="11262" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="11263" max="11263" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="11264" max="11264" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="11265" max="11265" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="11266" max="11266" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="11267" max="11267" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="11268" max="11268" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="11269" max="11269" width="8.45" style="3" customWidth="1"/>
-    <col min="11270" max="11270" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="11271" max="11271" width="7.725" style="3" customWidth="1"/>
-    <col min="11272" max="11272" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="11258" max="11258" width="6.6640625" style="3" customWidth="1"/>
+    <col min="11259" max="11259" width="7.83203125" style="3" customWidth="1"/>
+    <col min="11260" max="11260" width="7.1640625" style="3" customWidth="1"/>
+    <col min="11261" max="11261" width="7.6640625" style="3" customWidth="1"/>
+    <col min="11262" max="11263" width="5.33203125" style="3" customWidth="1"/>
+    <col min="11264" max="11264" width="5.1640625" style="3" customWidth="1"/>
+    <col min="11265" max="11265" width="7.33203125" style="3" customWidth="1"/>
+    <col min="11266" max="11266" width="4.1640625" style="3" customWidth="1"/>
+    <col min="11267" max="11267" width="6.33203125" style="3" customWidth="1"/>
+    <col min="11268" max="11268" width="7.6640625" style="3" customWidth="1"/>
+    <col min="11269" max="11269" width="8.5" style="3" customWidth="1"/>
+    <col min="11270" max="11270" width="8.33203125" style="3" customWidth="1"/>
+    <col min="11271" max="11271" width="7.6640625" style="3" customWidth="1"/>
+    <col min="11272" max="11272" width="6.83203125" style="3" customWidth="1"/>
     <col min="11273" max="11506" width="9" style="3"/>
-    <col min="11507" max="11507" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="11508" max="11508" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="11507" max="11507" width="6.33203125" style="3" customWidth="1"/>
+    <col min="11508" max="11508" width="7.33203125" style="3" customWidth="1"/>
     <col min="11509" max="11509" width="6" style="3" customWidth="1"/>
-    <col min="11510" max="11510" width="25.45" style="3" customWidth="1"/>
-    <col min="11511" max="11511" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="11512" max="11512" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="11510" max="11510" width="25.5" style="3" customWidth="1"/>
+    <col min="11511" max="11511" width="10.83203125" style="3" customWidth="1"/>
+    <col min="11512" max="11512" width="12.33203125" style="3" customWidth="1"/>
     <col min="11513" max="11513" width="11" style="3" customWidth="1"/>
-    <col min="11514" max="11514" width="6.725" style="3" customWidth="1"/>
-    <col min="11515" max="11515" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="11516" max="11516" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="11517" max="11517" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="11518" max="11518" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="11519" max="11519" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="11520" max="11520" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="11521" max="11521" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="11522" max="11522" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="11523" max="11523" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="11524" max="11524" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="11525" max="11525" width="8.45" style="3" customWidth="1"/>
-    <col min="11526" max="11526" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="11527" max="11527" width="7.725" style="3" customWidth="1"/>
-    <col min="11528" max="11528" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="11514" max="11514" width="6.6640625" style="3" customWidth="1"/>
+    <col min="11515" max="11515" width="7.83203125" style="3" customWidth="1"/>
+    <col min="11516" max="11516" width="7.1640625" style="3" customWidth="1"/>
+    <col min="11517" max="11517" width="7.6640625" style="3" customWidth="1"/>
+    <col min="11518" max="11519" width="5.33203125" style="3" customWidth="1"/>
+    <col min="11520" max="11520" width="5.1640625" style="3" customWidth="1"/>
+    <col min="11521" max="11521" width="7.33203125" style="3" customWidth="1"/>
+    <col min="11522" max="11522" width="4.1640625" style="3" customWidth="1"/>
+    <col min="11523" max="11523" width="6.33203125" style="3" customWidth="1"/>
+    <col min="11524" max="11524" width="7.6640625" style="3" customWidth="1"/>
+    <col min="11525" max="11525" width="8.5" style="3" customWidth="1"/>
+    <col min="11526" max="11526" width="8.33203125" style="3" customWidth="1"/>
+    <col min="11527" max="11527" width="7.6640625" style="3" customWidth="1"/>
+    <col min="11528" max="11528" width="6.83203125" style="3" customWidth="1"/>
     <col min="11529" max="11762" width="9" style="3"/>
-    <col min="11763" max="11763" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="11764" max="11764" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="11763" max="11763" width="6.33203125" style="3" customWidth="1"/>
+    <col min="11764" max="11764" width="7.33203125" style="3" customWidth="1"/>
     <col min="11765" max="11765" width="6" style="3" customWidth="1"/>
-    <col min="11766" max="11766" width="25.45" style="3" customWidth="1"/>
-    <col min="11767" max="11767" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="11768" max="11768" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="11766" max="11766" width="25.5" style="3" customWidth="1"/>
+    <col min="11767" max="11767" width="10.83203125" style="3" customWidth="1"/>
+    <col min="11768" max="11768" width="12.33203125" style="3" customWidth="1"/>
     <col min="11769" max="11769" width="11" style="3" customWidth="1"/>
-    <col min="11770" max="11770" width="6.725" style="3" customWidth="1"/>
-    <col min="11771" max="11771" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="11772" max="11772" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="11773" max="11773" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="11774" max="11774" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="11775" max="11775" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="11776" max="11776" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="11777" max="11777" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="11778" max="11778" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="11779" max="11779" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="11780" max="11780" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="11781" max="11781" width="8.45" style="3" customWidth="1"/>
-    <col min="11782" max="11782" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="11783" max="11783" width="7.725" style="3" customWidth="1"/>
-    <col min="11784" max="11784" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="11770" max="11770" width="6.6640625" style="3" customWidth="1"/>
+    <col min="11771" max="11771" width="7.83203125" style="3" customWidth="1"/>
+    <col min="11772" max="11772" width="7.1640625" style="3" customWidth="1"/>
+    <col min="11773" max="11773" width="7.6640625" style="3" customWidth="1"/>
+    <col min="11774" max="11775" width="5.33203125" style="3" customWidth="1"/>
+    <col min="11776" max="11776" width="5.1640625" style="3" customWidth="1"/>
+    <col min="11777" max="11777" width="7.33203125" style="3" customWidth="1"/>
+    <col min="11778" max="11778" width="4.1640625" style="3" customWidth="1"/>
+    <col min="11779" max="11779" width="6.33203125" style="3" customWidth="1"/>
+    <col min="11780" max="11780" width="7.6640625" style="3" customWidth="1"/>
+    <col min="11781" max="11781" width="8.5" style="3" customWidth="1"/>
+    <col min="11782" max="11782" width="8.33203125" style="3" customWidth="1"/>
+    <col min="11783" max="11783" width="7.6640625" style="3" customWidth="1"/>
+    <col min="11784" max="11784" width="6.83203125" style="3" customWidth="1"/>
     <col min="11785" max="12018" width="9" style="3"/>
-    <col min="12019" max="12019" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="12020" max="12020" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="12019" max="12019" width="6.33203125" style="3" customWidth="1"/>
+    <col min="12020" max="12020" width="7.33203125" style="3" customWidth="1"/>
     <col min="12021" max="12021" width="6" style="3" customWidth="1"/>
-    <col min="12022" max="12022" width="25.45" style="3" customWidth="1"/>
-    <col min="12023" max="12023" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="12024" max="12024" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="12022" max="12022" width="25.5" style="3" customWidth="1"/>
+    <col min="12023" max="12023" width="10.83203125" style="3" customWidth="1"/>
+    <col min="12024" max="12024" width="12.33203125" style="3" customWidth="1"/>
     <col min="12025" max="12025" width="11" style="3" customWidth="1"/>
-    <col min="12026" max="12026" width="6.725" style="3" customWidth="1"/>
-    <col min="12027" max="12027" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="12028" max="12028" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="12029" max="12029" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="12030" max="12030" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="12031" max="12031" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="12032" max="12032" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="12033" max="12033" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="12034" max="12034" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="12035" max="12035" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="12036" max="12036" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="12037" max="12037" width="8.45" style="3" customWidth="1"/>
-    <col min="12038" max="12038" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="12039" max="12039" width="7.725" style="3" customWidth="1"/>
-    <col min="12040" max="12040" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="12026" max="12026" width="6.6640625" style="3" customWidth="1"/>
+    <col min="12027" max="12027" width="7.83203125" style="3" customWidth="1"/>
+    <col min="12028" max="12028" width="7.1640625" style="3" customWidth="1"/>
+    <col min="12029" max="12029" width="7.6640625" style="3" customWidth="1"/>
+    <col min="12030" max="12031" width="5.33203125" style="3" customWidth="1"/>
+    <col min="12032" max="12032" width="5.1640625" style="3" customWidth="1"/>
+    <col min="12033" max="12033" width="7.33203125" style="3" customWidth="1"/>
+    <col min="12034" max="12034" width="4.1640625" style="3" customWidth="1"/>
+    <col min="12035" max="12035" width="6.33203125" style="3" customWidth="1"/>
+    <col min="12036" max="12036" width="7.6640625" style="3" customWidth="1"/>
+    <col min="12037" max="12037" width="8.5" style="3" customWidth="1"/>
+    <col min="12038" max="12038" width="8.33203125" style="3" customWidth="1"/>
+    <col min="12039" max="12039" width="7.6640625" style="3" customWidth="1"/>
+    <col min="12040" max="12040" width="6.83203125" style="3" customWidth="1"/>
     <col min="12041" max="12274" width="9" style="3"/>
-    <col min="12275" max="12275" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="12276" max="12276" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="12275" max="12275" width="6.33203125" style="3" customWidth="1"/>
+    <col min="12276" max="12276" width="7.33203125" style="3" customWidth="1"/>
     <col min="12277" max="12277" width="6" style="3" customWidth="1"/>
-    <col min="12278" max="12278" width="25.45" style="3" customWidth="1"/>
-    <col min="12279" max="12279" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="12280" max="12280" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="12278" max="12278" width="25.5" style="3" customWidth="1"/>
+    <col min="12279" max="12279" width="10.83203125" style="3" customWidth="1"/>
+    <col min="12280" max="12280" width="12.33203125" style="3" customWidth="1"/>
     <col min="12281" max="12281" width="11" style="3" customWidth="1"/>
-    <col min="12282" max="12282" width="6.725" style="3" customWidth="1"/>
-    <col min="12283" max="12283" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="12284" max="12284" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="12285" max="12285" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="12286" max="12286" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="12287" max="12287" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="12288" max="12288" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="12289" max="12289" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="12290" max="12290" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="12291" max="12291" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="12292" max="12292" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="12293" max="12293" width="8.45" style="3" customWidth="1"/>
-    <col min="12294" max="12294" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="12295" max="12295" width="7.725" style="3" customWidth="1"/>
-    <col min="12296" max="12296" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="12282" max="12282" width="6.6640625" style="3" customWidth="1"/>
+    <col min="12283" max="12283" width="7.83203125" style="3" customWidth="1"/>
+    <col min="12284" max="12284" width="7.1640625" style="3" customWidth="1"/>
+    <col min="12285" max="12285" width="7.6640625" style="3" customWidth="1"/>
+    <col min="12286" max="12287" width="5.33203125" style="3" customWidth="1"/>
+    <col min="12288" max="12288" width="5.1640625" style="3" customWidth="1"/>
+    <col min="12289" max="12289" width="7.33203125" style="3" customWidth="1"/>
+    <col min="12290" max="12290" width="4.1640625" style="3" customWidth="1"/>
+    <col min="12291" max="12291" width="6.33203125" style="3" customWidth="1"/>
+    <col min="12292" max="12292" width="7.6640625" style="3" customWidth="1"/>
+    <col min="12293" max="12293" width="8.5" style="3" customWidth="1"/>
+    <col min="12294" max="12294" width="8.33203125" style="3" customWidth="1"/>
+    <col min="12295" max="12295" width="7.6640625" style="3" customWidth="1"/>
+    <col min="12296" max="12296" width="6.83203125" style="3" customWidth="1"/>
     <col min="12297" max="12530" width="9" style="3"/>
-    <col min="12531" max="12531" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="12532" max="12532" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="12531" max="12531" width="6.33203125" style="3" customWidth="1"/>
+    <col min="12532" max="12532" width="7.33203125" style="3" customWidth="1"/>
     <col min="12533" max="12533" width="6" style="3" customWidth="1"/>
-    <col min="12534" max="12534" width="25.45" style="3" customWidth="1"/>
-    <col min="12535" max="12535" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="12536" max="12536" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="12534" max="12534" width="25.5" style="3" customWidth="1"/>
+    <col min="12535" max="12535" width="10.83203125" style="3" customWidth="1"/>
+    <col min="12536" max="12536" width="12.33203125" style="3" customWidth="1"/>
     <col min="12537" max="12537" width="11" style="3" customWidth="1"/>
-    <col min="12538" max="12538" width="6.725" style="3" customWidth="1"/>
-    <col min="12539" max="12539" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="12540" max="12540" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="12541" max="12541" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="12542" max="12542" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="12543" max="12543" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="12544" max="12544" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="12545" max="12545" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="12546" max="12546" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="12547" max="12547" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="12548" max="12548" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="12549" max="12549" width="8.45" style="3" customWidth="1"/>
-    <col min="12550" max="12550" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="12551" max="12551" width="7.725" style="3" customWidth="1"/>
-    <col min="12552" max="12552" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="12538" max="12538" width="6.6640625" style="3" customWidth="1"/>
+    <col min="12539" max="12539" width="7.83203125" style="3" customWidth="1"/>
+    <col min="12540" max="12540" width="7.1640625" style="3" customWidth="1"/>
+    <col min="12541" max="12541" width="7.6640625" style="3" customWidth="1"/>
+    <col min="12542" max="12543" width="5.33203125" style="3" customWidth="1"/>
+    <col min="12544" max="12544" width="5.1640625" style="3" customWidth="1"/>
+    <col min="12545" max="12545" width="7.33203125" style="3" customWidth="1"/>
+    <col min="12546" max="12546" width="4.1640625" style="3" customWidth="1"/>
+    <col min="12547" max="12547" width="6.33203125" style="3" customWidth="1"/>
+    <col min="12548" max="12548" width="7.6640625" style="3" customWidth="1"/>
+    <col min="12549" max="12549" width="8.5" style="3" customWidth="1"/>
+    <col min="12550" max="12550" width="8.33203125" style="3" customWidth="1"/>
+    <col min="12551" max="12551" width="7.6640625" style="3" customWidth="1"/>
+    <col min="12552" max="12552" width="6.83203125" style="3" customWidth="1"/>
     <col min="12553" max="12786" width="9" style="3"/>
-    <col min="12787" max="12787" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="12788" max="12788" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="12787" max="12787" width="6.33203125" style="3" customWidth="1"/>
+    <col min="12788" max="12788" width="7.33203125" style="3" customWidth="1"/>
     <col min="12789" max="12789" width="6" style="3" customWidth="1"/>
-    <col min="12790" max="12790" width="25.45" style="3" customWidth="1"/>
-    <col min="12791" max="12791" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="12792" max="12792" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="12790" max="12790" width="25.5" style="3" customWidth="1"/>
+    <col min="12791" max="12791" width="10.83203125" style="3" customWidth="1"/>
+    <col min="12792" max="12792" width="12.33203125" style="3" customWidth="1"/>
     <col min="12793" max="12793" width="11" style="3" customWidth="1"/>
-    <col min="12794" max="12794" width="6.725" style="3" customWidth="1"/>
-    <col min="12795" max="12795" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="12796" max="12796" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="12797" max="12797" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="12798" max="12798" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="12799" max="12799" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="12800" max="12800" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="12801" max="12801" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="12802" max="12802" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="12803" max="12803" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="12804" max="12804" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="12805" max="12805" width="8.45" style="3" customWidth="1"/>
-    <col min="12806" max="12806" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="12807" max="12807" width="7.725" style="3" customWidth="1"/>
-    <col min="12808" max="12808" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="12794" max="12794" width="6.6640625" style="3" customWidth="1"/>
+    <col min="12795" max="12795" width="7.83203125" style="3" customWidth="1"/>
+    <col min="12796" max="12796" width="7.1640625" style="3" customWidth="1"/>
+    <col min="12797" max="12797" width="7.6640625" style="3" customWidth="1"/>
+    <col min="12798" max="12799" width="5.33203125" style="3" customWidth="1"/>
+    <col min="12800" max="12800" width="5.1640625" style="3" customWidth="1"/>
+    <col min="12801" max="12801" width="7.33203125" style="3" customWidth="1"/>
+    <col min="12802" max="12802" width="4.1640625" style="3" customWidth="1"/>
+    <col min="12803" max="12803" width="6.33203125" style="3" customWidth="1"/>
+    <col min="12804" max="12804" width="7.6640625" style="3" customWidth="1"/>
+    <col min="12805" max="12805" width="8.5" style="3" customWidth="1"/>
+    <col min="12806" max="12806" width="8.33203125" style="3" customWidth="1"/>
+    <col min="12807" max="12807" width="7.6640625" style="3" customWidth="1"/>
+    <col min="12808" max="12808" width="6.83203125" style="3" customWidth="1"/>
     <col min="12809" max="13042" width="9" style="3"/>
-    <col min="13043" max="13043" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="13044" max="13044" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="13043" max="13043" width="6.33203125" style="3" customWidth="1"/>
+    <col min="13044" max="13044" width="7.33203125" style="3" customWidth="1"/>
     <col min="13045" max="13045" width="6" style="3" customWidth="1"/>
-    <col min="13046" max="13046" width="25.45" style="3" customWidth="1"/>
-    <col min="13047" max="13047" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="13048" max="13048" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="13046" max="13046" width="25.5" style="3" customWidth="1"/>
+    <col min="13047" max="13047" width="10.83203125" style="3" customWidth="1"/>
+    <col min="13048" max="13048" width="12.33203125" style="3" customWidth="1"/>
     <col min="13049" max="13049" width="11" style="3" customWidth="1"/>
-    <col min="13050" max="13050" width="6.725" style="3" customWidth="1"/>
-    <col min="13051" max="13051" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="13052" max="13052" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="13053" max="13053" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="13054" max="13054" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="13055" max="13055" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="13056" max="13056" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="13057" max="13057" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="13058" max="13058" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="13059" max="13059" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="13060" max="13060" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="13061" max="13061" width="8.45" style="3" customWidth="1"/>
-    <col min="13062" max="13062" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="13063" max="13063" width="7.725" style="3" customWidth="1"/>
-    <col min="13064" max="13064" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="13050" max="13050" width="6.6640625" style="3" customWidth="1"/>
+    <col min="13051" max="13051" width="7.83203125" style="3" customWidth="1"/>
+    <col min="13052" max="13052" width="7.1640625" style="3" customWidth="1"/>
+    <col min="13053" max="13053" width="7.6640625" style="3" customWidth="1"/>
+    <col min="13054" max="13055" width="5.33203125" style="3" customWidth="1"/>
+    <col min="13056" max="13056" width="5.1640625" style="3" customWidth="1"/>
+    <col min="13057" max="13057" width="7.33203125" style="3" customWidth="1"/>
+    <col min="13058" max="13058" width="4.1640625" style="3" customWidth="1"/>
+    <col min="13059" max="13059" width="6.33203125" style="3" customWidth="1"/>
+    <col min="13060" max="13060" width="7.6640625" style="3" customWidth="1"/>
+    <col min="13061" max="13061" width="8.5" style="3" customWidth="1"/>
+    <col min="13062" max="13062" width="8.33203125" style="3" customWidth="1"/>
+    <col min="13063" max="13063" width="7.6640625" style="3" customWidth="1"/>
+    <col min="13064" max="13064" width="6.83203125" style="3" customWidth="1"/>
     <col min="13065" max="13298" width="9" style="3"/>
-    <col min="13299" max="13299" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="13300" max="13300" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="13299" max="13299" width="6.33203125" style="3" customWidth="1"/>
+    <col min="13300" max="13300" width="7.33203125" style="3" customWidth="1"/>
     <col min="13301" max="13301" width="6" style="3" customWidth="1"/>
-    <col min="13302" max="13302" width="25.45" style="3" customWidth="1"/>
-    <col min="13303" max="13303" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="13304" max="13304" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="13302" max="13302" width="25.5" style="3" customWidth="1"/>
+    <col min="13303" max="13303" width="10.83203125" style="3" customWidth="1"/>
+    <col min="13304" max="13304" width="12.33203125" style="3" customWidth="1"/>
     <col min="13305" max="13305" width="11" style="3" customWidth="1"/>
-    <col min="13306" max="13306" width="6.725" style="3" customWidth="1"/>
-    <col min="13307" max="13307" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="13308" max="13308" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="13309" max="13309" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="13310" max="13310" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="13311" max="13311" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="13312" max="13312" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="13313" max="13313" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="13314" max="13314" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="13315" max="13315" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="13316" max="13316" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="13317" max="13317" width="8.45" style="3" customWidth="1"/>
-    <col min="13318" max="13318" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="13319" max="13319" width="7.725" style="3" customWidth="1"/>
-    <col min="13320" max="13320" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="13306" max="13306" width="6.6640625" style="3" customWidth="1"/>
+    <col min="13307" max="13307" width="7.83203125" style="3" customWidth="1"/>
+    <col min="13308" max="13308" width="7.1640625" style="3" customWidth="1"/>
+    <col min="13309" max="13309" width="7.6640625" style="3" customWidth="1"/>
+    <col min="13310" max="13311" width="5.33203125" style="3" customWidth="1"/>
+    <col min="13312" max="13312" width="5.1640625" style="3" customWidth="1"/>
+    <col min="13313" max="13313" width="7.33203125" style="3" customWidth="1"/>
+    <col min="13314" max="13314" width="4.1640625" style="3" customWidth="1"/>
+    <col min="13315" max="13315" width="6.33203125" style="3" customWidth="1"/>
+    <col min="13316" max="13316" width="7.6640625" style="3" customWidth="1"/>
+    <col min="13317" max="13317" width="8.5" style="3" customWidth="1"/>
+    <col min="13318" max="13318" width="8.33203125" style="3" customWidth="1"/>
+    <col min="13319" max="13319" width="7.6640625" style="3" customWidth="1"/>
+    <col min="13320" max="13320" width="6.83203125" style="3" customWidth="1"/>
     <col min="13321" max="13554" width="9" style="3"/>
-    <col min="13555" max="13555" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="13556" max="13556" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="13555" max="13555" width="6.33203125" style="3" customWidth="1"/>
+    <col min="13556" max="13556" width="7.33203125" style="3" customWidth="1"/>
     <col min="13557" max="13557" width="6" style="3" customWidth="1"/>
-    <col min="13558" max="13558" width="25.45" style="3" customWidth="1"/>
-    <col min="13559" max="13559" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="13560" max="13560" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="13558" max="13558" width="25.5" style="3" customWidth="1"/>
+    <col min="13559" max="13559" width="10.83203125" style="3" customWidth="1"/>
+    <col min="13560" max="13560" width="12.33203125" style="3" customWidth="1"/>
     <col min="13561" max="13561" width="11" style="3" customWidth="1"/>
-    <col min="13562" max="13562" width="6.725" style="3" customWidth="1"/>
-    <col min="13563" max="13563" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="13564" max="13564" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="13565" max="13565" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="13566" max="13566" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="13567" max="13567" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="13568" max="13568" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="13569" max="13569" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="13570" max="13570" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="13571" max="13571" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="13572" max="13572" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="13573" max="13573" width="8.45" style="3" customWidth="1"/>
-    <col min="13574" max="13574" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="13575" max="13575" width="7.725" style="3" customWidth="1"/>
-    <col min="13576" max="13576" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="13562" max="13562" width="6.6640625" style="3" customWidth="1"/>
+    <col min="13563" max="13563" width="7.83203125" style="3" customWidth="1"/>
+    <col min="13564" max="13564" width="7.1640625" style="3" customWidth="1"/>
+    <col min="13565" max="13565" width="7.6640625" style="3" customWidth="1"/>
+    <col min="13566" max="13567" width="5.33203125" style="3" customWidth="1"/>
+    <col min="13568" max="13568" width="5.1640625" style="3" customWidth="1"/>
+    <col min="13569" max="13569" width="7.33203125" style="3" customWidth="1"/>
+    <col min="13570" max="13570" width="4.1640625" style="3" customWidth="1"/>
+    <col min="13571" max="13571" width="6.33203125" style="3" customWidth="1"/>
+    <col min="13572" max="13572" width="7.6640625" style="3" customWidth="1"/>
+    <col min="13573" max="13573" width="8.5" style="3" customWidth="1"/>
+    <col min="13574" max="13574" width="8.33203125" style="3" customWidth="1"/>
+    <col min="13575" max="13575" width="7.6640625" style="3" customWidth="1"/>
+    <col min="13576" max="13576" width="6.83203125" style="3" customWidth="1"/>
     <col min="13577" max="13810" width="9" style="3"/>
-    <col min="13811" max="13811" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="13812" max="13812" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="13811" max="13811" width="6.33203125" style="3" customWidth="1"/>
+    <col min="13812" max="13812" width="7.33203125" style="3" customWidth="1"/>
     <col min="13813" max="13813" width="6" style="3" customWidth="1"/>
-    <col min="13814" max="13814" width="25.45" style="3" customWidth="1"/>
-    <col min="13815" max="13815" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="13816" max="13816" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="13814" max="13814" width="25.5" style="3" customWidth="1"/>
+    <col min="13815" max="13815" width="10.83203125" style="3" customWidth="1"/>
+    <col min="13816" max="13816" width="12.33203125" style="3" customWidth="1"/>
     <col min="13817" max="13817" width="11" style="3" customWidth="1"/>
-    <col min="13818" max="13818" width="6.725" style="3" customWidth="1"/>
-    <col min="13819" max="13819" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="13820" max="13820" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="13821" max="13821" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="13822" max="13822" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="13823" max="13823" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="13824" max="13824" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="13825" max="13825" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="13826" max="13826" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="13827" max="13827" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="13828" max="13828" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="13829" max="13829" width="8.45" style="3" customWidth="1"/>
-    <col min="13830" max="13830" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="13831" max="13831" width="7.725" style="3" customWidth="1"/>
-    <col min="13832" max="13832" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="13818" max="13818" width="6.6640625" style="3" customWidth="1"/>
+    <col min="13819" max="13819" width="7.83203125" style="3" customWidth="1"/>
+    <col min="13820" max="13820" width="7.1640625" style="3" customWidth="1"/>
+    <col min="13821" max="13821" width="7.6640625" style="3" customWidth="1"/>
+    <col min="13822" max="13823" width="5.33203125" style="3" customWidth="1"/>
+    <col min="13824" max="13824" width="5.1640625" style="3" customWidth="1"/>
+    <col min="13825" max="13825" width="7.33203125" style="3" customWidth="1"/>
+    <col min="13826" max="13826" width="4.1640625" style="3" customWidth="1"/>
+    <col min="13827" max="13827" width="6.33203125" style="3" customWidth="1"/>
+    <col min="13828" max="13828" width="7.6640625" style="3" customWidth="1"/>
+    <col min="13829" max="13829" width="8.5" style="3" customWidth="1"/>
+    <col min="13830" max="13830" width="8.33203125" style="3" customWidth="1"/>
+    <col min="13831" max="13831" width="7.6640625" style="3" customWidth="1"/>
+    <col min="13832" max="13832" width="6.83203125" style="3" customWidth="1"/>
     <col min="13833" max="14066" width="9" style="3"/>
-    <col min="14067" max="14067" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="14068" max="14068" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="14067" max="14067" width="6.33203125" style="3" customWidth="1"/>
+    <col min="14068" max="14068" width="7.33203125" style="3" customWidth="1"/>
     <col min="14069" max="14069" width="6" style="3" customWidth="1"/>
-    <col min="14070" max="14070" width="25.45" style="3" customWidth="1"/>
-    <col min="14071" max="14071" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="14072" max="14072" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="14070" max="14070" width="25.5" style="3" customWidth="1"/>
+    <col min="14071" max="14071" width="10.83203125" style="3" customWidth="1"/>
+    <col min="14072" max="14072" width="12.33203125" style="3" customWidth="1"/>
     <col min="14073" max="14073" width="11" style="3" customWidth="1"/>
-    <col min="14074" max="14074" width="6.725" style="3" customWidth="1"/>
-    <col min="14075" max="14075" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="14076" max="14076" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="14077" max="14077" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="14078" max="14078" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="14079" max="14079" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="14080" max="14080" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="14081" max="14081" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="14082" max="14082" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="14083" max="14083" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="14084" max="14084" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="14085" max="14085" width="8.45" style="3" customWidth="1"/>
-    <col min="14086" max="14086" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="14087" max="14087" width="7.725" style="3" customWidth="1"/>
-    <col min="14088" max="14088" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="14074" max="14074" width="6.6640625" style="3" customWidth="1"/>
+    <col min="14075" max="14075" width="7.83203125" style="3" customWidth="1"/>
+    <col min="14076" max="14076" width="7.1640625" style="3" customWidth="1"/>
+    <col min="14077" max="14077" width="7.6640625" style="3" customWidth="1"/>
+    <col min="14078" max="14079" width="5.33203125" style="3" customWidth="1"/>
+    <col min="14080" max="14080" width="5.1640625" style="3" customWidth="1"/>
+    <col min="14081" max="14081" width="7.33203125" style="3" customWidth="1"/>
+    <col min="14082" max="14082" width="4.1640625" style="3" customWidth="1"/>
+    <col min="14083" max="14083" width="6.33203125" style="3" customWidth="1"/>
+    <col min="14084" max="14084" width="7.6640625" style="3" customWidth="1"/>
+    <col min="14085" max="14085" width="8.5" style="3" customWidth="1"/>
+    <col min="14086" max="14086" width="8.33203125" style="3" customWidth="1"/>
+    <col min="14087" max="14087" width="7.6640625" style="3" customWidth="1"/>
+    <col min="14088" max="14088" width="6.83203125" style="3" customWidth="1"/>
     <col min="14089" max="14322" width="9" style="3"/>
-    <col min="14323" max="14323" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="14324" max="14324" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="14323" max="14323" width="6.33203125" style="3" customWidth="1"/>
+    <col min="14324" max="14324" width="7.33203125" style="3" customWidth="1"/>
     <col min="14325" max="14325" width="6" style="3" customWidth="1"/>
-    <col min="14326" max="14326" width="25.45" style="3" customWidth="1"/>
-    <col min="14327" max="14327" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="14328" max="14328" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="14326" max="14326" width="25.5" style="3" customWidth="1"/>
+    <col min="14327" max="14327" width="10.83203125" style="3" customWidth="1"/>
+    <col min="14328" max="14328" width="12.33203125" style="3" customWidth="1"/>
     <col min="14329" max="14329" width="11" style="3" customWidth="1"/>
-    <col min="14330" max="14330" width="6.725" style="3" customWidth="1"/>
-    <col min="14331" max="14331" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="14332" max="14332" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="14333" max="14333" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="14334" max="14334" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="14335" max="14335" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="14336" max="14336" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="14337" max="14337" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="14338" max="14338" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="14339" max="14339" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="14340" max="14340" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="14341" max="14341" width="8.45" style="3" customWidth="1"/>
-    <col min="14342" max="14342" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="14343" max="14343" width="7.725" style="3" customWidth="1"/>
-    <col min="14344" max="14344" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="14330" max="14330" width="6.6640625" style="3" customWidth="1"/>
+    <col min="14331" max="14331" width="7.83203125" style="3" customWidth="1"/>
+    <col min="14332" max="14332" width="7.1640625" style="3" customWidth="1"/>
+    <col min="14333" max="14333" width="7.6640625" style="3" customWidth="1"/>
+    <col min="14334" max="14335" width="5.33203125" style="3" customWidth="1"/>
+    <col min="14336" max="14336" width="5.1640625" style="3" customWidth="1"/>
+    <col min="14337" max="14337" width="7.33203125" style="3" customWidth="1"/>
+    <col min="14338" max="14338" width="4.1640625" style="3" customWidth="1"/>
+    <col min="14339" max="14339" width="6.33203125" style="3" customWidth="1"/>
+    <col min="14340" max="14340" width="7.6640625" style="3" customWidth="1"/>
+    <col min="14341" max="14341" width="8.5" style="3" customWidth="1"/>
+    <col min="14342" max="14342" width="8.33203125" style="3" customWidth="1"/>
+    <col min="14343" max="14343" width="7.6640625" style="3" customWidth="1"/>
+    <col min="14344" max="14344" width="6.83203125" style="3" customWidth="1"/>
     <col min="14345" max="14578" width="9" style="3"/>
-    <col min="14579" max="14579" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="14580" max="14580" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="14579" max="14579" width="6.33203125" style="3" customWidth="1"/>
+    <col min="14580" max="14580" width="7.33203125" style="3" customWidth="1"/>
     <col min="14581" max="14581" width="6" style="3" customWidth="1"/>
-    <col min="14582" max="14582" width="25.45" style="3" customWidth="1"/>
-    <col min="14583" max="14583" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="14584" max="14584" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="14582" max="14582" width="25.5" style="3" customWidth="1"/>
+    <col min="14583" max="14583" width="10.83203125" style="3" customWidth="1"/>
+    <col min="14584" max="14584" width="12.33203125" style="3" customWidth="1"/>
     <col min="14585" max="14585" width="11" style="3" customWidth="1"/>
-    <col min="14586" max="14586" width="6.725" style="3" customWidth="1"/>
-    <col min="14587" max="14587" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="14588" max="14588" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="14589" max="14589" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="14590" max="14590" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="14591" max="14591" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="14592" max="14592" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="14593" max="14593" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="14594" max="14594" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="14595" max="14595" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="14596" max="14596" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="14597" max="14597" width="8.45" style="3" customWidth="1"/>
-    <col min="14598" max="14598" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="14599" max="14599" width="7.725" style="3" customWidth="1"/>
-    <col min="14600" max="14600" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="14586" max="14586" width="6.6640625" style="3" customWidth="1"/>
+    <col min="14587" max="14587" width="7.83203125" style="3" customWidth="1"/>
+    <col min="14588" max="14588" width="7.1640625" style="3" customWidth="1"/>
+    <col min="14589" max="14589" width="7.6640625" style="3" customWidth="1"/>
+    <col min="14590" max="14591" width="5.33203125" style="3" customWidth="1"/>
+    <col min="14592" max="14592" width="5.1640625" style="3" customWidth="1"/>
+    <col min="14593" max="14593" width="7.33203125" style="3" customWidth="1"/>
+    <col min="14594" max="14594" width="4.1640625" style="3" customWidth="1"/>
+    <col min="14595" max="14595" width="6.33203125" style="3" customWidth="1"/>
+    <col min="14596" max="14596" width="7.6640625" style="3" customWidth="1"/>
+    <col min="14597" max="14597" width="8.5" style="3" customWidth="1"/>
+    <col min="14598" max="14598" width="8.33203125" style="3" customWidth="1"/>
+    <col min="14599" max="14599" width="7.6640625" style="3" customWidth="1"/>
+    <col min="14600" max="14600" width="6.83203125" style="3" customWidth="1"/>
     <col min="14601" max="14834" width="9" style="3"/>
-    <col min="14835" max="14835" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="14836" max="14836" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="14835" max="14835" width="6.33203125" style="3" customWidth="1"/>
+    <col min="14836" max="14836" width="7.33203125" style="3" customWidth="1"/>
     <col min="14837" max="14837" width="6" style="3" customWidth="1"/>
-    <col min="14838" max="14838" width="25.45" style="3" customWidth="1"/>
-    <col min="14839" max="14839" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="14840" max="14840" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="14838" max="14838" width="25.5" style="3" customWidth="1"/>
+    <col min="14839" max="14839" width="10.83203125" style="3" customWidth="1"/>
+    <col min="14840" max="14840" width="12.33203125" style="3" customWidth="1"/>
     <col min="14841" max="14841" width="11" style="3" customWidth="1"/>
-    <col min="14842" max="14842" width="6.725" style="3" customWidth="1"/>
-    <col min="14843" max="14843" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="14844" max="14844" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="14845" max="14845" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="14846" max="14846" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="14847" max="14847" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="14848" max="14848" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="14849" max="14849" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="14850" max="14850" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="14851" max="14851" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="14852" max="14852" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="14853" max="14853" width="8.45" style="3" customWidth="1"/>
-    <col min="14854" max="14854" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="14855" max="14855" width="7.725" style="3" customWidth="1"/>
-    <col min="14856" max="14856" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="14842" max="14842" width="6.6640625" style="3" customWidth="1"/>
+    <col min="14843" max="14843" width="7.83203125" style="3" customWidth="1"/>
+    <col min="14844" max="14844" width="7.1640625" style="3" customWidth="1"/>
+    <col min="14845" max="14845" width="7.6640625" style="3" customWidth="1"/>
+    <col min="14846" max="14847" width="5.33203125" style="3" customWidth="1"/>
+    <col min="14848" max="14848" width="5.1640625" style="3" customWidth="1"/>
+    <col min="14849" max="14849" width="7.33203125" style="3" customWidth="1"/>
+    <col min="14850" max="14850" width="4.1640625" style="3" customWidth="1"/>
+    <col min="14851" max="14851" width="6.33203125" style="3" customWidth="1"/>
+    <col min="14852" max="14852" width="7.6640625" style="3" customWidth="1"/>
+    <col min="14853" max="14853" width="8.5" style="3" customWidth="1"/>
+    <col min="14854" max="14854" width="8.33203125" style="3" customWidth="1"/>
+    <col min="14855" max="14855" width="7.6640625" style="3" customWidth="1"/>
+    <col min="14856" max="14856" width="6.83203125" style="3" customWidth="1"/>
     <col min="14857" max="15090" width="9" style="3"/>
-    <col min="15091" max="15091" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="15092" max="15092" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="15091" max="15091" width="6.33203125" style="3" customWidth="1"/>
+    <col min="15092" max="15092" width="7.33203125" style="3" customWidth="1"/>
     <col min="15093" max="15093" width="6" style="3" customWidth="1"/>
-    <col min="15094" max="15094" width="25.45" style="3" customWidth="1"/>
-    <col min="15095" max="15095" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="15096" max="15096" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="15094" max="15094" width="25.5" style="3" customWidth="1"/>
+    <col min="15095" max="15095" width="10.83203125" style="3" customWidth="1"/>
+    <col min="15096" max="15096" width="12.33203125" style="3" customWidth="1"/>
     <col min="15097" max="15097" width="11" style="3" customWidth="1"/>
-    <col min="15098" max="15098" width="6.725" style="3" customWidth="1"/>
-    <col min="15099" max="15099" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="15100" max="15100" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="15101" max="15101" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="15102" max="15102" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="15103" max="15103" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="15104" max="15104" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="15105" max="15105" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="15106" max="15106" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="15107" max="15107" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="15108" max="15108" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="15109" max="15109" width="8.45" style="3" customWidth="1"/>
-    <col min="15110" max="15110" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="15111" max="15111" width="7.725" style="3" customWidth="1"/>
-    <col min="15112" max="15112" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="15098" max="15098" width="6.6640625" style="3" customWidth="1"/>
+    <col min="15099" max="15099" width="7.83203125" style="3" customWidth="1"/>
+    <col min="15100" max="15100" width="7.1640625" style="3" customWidth="1"/>
+    <col min="15101" max="15101" width="7.6640625" style="3" customWidth="1"/>
+    <col min="15102" max="15103" width="5.33203125" style="3" customWidth="1"/>
+    <col min="15104" max="15104" width="5.1640625" style="3" customWidth="1"/>
+    <col min="15105" max="15105" width="7.33203125" style="3" customWidth="1"/>
+    <col min="15106" max="15106" width="4.1640625" style="3" customWidth="1"/>
+    <col min="15107" max="15107" width="6.33203125" style="3" customWidth="1"/>
+    <col min="15108" max="15108" width="7.6640625" style="3" customWidth="1"/>
+    <col min="15109" max="15109" width="8.5" style="3" customWidth="1"/>
+    <col min="15110" max="15110" width="8.33203125" style="3" customWidth="1"/>
+    <col min="15111" max="15111" width="7.6640625" style="3" customWidth="1"/>
+    <col min="15112" max="15112" width="6.83203125" style="3" customWidth="1"/>
     <col min="15113" max="15346" width="9" style="3"/>
-    <col min="15347" max="15347" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="15348" max="15348" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="15347" max="15347" width="6.33203125" style="3" customWidth="1"/>
+    <col min="15348" max="15348" width="7.33203125" style="3" customWidth="1"/>
     <col min="15349" max="15349" width="6" style="3" customWidth="1"/>
-    <col min="15350" max="15350" width="25.45" style="3" customWidth="1"/>
-    <col min="15351" max="15351" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="15352" max="15352" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="15350" max="15350" width="25.5" style="3" customWidth="1"/>
+    <col min="15351" max="15351" width="10.83203125" style="3" customWidth="1"/>
+    <col min="15352" max="15352" width="12.33203125" style="3" customWidth="1"/>
     <col min="15353" max="15353" width="11" style="3" customWidth="1"/>
-    <col min="15354" max="15354" width="6.725" style="3" customWidth="1"/>
-    <col min="15355" max="15355" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="15356" max="15356" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="15357" max="15357" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="15358" max="15358" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="15359" max="15359" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="15360" max="15360" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="15361" max="15361" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="15362" max="15362" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="15363" max="15363" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="15364" max="15364" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="15365" max="15365" width="8.45" style="3" customWidth="1"/>
-    <col min="15366" max="15366" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="15367" max="15367" width="7.725" style="3" customWidth="1"/>
-    <col min="15368" max="15368" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="15354" max="15354" width="6.6640625" style="3" customWidth="1"/>
+    <col min="15355" max="15355" width="7.83203125" style="3" customWidth="1"/>
+    <col min="15356" max="15356" width="7.1640625" style="3" customWidth="1"/>
+    <col min="15357" max="15357" width="7.6640625" style="3" customWidth="1"/>
+    <col min="15358" max="15359" width="5.33203125" style="3" customWidth="1"/>
+    <col min="15360" max="15360" width="5.1640625" style="3" customWidth="1"/>
+    <col min="15361" max="15361" width="7.33203125" style="3" customWidth="1"/>
+    <col min="15362" max="15362" width="4.1640625" style="3" customWidth="1"/>
+    <col min="15363" max="15363" width="6.33203125" style="3" customWidth="1"/>
+    <col min="15364" max="15364" width="7.6640625" style="3" customWidth="1"/>
+    <col min="15365" max="15365" width="8.5" style="3" customWidth="1"/>
+    <col min="15366" max="15366" width="8.33203125" style="3" customWidth="1"/>
+    <col min="15367" max="15367" width="7.6640625" style="3" customWidth="1"/>
+    <col min="15368" max="15368" width="6.83203125" style="3" customWidth="1"/>
     <col min="15369" max="15602" width="9" style="3"/>
-    <col min="15603" max="15603" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="15604" max="15604" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="15603" max="15603" width="6.33203125" style="3" customWidth="1"/>
+    <col min="15604" max="15604" width="7.33203125" style="3" customWidth="1"/>
     <col min="15605" max="15605" width="6" style="3" customWidth="1"/>
-    <col min="15606" max="15606" width="25.45" style="3" customWidth="1"/>
-    <col min="15607" max="15607" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="15608" max="15608" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="15606" max="15606" width="25.5" style="3" customWidth="1"/>
+    <col min="15607" max="15607" width="10.83203125" style="3" customWidth="1"/>
+    <col min="15608" max="15608" width="12.33203125" style="3" customWidth="1"/>
     <col min="15609" max="15609" width="11" style="3" customWidth="1"/>
-    <col min="15610" max="15610" width="6.725" style="3" customWidth="1"/>
-    <col min="15611" max="15611" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="15612" max="15612" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="15613" max="15613" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="15614" max="15614" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="15615" max="15615" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="15616" max="15616" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="15617" max="15617" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="15618" max="15618" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="15619" max="15619" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="15620" max="15620" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="15621" max="15621" width="8.45" style="3" customWidth="1"/>
-    <col min="15622" max="15622" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="15623" max="15623" width="7.725" style="3" customWidth="1"/>
-    <col min="15624" max="15624" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="15610" max="15610" width="6.6640625" style="3" customWidth="1"/>
+    <col min="15611" max="15611" width="7.83203125" style="3" customWidth="1"/>
+    <col min="15612" max="15612" width="7.1640625" style="3" customWidth="1"/>
+    <col min="15613" max="15613" width="7.6640625" style="3" customWidth="1"/>
+    <col min="15614" max="15615" width="5.33203125" style="3" customWidth="1"/>
+    <col min="15616" max="15616" width="5.1640625" style="3" customWidth="1"/>
+    <col min="15617" max="15617" width="7.33203125" style="3" customWidth="1"/>
+    <col min="15618" max="15618" width="4.1640625" style="3" customWidth="1"/>
+    <col min="15619" max="15619" width="6.33203125" style="3" customWidth="1"/>
+    <col min="15620" max="15620" width="7.6640625" style="3" customWidth="1"/>
+    <col min="15621" max="15621" width="8.5" style="3" customWidth="1"/>
+    <col min="15622" max="15622" width="8.33203125" style="3" customWidth="1"/>
+    <col min="15623" max="15623" width="7.6640625" style="3" customWidth="1"/>
+    <col min="15624" max="15624" width="6.83203125" style="3" customWidth="1"/>
     <col min="15625" max="15858" width="9" style="3"/>
-    <col min="15859" max="15859" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="15860" max="15860" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="15859" max="15859" width="6.33203125" style="3" customWidth="1"/>
+    <col min="15860" max="15860" width="7.33203125" style="3" customWidth="1"/>
     <col min="15861" max="15861" width="6" style="3" customWidth="1"/>
-    <col min="15862" max="15862" width="25.45" style="3" customWidth="1"/>
-    <col min="15863" max="15863" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="15864" max="15864" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="15862" max="15862" width="25.5" style="3" customWidth="1"/>
+    <col min="15863" max="15863" width="10.83203125" style="3" customWidth="1"/>
+    <col min="15864" max="15864" width="12.33203125" style="3" customWidth="1"/>
     <col min="15865" max="15865" width="11" style="3" customWidth="1"/>
-    <col min="15866" max="15866" width="6.725" style="3" customWidth="1"/>
-    <col min="15867" max="15867" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="15868" max="15868" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="15869" max="15869" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="15870" max="15870" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="15871" max="15871" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="15872" max="15872" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="15873" max="15873" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="15874" max="15874" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="15875" max="15875" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="15876" max="15876" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="15877" max="15877" width="8.45" style="3" customWidth="1"/>
-    <col min="15878" max="15878" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="15879" max="15879" width="7.725" style="3" customWidth="1"/>
-    <col min="15880" max="15880" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="15866" max="15866" width="6.6640625" style="3" customWidth="1"/>
+    <col min="15867" max="15867" width="7.83203125" style="3" customWidth="1"/>
+    <col min="15868" max="15868" width="7.1640625" style="3" customWidth="1"/>
+    <col min="15869" max="15869" width="7.6640625" style="3" customWidth="1"/>
+    <col min="15870" max="15871" width="5.33203125" style="3" customWidth="1"/>
+    <col min="15872" max="15872" width="5.1640625" style="3" customWidth="1"/>
+    <col min="15873" max="15873" width="7.33203125" style="3" customWidth="1"/>
+    <col min="15874" max="15874" width="4.1640625" style="3" customWidth="1"/>
+    <col min="15875" max="15875" width="6.33203125" style="3" customWidth="1"/>
+    <col min="15876" max="15876" width="7.6640625" style="3" customWidth="1"/>
+    <col min="15877" max="15877" width="8.5" style="3" customWidth="1"/>
+    <col min="15878" max="15878" width="8.33203125" style="3" customWidth="1"/>
+    <col min="15879" max="15879" width="7.6640625" style="3" customWidth="1"/>
+    <col min="15880" max="15880" width="6.83203125" style="3" customWidth="1"/>
     <col min="15881" max="16114" width="9" style="3"/>
-    <col min="16115" max="16115" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="16116" max="16116" width="7.36666666666667" style="3" customWidth="1"/>
+    <col min="16115" max="16115" width="6.33203125" style="3" customWidth="1"/>
+    <col min="16116" max="16116" width="7.33203125" style="3" customWidth="1"/>
     <col min="16117" max="16117" width="6" style="3" customWidth="1"/>
-    <col min="16118" max="16118" width="25.45" style="3" customWidth="1"/>
-    <col min="16119" max="16119" width="10.9083333333333" style="3" customWidth="1"/>
-    <col min="16120" max="16120" width="12.3666666666667" style="3" customWidth="1"/>
+    <col min="16118" max="16118" width="25.5" style="3" customWidth="1"/>
+    <col min="16119" max="16119" width="10.83203125" style="3" customWidth="1"/>
+    <col min="16120" max="16120" width="12.33203125" style="3" customWidth="1"/>
     <col min="16121" max="16121" width="11" style="3" customWidth="1"/>
-    <col min="16122" max="16122" width="6.725" style="3" customWidth="1"/>
-    <col min="16123" max="16123" width="7.90833333333333" style="3" customWidth="1"/>
-    <col min="16124" max="16124" width="7.09166666666667" style="3" customWidth="1"/>
-    <col min="16125" max="16125" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="16126" max="16126" width="5.36666666666667" style="3" customWidth="1"/>
-    <col min="16127" max="16127" width="5.26666666666667" style="3" customWidth="1"/>
-    <col min="16128" max="16128" width="5.09166666666667" style="3" customWidth="1"/>
-    <col min="16129" max="16129" width="7.26666666666667" style="3" customWidth="1"/>
-    <col min="16130" max="16130" width="4.09166666666667" style="3" customWidth="1"/>
-    <col min="16131" max="16131" width="6.26666666666667" style="3" customWidth="1"/>
-    <col min="16132" max="16132" width="7.63333333333333" style="3" customWidth="1"/>
-    <col min="16133" max="16133" width="8.45" style="3" customWidth="1"/>
-    <col min="16134" max="16134" width="8.26666666666667" style="3" customWidth="1"/>
-    <col min="16135" max="16135" width="7.725" style="3" customWidth="1"/>
-    <col min="16136" max="16136" width="6.90833333333333" style="3" customWidth="1"/>
+    <col min="16122" max="16122" width="6.6640625" style="3" customWidth="1"/>
+    <col min="16123" max="16123" width="7.83203125" style="3" customWidth="1"/>
+    <col min="16124" max="16124" width="7.1640625" style="3" customWidth="1"/>
+    <col min="16125" max="16125" width="7.6640625" style="3" customWidth="1"/>
+    <col min="16126" max="16127" width="5.33203125" style="3" customWidth="1"/>
+    <col min="16128" max="16128" width="5.1640625" style="3" customWidth="1"/>
+    <col min="16129" max="16129" width="7.33203125" style="3" customWidth="1"/>
+    <col min="16130" max="16130" width="4.1640625" style="3" customWidth="1"/>
+    <col min="16131" max="16131" width="6.33203125" style="3" customWidth="1"/>
+    <col min="16132" max="16132" width="7.6640625" style="3" customWidth="1"/>
+    <col min="16133" max="16133" width="8.5" style="3" customWidth="1"/>
+    <col min="16134" max="16134" width="8.33203125" style="3" customWidth="1"/>
+    <col min="16135" max="16135" width="7.6640625" style="3" customWidth="1"/>
+    <col min="16136" max="16136" width="6.83203125" style="3" customWidth="1"/>
     <col min="16137" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" spans="1:19">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:19" ht="26">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37"/>
+      <c r="S1" s="37"/>
     </row>
-    <row r="2" s="1" customFormat="1" ht="12.75" spans="1:19">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:19" s="1" customFormat="1" ht="14">
+      <c r="A2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="7" t="s">
+      <c r="B2" s="39"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="7" t="s">
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="12" spans="1:19">
-      <c r="A3" s="10" t="s">
+    <row r="3" spans="1:19" s="1" customFormat="1" ht="14">
+      <c r="A3" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="42"/>
+      <c r="C3" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="13" t="s">
+      <c r="D3" s="43"/>
+      <c r="E3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="15" t="s">
+      <c r="H3" s="42"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="12"/>
-      <c r="O3" s="15" t="s">
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="11"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="17"/>
+      <c r="P3" s="42"/>
+      <c r="Q3" s="42"/>
+      <c r="R3" s="42"/>
+      <c r="S3" s="45"/>
     </row>
-    <row r="4" ht="14.25" spans="1:19">
-      <c r="A4" s="18" t="s">
+    <row r="4" spans="1:19">
+      <c r="A4" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="22"/>
-      <c r="O4" s="21"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
-      <c r="S4" s="26"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="49"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="51"/>
+      <c r="N4" s="50"/>
+      <c r="O4" s="49"/>
+      <c r="P4" s="51"/>
+      <c r="Q4" s="51"/>
+      <c r="R4" s="51"/>
+      <c r="S4" s="53"/>
     </row>
-    <row r="5" s="1" customFormat="1" ht="12" spans="1:19">
-      <c r="A5" s="27" t="s">
+    <row r="5" spans="1:19" s="1" customFormat="1" ht="14">
+      <c r="A5" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="28"/>
-      <c r="C5" s="29" t="s">
+      <c r="B5" s="55"/>
+      <c r="C5" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="31" t="s">
+      <c r="D5" s="12"/>
+      <c r="E5" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="F5" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="33" t="s">
+      <c r="G5" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="34"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="30"/>
-      <c r="K5" s="31" t="s">
+      <c r="H5" s="57"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="L5" s="34"/>
-      <c r="M5" s="34"/>
-      <c r="N5" s="30"/>
-      <c r="O5" s="33"/>
-      <c r="P5" s="34"/>
-      <c r="Q5" s="34"/>
-      <c r="R5" s="34"/>
-      <c r="S5" s="36"/>
+      <c r="L5" s="57"/>
+      <c r="M5" s="57"/>
+      <c r="N5" s="59"/>
+      <c r="O5" s="56"/>
+      <c r="P5" s="57"/>
+      <c r="Q5" s="57"/>
+      <c r="R5" s="57"/>
+      <c r="S5" s="60"/>
     </row>
     <row r="6" spans="1:19">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="21" t="s">
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="22"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="21"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="22"/>
-      <c r="O6" s="21"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
-      <c r="S6" s="26"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="50"/>
+      <c r="K6" s="49"/>
+      <c r="L6" s="51"/>
+      <c r="M6" s="51"/>
+      <c r="N6" s="50"/>
+      <c r="O6" s="49"/>
+      <c r="P6" s="51"/>
+      <c r="Q6" s="51"/>
+      <c r="R6" s="51"/>
+      <c r="S6" s="53"/>
     </row>
-    <row r="7" s="1" customFormat="1" ht="12" spans="1:19">
-      <c r="A7" s="40" t="s">
+    <row r="7" spans="1:19" s="1" customFormat="1" ht="14">
+      <c r="A7" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="34"/>
-      <c r="C7" s="34" t="s">
+      <c r="B7" s="57"/>
+      <c r="C7" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="30"/>
-      <c r="E7" s="31" t="s">
+      <c r="D7" s="59"/>
+      <c r="E7" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="32" t="s">
+      <c r="F7" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="31" t="s">
+      <c r="G7" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="34" t="s">
+      <c r="H7" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="35"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="31" t="s">
+      <c r="I7" s="58"/>
+      <c r="J7" s="59"/>
+      <c r="K7" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="L7" s="34"/>
-      <c r="M7" s="34"/>
-      <c r="N7" s="30"/>
-      <c r="O7" s="31"/>
-      <c r="P7" s="34"/>
-      <c r="Q7" s="34"/>
-      <c r="R7" s="34"/>
-      <c r="S7" s="36"/>
+      <c r="L7" s="57"/>
+      <c r="M7" s="57"/>
+      <c r="N7" s="59"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="57"/>
+      <c r="Q7" s="57"/>
+      <c r="R7" s="57"/>
+      <c r="S7" s="60"/>
     </row>
-    <row r="8" ht="14.25" spans="1:19">
-      <c r="A8" s="18" t="s">
+    <row r="8" spans="1:19">
+      <c r="A8" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="41" t="s">
+      <c r="B8" s="47"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="20"/>
-      <c r="G8" s="41" t="s">
+      <c r="F8" s="48"/>
+      <c r="G8" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="19"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="21"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="22"/>
-      <c r="O8" s="21"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
-      <c r="S8" s="26"/>
+      <c r="H8" s="47"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="49"/>
+      <c r="L8" s="51"/>
+      <c r="M8" s="51"/>
+      <c r="N8" s="50"/>
+      <c r="O8" s="49"/>
+      <c r="P8" s="51"/>
+      <c r="Q8" s="51"/>
+      <c r="R8" s="51"/>
+      <c r="S8" s="53"/>
     </row>
-    <row r="9" s="1" customFormat="1" ht="12" spans="1:19">
-      <c r="A9" s="40" t="s">
+    <row r="9" spans="1:19" s="1" customFormat="1" ht="14">
+      <c r="A9" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="31" t="s">
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="32" t="s">
+      <c r="F9" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="G9" s="31" t="s">
+      <c r="G9" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="34" t="s">
+      <c r="H9" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="35"/>
-      <c r="J9" s="34"/>
-      <c r="K9" s="31" t="s">
+      <c r="I9" s="58"/>
+      <c r="J9" s="57"/>
+      <c r="K9" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="L9" s="34" t="s">
+      <c r="L9" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="M9" s="34"/>
-      <c r="N9" s="30"/>
-      <c r="O9" s="43" t="s">
+      <c r="M9" s="57"/>
+      <c r="N9" s="59"/>
+      <c r="O9" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="P9" s="34" t="s">
+      <c r="P9" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="Q9" s="34"/>
-      <c r="R9" s="34"/>
-      <c r="S9" s="36"/>
+      <c r="Q9" s="57"/>
+      <c r="R9" s="57"/>
+      <c r="S9" s="60"/>
     </row>
-    <row r="10" ht="14.25" spans="1:19">
-      <c r="A10" s="18" t="str">
+    <row r="10" spans="1:19">
+      <c r="A10" s="46" t="str">
         <f>[1]IV!$F$2</f>
         <v>PO2603230466</v>
       </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="44" t="s">
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="45"/>
-      <c r="G10" s="21" t="s">
+      <c r="F10" s="68"/>
+      <c r="G10" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="H10" s="23"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="23"/>
-      <c r="K10" s="21" t="s">
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="L10" s="23"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="22"/>
-      <c r="O10" s="21"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
-      <c r="S10" s="26"/>
+      <c r="L10" s="51"/>
+      <c r="M10" s="51"/>
+      <c r="N10" s="50"/>
+      <c r="O10" s="49"/>
+      <c r="P10" s="51"/>
+      <c r="Q10" s="51"/>
+      <c r="R10" s="51"/>
+      <c r="S10" s="53"/>
     </row>
-    <row r="11" s="1" customFormat="1" ht="12" spans="1:19">
-      <c r="A11" s="40" t="s">
+    <row r="11" spans="1:19" s="1" customFormat="1" ht="14">
+      <c r="A11" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="34"/>
-      <c r="C11" s="34" t="s">
+      <c r="B11" s="57"/>
+      <c r="C11" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="30"/>
-      <c r="E11" s="46" t="s">
+      <c r="D11" s="59"/>
+      <c r="E11" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="47" t="s">
+      <c r="F11" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="G11" s="33" t="s">
+      <c r="G11" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="H11" s="30"/>
-      <c r="I11" s="48" t="s">
+      <c r="H11" s="59"/>
+      <c r="I11" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="J11" s="29" t="s">
+      <c r="J11" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="K11" s="31" t="s">
+      <c r="K11" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="L11" s="34"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="29" t="s">
+      <c r="L11" s="57"/>
+      <c r="M11" s="59"/>
+      <c r="N11" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="O11" s="34"/>
-      <c r="P11" s="30"/>
-      <c r="Q11" s="31" t="s">
+      <c r="O11" s="57"/>
+      <c r="P11" s="59"/>
+      <c r="Q11" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="R11" s="49"/>
-      <c r="S11" s="50"/>
+      <c r="R11" s="69"/>
+      <c r="S11" s="70"/>
     </row>
-    <row r="12" ht="14.25" spans="1:19">
-      <c r="A12" s="18" t="s">
+    <row r="12" spans="1:19">
+      <c r="A12" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="51">
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="19">
         <f>[1]PL!$F$15</f>
         <v>43</v>
       </c>
-      <c r="F12" s="51">
+      <c r="F12" s="19">
         <f>[1]PL!$H$15</f>
         <v>944.8</v>
       </c>
-      <c r="G12" s="41">
+      <c r="G12" s="65">
         <f>[1]PL!$G$15</f>
         <v>761.4</v>
       </c>
-      <c r="H12" s="20"/>
-      <c r="I12" s="41" t="s">
+      <c r="H12" s="48"/>
+      <c r="I12" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="J12" s="19"/>
-      <c r="K12" s="52" t="s">
+      <c r="J12" s="47"/>
+      <c r="K12" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="L12" s="53">
+      <c r="L12" s="71">
         <f>[2]sheet!$O$16/5.5</f>
-        <v>1771.40727272727</v>
+        <v>1771.4072727272701</v>
       </c>
-      <c r="M12" s="54"/>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="20"/>
-      <c r="Q12" s="41"/>
-      <c r="R12" s="19"/>
-      <c r="S12" s="55"/>
+      <c r="M12" s="72"/>
+      <c r="N12" s="47"/>
+      <c r="O12" s="47"/>
+      <c r="P12" s="48"/>
+      <c r="Q12" s="65"/>
+      <c r="R12" s="47"/>
+      <c r="S12" s="73"/>
     </row>
-    <row r="13" s="1" customFormat="1" ht="12" spans="1:19">
-      <c r="A13" s="56" t="s">
+    <row r="13" spans="1:19" s="1" customFormat="1" ht="14">
+      <c r="A13" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="57"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="58"/>
-      <c r="I13" s="58"/>
-      <c r="J13" s="58"/>
-      <c r="K13" s="58"/>
-      <c r="L13" s="58"/>
-      <c r="M13" s="58"/>
-      <c r="N13" s="58"/>
-      <c r="O13" s="58"/>
-      <c r="P13" s="58"/>
-      <c r="Q13" s="58"/>
-      <c r="R13" s="58"/>
-      <c r="S13" s="59"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="74"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="74"/>
+      <c r="J13" s="74"/>
+      <c r="K13" s="74"/>
+      <c r="L13" s="74"/>
+      <c r="M13" s="74"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="74"/>
+      <c r="P13" s="74"/>
+      <c r="Q13" s="74"/>
+      <c r="R13" s="74"/>
+      <c r="S13" s="75"/>
     </row>
-    <row r="14" s="1" customFormat="1" ht="12.75" spans="1:19">
-      <c r="A14" s="60"/>
-      <c r="B14" s="61"/>
-      <c r="C14" s="61"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="62"/>
-      <c r="J14" s="62"/>
-      <c r="K14" s="62"/>
-      <c r="L14" s="62"/>
-      <c r="M14" s="62"/>
-      <c r="N14" s="62"/>
-      <c r="O14" s="62"/>
-      <c r="P14" s="62"/>
-      <c r="Q14" s="62"/>
-      <c r="R14" s="62"/>
-      <c r="S14" s="63"/>
+    <row r="14" spans="1:19" s="1" customFormat="1" ht="14">
+      <c r="A14" s="76"/>
+      <c r="B14" s="77"/>
+      <c r="C14" s="77"/>
+      <c r="D14" s="78"/>
+      <c r="E14" s="78"/>
+      <c r="F14" s="78"/>
+      <c r="G14" s="78"/>
+      <c r="H14" s="78"/>
+      <c r="I14" s="78"/>
+      <c r="J14" s="78"/>
+      <c r="K14" s="78"/>
+      <c r="L14" s="78"/>
+      <c r="M14" s="78"/>
+      <c r="N14" s="78"/>
+      <c r="O14" s="78"/>
+      <c r="P14" s="78"/>
+      <c r="Q14" s="78"/>
+      <c r="R14" s="78"/>
+      <c r="S14" s="79"/>
     </row>
-    <row r="15" s="1" customFormat="1" ht="12" spans="1:19">
-      <c r="A15" s="64" t="s">
+    <row r="15" spans="1:19" s="1" customFormat="1" ht="14">
+      <c r="A15" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="65"/>
-      <c r="D15" s="65"/>
-      <c r="E15" s="65"/>
-      <c r="F15" s="65"/>
-      <c r="G15" s="65"/>
-      <c r="H15" s="65"/>
-      <c r="I15" s="65"/>
-      <c r="J15" s="65"/>
-      <c r="K15" s="65"/>
-      <c r="L15" s="65"/>
-      <c r="M15" s="65"/>
-      <c r="N15" s="65"/>
-      <c r="O15" s="65"/>
-      <c r="P15" s="65"/>
-      <c r="Q15" s="65"/>
-      <c r="R15" s="65"/>
-      <c r="S15" s="66"/>
+      <c r="C15" s="80"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="80"/>
+      <c r="G15" s="80"/>
+      <c r="H15" s="80"/>
+      <c r="I15" s="80"/>
+      <c r="J15" s="80"/>
+      <c r="K15" s="80"/>
+      <c r="L15" s="80"/>
+      <c r="M15" s="80"/>
+      <c r="N15" s="80"/>
+      <c r="O15" s="80"/>
+      <c r="P15" s="80"/>
+      <c r="Q15" s="80"/>
+      <c r="R15" s="80"/>
+      <c r="S15" s="81"/>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="64" t="s">
+      <c r="A16" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="67"/>
-      <c r="C16" s="67"/>
-      <c r="D16" s="67"/>
-      <c r="E16" s="67"/>
-      <c r="F16" s="67"/>
-      <c r="G16" s="67"/>
-      <c r="H16" s="67"/>
-      <c r="I16" s="67"/>
-      <c r="J16" s="67"/>
-      <c r="K16" s="67"/>
-      <c r="L16" s="67"/>
-      <c r="M16" s="67"/>
-      <c r="N16" s="67"/>
-      <c r="O16" s="67"/>
-      <c r="P16" s="67"/>
-      <c r="Q16" s="67"/>
-      <c r="R16" s="67"/>
-      <c r="S16" s="68"/>
+      <c r="B16" s="82"/>
+      <c r="C16" s="82"/>
+      <c r="D16" s="82"/>
+      <c r="E16" s="82"/>
+      <c r="F16" s="82"/>
+      <c r="G16" s="82"/>
+      <c r="H16" s="82"/>
+      <c r="I16" s="82"/>
+      <c r="J16" s="82"/>
+      <c r="K16" s="82"/>
+      <c r="L16" s="82"/>
+      <c r="M16" s="82"/>
+      <c r="N16" s="82"/>
+      <c r="O16" s="82"/>
+      <c r="P16" s="82"/>
+      <c r="Q16" s="82"/>
+      <c r="R16" s="82"/>
+      <c r="S16" s="83"/>
     </row>
-    <row r="17" ht="14.25" spans="1:1024 1025:16370">
-      <c r="A17" s="69"/>
-      <c r="B17" s="67"/>
-      <c r="C17" s="67"/>
-      <c r="D17" s="67"/>
-      <c r="E17" s="67"/>
-      <c r="F17" s="67"/>
-      <c r="G17" s="67"/>
-      <c r="H17" s="67"/>
-      <c r="I17" s="67"/>
-      <c r="J17" s="67"/>
-      <c r="K17" s="67"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="65"/>
-      <c r="P17" s="65"/>
-      <c r="Q17" s="65"/>
-      <c r="R17" s="65"/>
-      <c r="S17" s="66"/>
+    <row r="17" spans="1:16370">
+      <c r="A17" s="84"/>
+      <c r="B17" s="82"/>
+      <c r="C17" s="82"/>
+      <c r="D17" s="82"/>
+      <c r="E17" s="82"/>
+      <c r="F17" s="82"/>
+      <c r="G17" s="82"/>
+      <c r="H17" s="82"/>
+      <c r="I17" s="82"/>
+      <c r="J17" s="82"/>
+      <c r="K17" s="82"/>
+      <c r="L17" s="85"/>
+      <c r="M17" s="85"/>
+      <c r="N17" s="85"/>
+      <c r="O17" s="80"/>
+      <c r="P17" s="80"/>
+      <c r="Q17" s="80"/>
+      <c r="R17" s="80"/>
+      <c r="S17" s="81"/>
     </row>
-    <row r="18" s="2" customFormat="1" ht="14.25" spans="1:1024 1025:16370">
-      <c r="A18" s="70" t="s">
+    <row r="18" spans="1:16370" s="2" customFormat="1" ht="14">
+      <c r="A18" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="71" t="s">
+      <c r="B18" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="72"/>
-      <c r="D18" s="73" t="s">
+      <c r="C18" s="26"/>
+      <c r="D18" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="E18" s="72"/>
-      <c r="F18" s="74" t="s">
+      <c r="E18" s="26"/>
+      <c r="F18" s="86" t="s">
         <v>13</v>
       </c>
-      <c r="G18" s="74"/>
-      <c r="H18" s="72"/>
-      <c r="I18" s="73" t="s">
+      <c r="G18" s="86"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="J18" s="74"/>
-      <c r="K18" s="75" t="s">
+      <c r="J18" s="86"/>
+      <c r="K18" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="L18" s="76" t="s">
+      <c r="L18" s="88" t="s">
         <v>13</v>
       </c>
-      <c r="M18" s="76"/>
-      <c r="N18" s="76"/>
-      <c r="O18" s="76"/>
-      <c r="P18" s="76"/>
-      <c r="Q18" s="76"/>
-      <c r="R18" s="76"/>
-      <c r="S18" s="77"/>
+      <c r="M18" s="88"/>
+      <c r="N18" s="88"/>
+      <c r="O18" s="88"/>
+      <c r="P18" s="88"/>
+      <c r="Q18" s="88"/>
+      <c r="R18" s="88"/>
+      <c r="S18" s="89"/>
     </row>
-    <row r="19" s="1" customFormat="1" ht="12" spans="1:1024 1025:16370">
-      <c r="A19" s="78" t="s">
+    <row r="19" spans="1:16370" s="1" customFormat="1" ht="14">
+      <c r="A19" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="79" t="s">
+      <c r="B19" s="90" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="79"/>
-      <c r="D19" s="80" t="s">
+      <c r="C19" s="90"/>
+      <c r="D19" s="91" t="s">
         <v>50</v>
       </c>
-      <c r="E19" s="80"/>
-      <c r="F19" s="80"/>
-      <c r="G19" s="80" t="s">
+      <c r="E19" s="91"/>
+      <c r="F19" s="91"/>
+      <c r="G19" s="91" t="s">
         <v>51</v>
       </c>
-      <c r="H19" s="80"/>
-      <c r="I19" s="79" t="s">
+      <c r="H19" s="91"/>
+      <c r="I19" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="J19" s="79"/>
-      <c r="K19" s="80" t="s">
+      <c r="J19" s="90"/>
+      <c r="K19" s="91" t="s">
         <v>53</v>
       </c>
-      <c r="L19" s="80"/>
-      <c r="M19" s="80" t="s">
+      <c r="L19" s="91"/>
+      <c r="M19" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="N19" s="80"/>
-      <c r="O19" s="80"/>
-      <c r="P19" s="79" t="s">
+      <c r="N19" s="91"/>
+      <c r="O19" s="91"/>
+      <c r="P19" s="90" t="s">
         <v>55</v>
       </c>
-      <c r="Q19" s="79"/>
-      <c r="R19" s="79"/>
-      <c r="S19" s="81" t="s">
+      <c r="Q19" s="90"/>
+      <c r="R19" s="90"/>
+      <c r="S19" s="30" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="14.25" spans="1:1024 1025:16370">
-      <c r="A20" s="82">
+    <row r="20" spans="1:16370" s="1" customFormat="1">
+      <c r="A20" s="31">
         <v>1</v>
       </c>
-      <c r="B20" s="83">
+      <c r="B20" s="92">
         <f>[1]PL!$B$9</f>
         <v>3918909000</v>
       </c>
-      <c r="C20" s="83"/>
-      <c r="D20" s="83" t="s">
+      <c r="C20" s="92"/>
+      <c r="D20" s="92" t="s">
         <v>57</v>
       </c>
-      <c r="E20" s="83"/>
-      <c r="F20" s="83"/>
-      <c r="G20" s="84">
+      <c r="E20" s="92"/>
+      <c r="F20" s="92"/>
+      <c r="G20" s="32">
         <f>[1]IV!$D$9</f>
         <v>125</v>
       </c>
-      <c r="H20" s="84" t="s">
+      <c r="H20" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="I20" s="85">
+      <c r="I20" s="93">
         <f>[1]IV!$F$9</f>
-        <v>4.35090909090909</v>
+        <v>4.3509090909090897</v>
       </c>
-      <c r="J20" s="86"/>
-      <c r="K20" s="87" t="s">
+      <c r="J20" s="94"/>
+      <c r="K20" s="95" t="s">
         <v>59</v>
       </c>
-      <c r="L20" s="87"/>
-      <c r="M20" s="88" t="s">
+      <c r="L20" s="95"/>
+      <c r="M20" s="96" t="s">
         <v>31</v>
       </c>
-      <c r="N20" s="88"/>
-      <c r="O20" s="88"/>
-      <c r="P20" s="88" t="s">
+      <c r="N20" s="96"/>
+      <c r="O20" s="96"/>
+      <c r="P20" s="96" t="s">
         <v>60</v>
       </c>
-      <c r="Q20" s="88"/>
-      <c r="R20" s="88"/>
-      <c r="S20" s="89" t="s">
+      <c r="Q20" s="96"/>
+      <c r="R20" s="96"/>
+      <c r="S20" s="33" t="s">
         <v>61</v>
       </c>
       <c r="T20" s="3"/>
@@ -20450,40 +19772,40 @@
       <c r="XEO20" s="3"/>
       <c r="XEP20" s="3"/>
     </row>
-    <row r="21" s="1" customFormat="1" spans="1:1024 1025:16370">
-      <c r="A21" s="82"/>
-      <c r="B21" s="83"/>
-      <c r="C21" s="83"/>
-      <c r="D21" s="90" t="s">
+    <row r="21" spans="1:16370" s="1" customFormat="1">
+      <c r="A21" s="31"/>
+      <c r="B21" s="92"/>
+      <c r="C21" s="92"/>
+      <c r="D21" s="100" t="s">
         <v>62</v>
       </c>
-      <c r="E21" s="90"/>
-      <c r="F21" s="90"/>
-      <c r="G21" s="91">
+      <c r="E21" s="100"/>
+      <c r="F21" s="100"/>
+      <c r="G21" s="34">
         <f>[1]PL!$G$9</f>
         <v>75</v>
       </c>
-      <c r="H21" s="84" t="s">
+      <c r="H21" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="I21" s="92">
+      <c r="I21" s="97">
         <f>I20*G20</f>
-        <v>543.863636363636</v>
+        <v>543.86363636363603</v>
       </c>
-      <c r="J21" s="93"/>
-      <c r="K21" s="87" t="s">
+      <c r="J21" s="98"/>
+      <c r="K21" s="95" t="s">
         <v>64</v>
       </c>
-      <c r="L21" s="87"/>
-      <c r="M21" s="87" t="s">
+      <c r="L21" s="95"/>
+      <c r="M21" s="95" t="s">
         <v>65</v>
       </c>
-      <c r="N21" s="87"/>
-      <c r="O21" s="87"/>
-      <c r="P21" s="87"/>
-      <c r="Q21" s="87"/>
-      <c r="R21" s="87"/>
-      <c r="S21" s="89"/>
+      <c r="N21" s="95"/>
+      <c r="O21" s="95"/>
+      <c r="P21" s="95"/>
+      <c r="Q21" s="95"/>
+      <c r="R21" s="95"/>
+      <c r="S21" s="33"/>
       <c r="T21" s="3"/>
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
@@ -36836,33 +36158,33 @@
       <c r="XEO21" s="3"/>
       <c r="XEP21" s="3"/>
     </row>
-    <row r="22" s="1" customFormat="1" spans="1:1024 1025:16370">
-      <c r="A22" s="94"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="95"/>
-      <c r="E22" s="95"/>
-      <c r="F22" s="95"/>
-      <c r="G22" s="96">
+    <row r="22" spans="1:16370" s="1" customFormat="1">
+      <c r="A22" s="35"/>
+      <c r="B22" s="51"/>
+      <c r="C22" s="51"/>
+      <c r="D22" s="101"/>
+      <c r="E22" s="101"/>
+      <c r="F22" s="101"/>
+      <c r="G22" s="36">
         <f>G20</f>
         <v>125</v>
       </c>
-      <c r="H22" s="96" t="s">
+      <c r="H22" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="I22" s="24" t="s">
+      <c r="I22" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="J22" s="97"/>
-      <c r="K22" s="97"/>
-      <c r="L22" s="97"/>
-      <c r="M22" s="97"/>
-      <c r="N22" s="97"/>
-      <c r="O22" s="97"/>
-      <c r="P22" s="97"/>
-      <c r="Q22" s="97"/>
-      <c r="R22" s="97"/>
-      <c r="S22" s="25"/>
+      <c r="J22" s="99"/>
+      <c r="K22" s="99"/>
+      <c r="L22" s="99"/>
+      <c r="M22" s="99"/>
+      <c r="N22" s="99"/>
+      <c r="O22" s="99"/>
+      <c r="P22" s="99"/>
+      <c r="Q22" s="99"/>
+      <c r="R22" s="99"/>
+      <c r="S22" s="10"/>
       <c r="T22" s="3"/>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
@@ -53215,496 +52537,521 @@
       <c r="XEO22" s="3"/>
       <c r="XEP22" s="3"/>
     </row>
-    <row r="23" ht="14.25" spans="1:1024 1025:16370">
-      <c r="A23" s="82">
+    <row r="23" spans="1:16370">
+      <c r="A23" s="31">
         <v>2</v>
       </c>
-      <c r="B23" s="83">
+      <c r="B23" s="92">
         <f>[1]PL!$B$9</f>
         <v>3918909000</v>
       </c>
-      <c r="C23" s="83"/>
-      <c r="D23" s="83" t="s">
+      <c r="C23" s="92"/>
+      <c r="D23" s="92" t="s">
         <v>57</v>
       </c>
-      <c r="E23" s="83"/>
-      <c r="F23" s="83"/>
-      <c r="G23" s="84">
+      <c r="E23" s="92"/>
+      <c r="F23" s="92"/>
+      <c r="G23" s="32">
         <f>[1]IV!$D$10</f>
         <v>192</v>
       </c>
-      <c r="H23" s="84" t="s">
+      <c r="H23" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="I23" s="85">
+      <c r="I23" s="93">
         <f>[1]IV!$F$10</f>
-        <v>9.12181818181818</v>
+        <v>9.1218181818181794</v>
       </c>
-      <c r="J23" s="86"/>
-      <c r="K23" s="87" t="s">
+      <c r="J23" s="94"/>
+      <c r="K23" s="95" t="s">
         <v>59</v>
       </c>
-      <c r="L23" s="87"/>
-      <c r="M23" s="88" t="s">
+      <c r="L23" s="95"/>
+      <c r="M23" s="96" t="s">
         <v>31</v>
       </c>
-      <c r="N23" s="88"/>
-      <c r="O23" s="88"/>
-      <c r="P23" s="88" t="s">
+      <c r="N23" s="96"/>
+      <c r="O23" s="96"/>
+      <c r="P23" s="96" t="s">
         <v>60</v>
       </c>
-      <c r="Q23" s="88"/>
-      <c r="R23" s="88"/>
-      <c r="S23" s="89" t="s">
+      <c r="Q23" s="96"/>
+      <c r="R23" s="96"/>
+      <c r="S23" s="33" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:1024 1025:16370">
-      <c r="A24" s="82"/>
-      <c r="B24" s="83"/>
-      <c r="C24" s="83"/>
-      <c r="D24" s="90" t="s">
+    <row r="24" spans="1:16370">
+      <c r="A24" s="31"/>
+      <c r="B24" s="92"/>
+      <c r="C24" s="92"/>
+      <c r="D24" s="100" t="s">
         <v>62</v>
       </c>
-      <c r="E24" s="90"/>
-      <c r="F24" s="90"/>
-      <c r="G24" s="91">
+      <c r="E24" s="100"/>
+      <c r="F24" s="100"/>
+      <c r="G24" s="34">
         <f>[1]PL!$G$10</f>
         <v>230.4</v>
       </c>
-      <c r="H24" s="84" t="s">
+      <c r="H24" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="I24" s="92">
+      <c r="I24" s="97">
         <f>I23*G23</f>
-        <v>1751.38909090909</v>
+        <v>1751.3890909090901</v>
       </c>
-      <c r="J24" s="93"/>
-      <c r="K24" s="87" t="s">
+      <c r="J24" s="98"/>
+      <c r="K24" s="95" t="s">
         <v>64</v>
       </c>
-      <c r="L24" s="87"/>
-      <c r="M24" s="87" t="s">
+      <c r="L24" s="95"/>
+      <c r="M24" s="95" t="s">
         <v>65</v>
       </c>
-      <c r="N24" s="87"/>
-      <c r="O24" s="87"/>
-      <c r="P24" s="87"/>
-      <c r="Q24" s="87"/>
-      <c r="R24" s="87"/>
-      <c r="S24" s="89"/>
+      <c r="N24" s="95"/>
+      <c r="O24" s="95"/>
+      <c r="P24" s="95"/>
+      <c r="Q24" s="95"/>
+      <c r="R24" s="95"/>
+      <c r="S24" s="33"/>
     </row>
-    <row r="25" spans="1:1024 1025:16370">
-      <c r="A25" s="94"/>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="95"/>
-      <c r="E25" s="95"/>
-      <c r="F25" s="95"/>
-      <c r="G25" s="96">
+    <row r="25" spans="1:16370">
+      <c r="A25" s="35"/>
+      <c r="B25" s="51"/>
+      <c r="C25" s="51"/>
+      <c r="D25" s="101"/>
+      <c r="E25" s="101"/>
+      <c r="F25" s="101"/>
+      <c r="G25" s="36">
         <f>G23</f>
         <v>192</v>
       </c>
-      <c r="H25" s="96" t="s">
+      <c r="H25" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="I25" s="24" t="s">
+      <c r="I25" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="J25" s="97"/>
-      <c r="K25" s="97"/>
-      <c r="L25" s="97"/>
-      <c r="M25" s="97"/>
-      <c r="N25" s="97"/>
-      <c r="O25" s="97"/>
-      <c r="P25" s="97"/>
-      <c r="Q25" s="97"/>
-      <c r="R25" s="97"/>
-      <c r="S25" s="25"/>
+      <c r="J25" s="99"/>
+      <c r="K25" s="99"/>
+      <c r="L25" s="99"/>
+      <c r="M25" s="99"/>
+      <c r="N25" s="99"/>
+      <c r="O25" s="99"/>
+      <c r="P25" s="99"/>
+      <c r="Q25" s="99"/>
+      <c r="R25" s="99"/>
+      <c r="S25" s="10"/>
     </row>
-    <row r="26" ht="14.25" spans="1:1024 1025:16370">
-      <c r="A26" s="82">
+    <row r="26" spans="1:16370">
+      <c r="A26" s="31">
         <v>3</v>
       </c>
-      <c r="B26" s="83">
+      <c r="B26" s="92">
         <f>[1]PL!$B$9</f>
         <v>3918909000</v>
       </c>
-      <c r="C26" s="83"/>
-      <c r="D26" s="83" t="s">
+      <c r="C26" s="92"/>
+      <c r="D26" s="92" t="s">
         <v>57</v>
       </c>
-      <c r="E26" s="83"/>
-      <c r="F26" s="83"/>
-      <c r="G26" s="84">
+      <c r="E26" s="92"/>
+      <c r="F26" s="92"/>
+      <c r="G26" s="32">
         <f>[1]IV!$D$11</f>
         <v>66</v>
       </c>
-      <c r="H26" s="84" t="s">
+      <c r="H26" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="I26" s="85">
+      <c r="I26" s="93">
         <f>[1]IV!$F$11</f>
-        <v>18.6290909090909</v>
+        <v>18.629090909090898</v>
       </c>
-      <c r="J26" s="86"/>
-      <c r="K26" s="87" t="s">
+      <c r="J26" s="94"/>
+      <c r="K26" s="95" t="s">
         <v>59</v>
       </c>
-      <c r="L26" s="87"/>
-      <c r="M26" s="88" t="s">
+      <c r="L26" s="95"/>
+      <c r="M26" s="96" t="s">
         <v>31</v>
       </c>
-      <c r="N26" s="88"/>
-      <c r="O26" s="88"/>
-      <c r="P26" s="88" t="s">
+      <c r="N26" s="96"/>
+      <c r="O26" s="96"/>
+      <c r="P26" s="96" t="s">
         <v>60</v>
       </c>
-      <c r="Q26" s="88"/>
-      <c r="R26" s="88"/>
-      <c r="S26" s="89" t="s">
+      <c r="Q26" s="96"/>
+      <c r="R26" s="96"/>
+      <c r="S26" s="33" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:1024 1025:16370">
-      <c r="A27" s="82"/>
-      <c r="B27" s="83"/>
-      <c r="C27" s="83"/>
-      <c r="D27" s="90" t="s">
+    <row r="27" spans="1:16370">
+      <c r="A27" s="31"/>
+      <c r="B27" s="92"/>
+      <c r="C27" s="92"/>
+      <c r="D27" s="100" t="s">
         <v>62</v>
       </c>
-      <c r="E27" s="90"/>
-      <c r="F27" s="90"/>
-      <c r="G27" s="91">
+      <c r="E27" s="100"/>
+      <c r="F27" s="100"/>
+      <c r="G27" s="34">
         <f>[1]PL!$G$11</f>
         <v>198</v>
       </c>
-      <c r="H27" s="84" t="s">
+      <c r="H27" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="I27" s="92">
+      <c r="I27" s="97">
         <f>I26*G26</f>
         <v>1229.52</v>
       </c>
-      <c r="J27" s="93"/>
-      <c r="K27" s="87" t="s">
+      <c r="J27" s="98"/>
+      <c r="K27" s="95" t="s">
         <v>64</v>
       </c>
-      <c r="L27" s="87"/>
-      <c r="M27" s="87" t="s">
+      <c r="L27" s="95"/>
+      <c r="M27" s="95" t="s">
         <v>65</v>
       </c>
-      <c r="N27" s="87"/>
-      <c r="O27" s="87"/>
-      <c r="P27" s="87"/>
-      <c r="Q27" s="87"/>
-      <c r="R27" s="87"/>
-      <c r="S27" s="89"/>
+      <c r="N27" s="95"/>
+      <c r="O27" s="95"/>
+      <c r="P27" s="95"/>
+      <c r="Q27" s="95"/>
+      <c r="R27" s="95"/>
+      <c r="S27" s="33"/>
     </row>
-    <row r="28" spans="1:1024 1025:16370">
-      <c r="A28" s="94"/>
-      <c r="B28" s="23"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="95"/>
-      <c r="E28" s="95"/>
-      <c r="F28" s="95"/>
-      <c r="G28" s="96">
+    <row r="28" spans="1:16370">
+      <c r="A28" s="35"/>
+      <c r="B28" s="51"/>
+      <c r="C28" s="51"/>
+      <c r="D28" s="101"/>
+      <c r="E28" s="101"/>
+      <c r="F28" s="101"/>
+      <c r="G28" s="36">
         <f>G26</f>
         <v>66</v>
       </c>
-      <c r="H28" s="96" t="s">
+      <c r="H28" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="I28" s="24" t="s">
+      <c r="I28" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="J28" s="97"/>
-      <c r="K28" s="97"/>
-      <c r="L28" s="97"/>
-      <c r="M28" s="97"/>
-      <c r="N28" s="97"/>
-      <c r="O28" s="97"/>
-      <c r="P28" s="97"/>
-      <c r="Q28" s="97"/>
-      <c r="R28" s="97"/>
-      <c r="S28" s="25"/>
+      <c r="J28" s="99"/>
+      <c r="K28" s="99"/>
+      <c r="L28" s="99"/>
+      <c r="M28" s="99"/>
+      <c r="N28" s="99"/>
+      <c r="O28" s="99"/>
+      <c r="P28" s="99"/>
+      <c r="Q28" s="99"/>
+      <c r="R28" s="99"/>
+      <c r="S28" s="10"/>
     </row>
-    <row r="29" ht="14.25" spans="1:1024 1025:16370">
-      <c r="A29" s="82">
+    <row r="29" spans="1:16370">
+      <c r="A29" s="31">
         <v>4</v>
       </c>
-      <c r="B29" s="83">
+      <c r="B29" s="92">
         <f>[1]PL!$B$9</f>
         <v>3918909000</v>
       </c>
-      <c r="C29" s="83"/>
-      <c r="D29" s="83" t="s">
+      <c r="C29" s="92"/>
+      <c r="D29" s="92" t="s">
         <v>57</v>
       </c>
-      <c r="E29" s="83"/>
-      <c r="F29" s="83"/>
-      <c r="G29" s="84">
+      <c r="E29" s="92"/>
+      <c r="F29" s="92"/>
+      <c r="G29" s="32">
         <f>[1]IV!$D$12</f>
         <v>30</v>
       </c>
-      <c r="H29" s="84" t="s">
+      <c r="H29" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="I29" s="85">
+      <c r="I29" s="93">
         <f>[1]IV!$F$12</f>
-        <v>20.4927272727273</v>
+        <v>20.492727272727301</v>
       </c>
-      <c r="J29" s="86"/>
-      <c r="K29" s="87" t="s">
+      <c r="J29" s="94"/>
+      <c r="K29" s="95" t="s">
         <v>59</v>
       </c>
-      <c r="L29" s="87"/>
-      <c r="M29" s="88" t="s">
+      <c r="L29" s="95"/>
+      <c r="M29" s="96" t="s">
         <v>31</v>
       </c>
-      <c r="N29" s="88"/>
-      <c r="O29" s="88"/>
-      <c r="P29" s="88" t="s">
+      <c r="N29" s="96"/>
+      <c r="O29" s="96"/>
+      <c r="P29" s="96" t="s">
         <v>60</v>
       </c>
-      <c r="Q29" s="88"/>
-      <c r="R29" s="88"/>
-      <c r="S29" s="89" t="s">
+      <c r="Q29" s="96"/>
+      <c r="R29" s="96"/>
+      <c r="S29" s="33" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:1024 1025:16370">
-      <c r="A30" s="82"/>
-      <c r="B30" s="83"/>
-      <c r="C30" s="83"/>
-      <c r="D30" s="90" t="s">
+    <row r="30" spans="1:16370">
+      <c r="A30" s="31"/>
+      <c r="B30" s="92"/>
+      <c r="C30" s="92"/>
+      <c r="D30" s="100" t="s">
         <v>62</v>
       </c>
-      <c r="E30" s="90"/>
-      <c r="F30" s="90"/>
-      <c r="G30" s="91">
+      <c r="E30" s="100"/>
+      <c r="F30" s="100"/>
+      <c r="G30" s="34">
         <f>[1]PL!$G$12</f>
         <v>90</v>
       </c>
-      <c r="H30" s="84" t="s">
+      <c r="H30" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="I30" s="92">
+      <c r="I30" s="97">
         <f>I29*G29</f>
-        <v>614.781818181818</v>
+        <v>614.78181818181804</v>
       </c>
-      <c r="J30" s="93"/>
-      <c r="K30" s="87" t="s">
+      <c r="J30" s="98"/>
+      <c r="K30" s="95" t="s">
         <v>64</v>
       </c>
-      <c r="L30" s="87"/>
-      <c r="M30" s="87" t="s">
+      <c r="L30" s="95"/>
+      <c r="M30" s="95" t="s">
         <v>65</v>
       </c>
-      <c r="N30" s="87"/>
-      <c r="O30" s="87"/>
-      <c r="P30" s="87"/>
-      <c r="Q30" s="87"/>
-      <c r="R30" s="87"/>
-      <c r="S30" s="89"/>
+      <c r="N30" s="95"/>
+      <c r="O30" s="95"/>
+      <c r="P30" s="95"/>
+      <c r="Q30" s="95"/>
+      <c r="R30" s="95"/>
+      <c r="S30" s="33"/>
     </row>
-    <row r="31" spans="1:1024 1025:16370">
-      <c r="A31" s="94"/>
-      <c r="B31" s="23"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="95"/>
-      <c r="E31" s="95"/>
-      <c r="F31" s="95"/>
-      <c r="G31" s="96">
+    <row r="31" spans="1:16370">
+      <c r="A31" s="35"/>
+      <c r="B31" s="51"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="101"/>
+      <c r="E31" s="101"/>
+      <c r="F31" s="101"/>
+      <c r="G31" s="36">
         <f>G29</f>
         <v>30</v>
       </c>
-      <c r="H31" s="96" t="s">
+      <c r="H31" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="I31" s="24" t="s">
+      <c r="I31" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="J31" s="97"/>
-      <c r="K31" s="97"/>
-      <c r="L31" s="97"/>
-      <c r="M31" s="97"/>
-      <c r="N31" s="97"/>
-      <c r="O31" s="97"/>
-      <c r="P31" s="97"/>
-      <c r="Q31" s="97"/>
-      <c r="R31" s="97"/>
-      <c r="S31" s="25"/>
+      <c r="J31" s="99"/>
+      <c r="K31" s="99"/>
+      <c r="L31" s="99"/>
+      <c r="M31" s="99"/>
+      <c r="N31" s="99"/>
+      <c r="O31" s="99"/>
+      <c r="P31" s="99"/>
+      <c r="Q31" s="99"/>
+      <c r="R31" s="99"/>
+      <c r="S31" s="10"/>
     </row>
-    <row r="32" ht="14.25" spans="1:1024 1025:16370">
-      <c r="A32" s="82">
+    <row r="32" spans="1:16370">
+      <c r="A32" s="31">
         <v>5</v>
       </c>
-      <c r="B32" s="83">
+      <c r="B32" s="92">
         <f>[1]PL!$B$9</f>
         <v>3918909000</v>
       </c>
-      <c r="C32" s="83"/>
-      <c r="D32" s="83" t="s">
+      <c r="C32" s="92"/>
+      <c r="D32" s="92" t="s">
         <v>57</v>
       </c>
-      <c r="E32" s="83"/>
-      <c r="F32" s="83"/>
-      <c r="G32" s="84">
+      <c r="E32" s="92"/>
+      <c r="F32" s="92"/>
+      <c r="G32" s="32">
         <f>[1]IV!$D$13</f>
         <v>40</v>
       </c>
-      <c r="H32" s="84" t="s">
+      <c r="H32" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="I32" s="85">
+      <c r="I32" s="93">
         <f>[1]IV!$F$13</f>
-        <v>30.2072727272727</v>
+        <v>30.207272727272699</v>
       </c>
-      <c r="J32" s="86"/>
-      <c r="K32" s="87" t="s">
+      <c r="J32" s="94"/>
+      <c r="K32" s="95" t="s">
         <v>59</v>
       </c>
-      <c r="L32" s="87"/>
-      <c r="M32" s="88" t="s">
+      <c r="L32" s="95"/>
+      <c r="M32" s="96" t="s">
         <v>31</v>
       </c>
-      <c r="N32" s="88"/>
-      <c r="O32" s="88"/>
-      <c r="P32" s="88" t="s">
+      <c r="N32" s="96"/>
+      <c r="O32" s="96"/>
+      <c r="P32" s="96" t="s">
         <v>60</v>
       </c>
-      <c r="Q32" s="88"/>
-      <c r="R32" s="88"/>
-      <c r="S32" s="89" t="s">
+      <c r="Q32" s="96"/>
+      <c r="R32" s="96"/>
+      <c r="S32" s="33" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="82"/>
-      <c r="B33" s="83"/>
-      <c r="C33" s="83"/>
-      <c r="D33" s="90" t="s">
+      <c r="A33" s="31"/>
+      <c r="B33" s="92"/>
+      <c r="C33" s="92"/>
+      <c r="D33" s="100" t="s">
         <v>62</v>
       </c>
-      <c r="E33" s="90"/>
-      <c r="F33" s="90"/>
-      <c r="G33" s="91">
+      <c r="E33" s="100"/>
+      <c r="F33" s="100"/>
+      <c r="G33" s="34">
         <f>[1]PL!$G$13</f>
         <v>168</v>
       </c>
-      <c r="H33" s="84" t="s">
+      <c r="H33" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="I33" s="92">
+      <c r="I33" s="97">
         <f>I32*G32</f>
         <v>1208.29090909091</v>
       </c>
-      <c r="J33" s="93"/>
-      <c r="K33" s="87" t="s">
+      <c r="J33" s="98"/>
+      <c r="K33" s="95" t="s">
         <v>64</v>
       </c>
-      <c r="L33" s="87"/>
-      <c r="M33" s="87" t="s">
+      <c r="L33" s="95"/>
+      <c r="M33" s="95" t="s">
         <v>65</v>
       </c>
-      <c r="N33" s="87"/>
-      <c r="O33" s="87"/>
-      <c r="P33" s="87"/>
-      <c r="Q33" s="87"/>
-      <c r="R33" s="87"/>
-      <c r="S33" s="89"/>
+      <c r="N33" s="95"/>
+      <c r="O33" s="95"/>
+      <c r="P33" s="95"/>
+      <c r="Q33" s="95"/>
+      <c r="R33" s="95"/>
+      <c r="S33" s="33"/>
     </row>
     <row r="34" spans="1:19">
-      <c r="A34" s="94"/>
-      <c r="B34" s="23"/>
-      <c r="C34" s="23"/>
-      <c r="D34" s="95"/>
-      <c r="E34" s="95"/>
-      <c r="F34" s="95"/>
-      <c r="G34" s="96">
+      <c r="A34" s="35"/>
+      <c r="B34" s="51"/>
+      <c r="C34" s="51"/>
+      <c r="D34" s="101"/>
+      <c r="E34" s="101"/>
+      <c r="F34" s="101"/>
+      <c r="G34" s="36">
         <f>G32</f>
         <v>40</v>
       </c>
-      <c r="H34" s="96" t="s">
+      <c r="H34" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="I34" s="24" t="s">
+      <c r="I34" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="J34" s="97"/>
-      <c r="K34" s="97"/>
-      <c r="L34" s="97"/>
-      <c r="M34" s="97"/>
-      <c r="N34" s="97"/>
-      <c r="O34" s="97"/>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="97"/>
-      <c r="S34" s="25"/>
+      <c r="J34" s="99"/>
+      <c r="K34" s="99"/>
+      <c r="L34" s="99"/>
+      <c r="M34" s="99"/>
+      <c r="N34" s="99"/>
+      <c r="O34" s="99"/>
+      <c r="P34" s="99"/>
+      <c r="Q34" s="99"/>
+      <c r="R34" s="99"/>
+      <c r="S34" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="160">
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="J2:N2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="K4:N4"/>
-    <mergeCell ref="O4:S4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="O6:S6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="P7:S7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="O8:S8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="P9:S9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:J10"/>
-    <mergeCell ref="K10:N10"/>
-    <mergeCell ref="O10:S10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="Q12:S12"/>
-    <mergeCell ref="C13:S13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="D14:S14"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="M34:O34"/>
+    <mergeCell ref="P34:R34"/>
+    <mergeCell ref="D21:F22"/>
+    <mergeCell ref="D24:F25"/>
+    <mergeCell ref="D27:F28"/>
+    <mergeCell ref="D30:F31"/>
+    <mergeCell ref="D33:F34"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="M32:O32"/>
+    <mergeCell ref="P32:R32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="M33:O33"/>
+    <mergeCell ref="P33:R33"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="M30:O30"/>
+    <mergeCell ref="P30:R30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="M31:O31"/>
+    <mergeCell ref="P31:R31"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="M28:O28"/>
+    <mergeCell ref="P28:R28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="M29:O29"/>
+    <mergeCell ref="P29:R29"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="M26:O26"/>
+    <mergeCell ref="P26:R26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="M27:O27"/>
+    <mergeCell ref="P27:R27"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="P24:R24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="M25:O25"/>
+    <mergeCell ref="P25:R25"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="M22:O22"/>
+    <mergeCell ref="P22:R22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="M23:O23"/>
+    <mergeCell ref="P23:R23"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="M20:O20"/>
+    <mergeCell ref="P20:R20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="M21:O21"/>
+    <mergeCell ref="P21:R21"/>
     <mergeCell ref="C15:S15"/>
     <mergeCell ref="B16:S16"/>
     <mergeCell ref="A17:K17"/>
@@ -53720,94 +53067,68 @@
     <mergeCell ref="K19:L19"/>
     <mergeCell ref="M19:O19"/>
     <mergeCell ref="P19:R19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="M20:O20"/>
-    <mergeCell ref="P20:R20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="M21:O21"/>
-    <mergeCell ref="P21:R21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="M22:O22"/>
-    <mergeCell ref="P22:R22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="M23:O23"/>
-    <mergeCell ref="P23:R23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="P24:R24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="M25:O25"/>
-    <mergeCell ref="P25:R25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="M26:O26"/>
-    <mergeCell ref="P26:R26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="M27:O27"/>
-    <mergeCell ref="P27:R27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="M28:O28"/>
-    <mergeCell ref="P28:R28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="M29:O29"/>
-    <mergeCell ref="P29:R29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="M30:O30"/>
-    <mergeCell ref="P30:R30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="M31:O31"/>
-    <mergeCell ref="P31:R31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="M32:O32"/>
-    <mergeCell ref="P32:R32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="M33:O33"/>
-    <mergeCell ref="P33:R33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="M34:O34"/>
-    <mergeCell ref="P34:R34"/>
-    <mergeCell ref="D21:F22"/>
-    <mergeCell ref="D24:F25"/>
-    <mergeCell ref="D27:F28"/>
-    <mergeCell ref="D30:F31"/>
-    <mergeCell ref="D33:F34"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="Q12:S12"/>
+    <mergeCell ref="C13:S13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="D14:S14"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:J10"/>
+    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="O10:S10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="O8:S8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="P9:S9"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="O6:S6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="P7:S7"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="O4:S4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="J2:N2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="P3:S3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="70" orientation="landscape"/>
-  <headerFooter/>
 </worksheet>
 </file>